--- a/data/values.xlsx
+++ b/data/values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\extreme_weather_risk\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4574C322-EA65-48FF-993A-6D1C9DE7A2FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15F6972D-F1B0-4060-BEE6-242680179736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25710" yWindow="-4220" windowWidth="19070" windowHeight="12010" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="responses" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2552" uniqueCount="700">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2559" uniqueCount="707">
   <si>
     <t>id_I</t>
   </si>
@@ -3775,12 +3775,33 @@
       <t> </t>
     </r>
   </si>
+  <si>
+    <t>hww</t>
+  </si>
+  <si>
+    <t>hws</t>
+  </si>
+  <si>
+    <t>ici</t>
+  </si>
+  <si>
+    <t>abl</t>
+  </si>
+  <si>
+    <t>erf</t>
+  </si>
+  <si>
+    <t>gal</t>
+  </si>
+  <si>
+    <t>sto</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3814,13 +3835,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -3880,7 +3894,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3936,33 +3950,17 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8301,7 +8299,7 @@
       <c r="D223" t="s">
         <v>32</v>
       </c>
-      <c r="E223" s="22" t="s">
+      <c r="E223" s="16" t="s">
         <v>269</v>
       </c>
     </row>
@@ -8318,7 +8316,7 @@
       <c r="D224" t="s">
         <v>5</v>
       </c>
-      <c r="E224" s="22" t="s">
+      <c r="E224" s="16" t="s">
         <v>343</v>
       </c>
     </row>
@@ -8335,7 +8333,7 @@
       <c r="D225" t="s">
         <v>6</v>
       </c>
-      <c r="E225" s="22" t="s">
+      <c r="E225" s="16" t="s">
         <v>344</v>
       </c>
       <c r="F225" s="8">
@@ -8355,7 +8353,7 @@
       <c r="D226" t="s">
         <v>7</v>
       </c>
-      <c r="E226" s="22" t="s">
+      <c r="E226" s="16" t="s">
         <v>345</v>
       </c>
       <c r="F226" s="8">
@@ -8375,7 +8373,7 @@
       <c r="D227" t="s">
         <v>8</v>
       </c>
-      <c r="E227" s="22" t="s">
+      <c r="E227" s="16" t="s">
         <v>346</v>
       </c>
       <c r="F227" s="8">
@@ -8395,7 +8393,7 @@
       <c r="D228" t="s">
         <v>9</v>
       </c>
-      <c r="E228" s="22" t="s">
+      <c r="E228" s="16" t="s">
         <v>347</v>
       </c>
       <c r="F228" s="8">
@@ -8415,7 +8413,7 @@
       <c r="D229" t="s">
         <v>10</v>
       </c>
-      <c r="E229" s="22" t="s">
+      <c r="E229" s="16" t="s">
         <v>348</v>
       </c>
       <c r="F229" s="8">
@@ -8435,7 +8433,7 @@
       <c r="D230" t="s">
         <v>11</v>
       </c>
-      <c r="E230" s="22" t="s">
+      <c r="E230" s="16" t="s">
         <v>348</v>
       </c>
       <c r="F230" s="8">
@@ -8455,7 +8453,7 @@
       <c r="D231" t="s">
         <v>12</v>
       </c>
-      <c r="E231" s="22" t="s">
+      <c r="E231" s="16" t="s">
         <v>349</v>
       </c>
     </row>
@@ -8472,7 +8470,7 @@
       <c r="D232" t="s">
         <v>5</v>
       </c>
-      <c r="E232" s="22" t="s">
+      <c r="E232" s="16" t="s">
         <v>350</v>
       </c>
     </row>
@@ -8489,7 +8487,7 @@
       <c r="D233" t="s">
         <v>6</v>
       </c>
-      <c r="E233" s="22" t="s">
+      <c r="E233" s="16" t="s">
         <v>351</v>
       </c>
       <c r="F233" s="8">
@@ -8509,7 +8507,7 @@
       <c r="D234" t="s">
         <v>7</v>
       </c>
-      <c r="E234" s="22" t="s">
+      <c r="E234" s="16" t="s">
         <v>352</v>
       </c>
     </row>
@@ -8526,7 +8524,7 @@
       <c r="D235" t="s">
         <v>8</v>
       </c>
-      <c r="E235" s="22" t="s">
+      <c r="E235" s="16" t="s">
         <v>353</v>
       </c>
       <c r="F235" s="8" t="s">
@@ -8546,7 +8544,7 @@
       <c r="D236" t="s">
         <v>9</v>
       </c>
-      <c r="E236" s="22" t="s">
+      <c r="E236" s="16" t="s">
         <v>354</v>
       </c>
       <c r="F236" s="8">
@@ -8566,7 +8564,7 @@
       <c r="D237" t="s">
         <v>10</v>
       </c>
-      <c r="E237" s="22" t="s">
+      <c r="E237" s="16" t="s">
         <v>355</v>
       </c>
       <c r="F237" s="8" t="s">
@@ -8586,7 +8584,7 @@
       <c r="D238" t="s">
         <v>11</v>
       </c>
-      <c r="E238" s="22" t="s">
+      <c r="E238" s="16" t="s">
         <v>356</v>
       </c>
     </row>
@@ -8603,7 +8601,7 @@
       <c r="D239" t="s">
         <v>5</v>
       </c>
-      <c r="E239" s="22" t="s">
+      <c r="E239" s="16" t="s">
         <v>357</v>
       </c>
     </row>
@@ -8620,7 +8618,7 @@
       <c r="D240" t="s">
         <v>6</v>
       </c>
-      <c r="E240" s="22" t="s">
+      <c r="E240" s="16" t="s">
         <v>358</v>
       </c>
       <c r="F240" s="8">
@@ -8640,7 +8638,7 @@
       <c r="D241" t="s">
         <v>7</v>
       </c>
-      <c r="E241" s="22" t="s">
+      <c r="E241" s="16" t="s">
         <v>359</v>
       </c>
     </row>
@@ -8657,7 +8655,7 @@
       <c r="D242" t="s">
         <v>8</v>
       </c>
-      <c r="E242" s="22" t="s">
+      <c r="E242" s="16" t="s">
         <v>360</v>
       </c>
       <c r="F242" s="8">
@@ -8677,7 +8675,7 @@
       <c r="D243" t="s">
         <v>9</v>
       </c>
-      <c r="E243" s="22" t="s">
+      <c r="E243" s="16" t="s">
         <v>361</v>
       </c>
       <c r="F243" s="8">
@@ -8697,7 +8695,7 @@
       <c r="D244" t="s">
         <v>10</v>
       </c>
-      <c r="E244" s="22">
+      <c r="E244" s="16">
         <v>1</v>
       </c>
       <c r="F244" s="8">
@@ -8717,7 +8715,7 @@
       <c r="D245" t="s">
         <v>11</v>
       </c>
-      <c r="E245" s="22">
+      <c r="E245" s="16">
         <v>1</v>
       </c>
       <c r="F245" s="8">
@@ -8737,7 +8735,7 @@
       <c r="D246" t="s">
         <v>5</v>
       </c>
-      <c r="E246" s="22" t="s">
+      <c r="E246" s="16" t="s">
         <v>359</v>
       </c>
     </row>
@@ -8754,7 +8752,7 @@
       <c r="D247" t="s">
         <v>6</v>
       </c>
-      <c r="E247" s="22" t="s">
+      <c r="E247" s="16" t="s">
         <v>362</v>
       </c>
       <c r="F247" s="8">
@@ -8774,7 +8772,7 @@
       <c r="D248" t="s">
         <v>7</v>
       </c>
-      <c r="E248" s="22" t="s">
+      <c r="E248" s="16" t="s">
         <v>359</v>
       </c>
     </row>
@@ -8791,7 +8789,7 @@
       <c r="D249" t="s">
         <v>8</v>
       </c>
-      <c r="E249" s="22" t="s">
+      <c r="E249" s="16" t="s">
         <v>363</v>
       </c>
     </row>
@@ -8808,7 +8806,7 @@
       <c r="D250" t="s">
         <v>9</v>
       </c>
-      <c r="E250" s="22" t="s">
+      <c r="E250" s="16" t="s">
         <v>364</v>
       </c>
       <c r="F250" s="8">
@@ -8828,7 +8826,7 @@
       <c r="D251" t="s">
         <v>10</v>
       </c>
-      <c r="E251" s="22" t="s">
+      <c r="E251" s="16" t="s">
         <v>364</v>
       </c>
       <c r="F251" s="8">
@@ -8848,7 +8846,7 @@
       <c r="D252" t="s">
         <v>11</v>
       </c>
-      <c r="E252" s="22" t="s">
+      <c r="E252" s="16" t="s">
         <v>364</v>
       </c>
       <c r="F252" s="8">
@@ -8868,7 +8866,6 @@
       <c r="D253" t="s">
         <v>5</v>
       </c>
-      <c r="E253" s="22"/>
     </row>
     <row r="254" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A254">
@@ -8883,7 +8880,7 @@
       <c r="D254" t="s">
         <v>6</v>
       </c>
-      <c r="E254" s="22" t="s">
+      <c r="E254" s="16" t="s">
         <v>365</v>
       </c>
       <c r="F254" s="8">
@@ -8903,7 +8900,6 @@
       <c r="D255" t="s">
         <v>7</v>
       </c>
-      <c r="E255" s="22"/>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A256">
@@ -8918,7 +8914,6 @@
       <c r="D256" t="s">
         <v>8</v>
       </c>
-      <c r="E256" s="22"/>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A257">
@@ -8933,7 +8928,6 @@
       <c r="D257" t="s">
         <v>9</v>
       </c>
-      <c r="E257" s="22"/>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A258">
@@ -8948,7 +8942,6 @@
       <c r="D258" t="s">
         <v>10</v>
       </c>
-      <c r="E258" s="22"/>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A259">
@@ -8963,7 +8956,6 @@
       <c r="D259" t="s">
         <v>11</v>
       </c>
-      <c r="E259" s="22"/>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A260">
@@ -8978,7 +8970,6 @@
       <c r="D260" t="s">
         <v>5</v>
       </c>
-      <c r="E260" s="22"/>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A261">
@@ -8993,7 +8984,6 @@
       <c r="D261" t="s">
         <v>6</v>
       </c>
-      <c r="E261" s="22"/>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A262">
@@ -9008,7 +8998,6 @@
       <c r="D262" t="s">
         <v>7</v>
       </c>
-      <c r="E262" s="22"/>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A263">
@@ -9023,7 +9012,6 @@
       <c r="D263" t="s">
         <v>8</v>
       </c>
-      <c r="E263" s="22"/>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A264">
@@ -9038,7 +9026,6 @@
       <c r="D264" t="s">
         <v>9</v>
       </c>
-      <c r="E264" s="22"/>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A265">
@@ -9053,7 +9040,6 @@
       <c r="D265" t="s">
         <v>10</v>
       </c>
-      <c r="E265" s="22"/>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A266">
@@ -9068,7 +9054,6 @@
       <c r="D266" t="s">
         <v>11</v>
       </c>
-      <c r="E266" s="22"/>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A267">
@@ -9083,7 +9068,7 @@
       <c r="D267" t="s">
         <v>98</v>
       </c>
-      <c r="E267" s="23">
+      <c r="E267" s="18">
         <v>1</v>
       </c>
       <c r="F267" s="8">
@@ -9103,7 +9088,7 @@
       <c r="D268" t="s">
         <v>32</v>
       </c>
-      <c r="E268" s="23" t="s">
+      <c r="E268" s="18" t="s">
         <v>379</v>
       </c>
       <c r="F268" s="8">
@@ -9123,7 +9108,7 @@
       <c r="D269" t="s">
         <v>5</v>
       </c>
-      <c r="E269" s="22" t="s">
+      <c r="E269" s="16" t="s">
         <v>366</v>
       </c>
     </row>
@@ -9140,7 +9125,7 @@
       <c r="D270" t="s">
         <v>6</v>
       </c>
-      <c r="E270" s="22">
+      <c r="E270" s="16">
         <v>0</v>
       </c>
       <c r="F270" s="8">
@@ -9160,7 +9145,7 @@
       <c r="D271" t="s">
         <v>7</v>
       </c>
-      <c r="E271" s="22" t="s">
+      <c r="E271" s="16" t="s">
         <v>366</v>
       </c>
     </row>
@@ -9177,7 +9162,7 @@
       <c r="D272" t="s">
         <v>8</v>
       </c>
-      <c r="E272" s="22">
+      <c r="E272" s="16">
         <v>0</v>
       </c>
       <c r="F272" s="8">
@@ -9197,7 +9182,7 @@
       <c r="D273" t="s">
         <v>9</v>
       </c>
-      <c r="E273" s="22">
+      <c r="E273" s="16">
         <v>0</v>
       </c>
       <c r="F273" s="8">
@@ -9217,7 +9202,7 @@
       <c r="D274" t="s">
         <v>10</v>
       </c>
-      <c r="E274" s="22" t="s">
+      <c r="E274" s="16" t="s">
         <v>367</v>
       </c>
     </row>
@@ -9234,7 +9219,7 @@
       <c r="D275" t="s">
         <v>11</v>
       </c>
-      <c r="E275" s="22" t="s">
+      <c r="E275" s="16" t="s">
         <v>368</v>
       </c>
     </row>
@@ -9251,7 +9236,6 @@
       <c r="D276" t="s">
         <v>5</v>
       </c>
-      <c r="E276" s="22"/>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A277">
@@ -9266,7 +9250,6 @@
       <c r="D277" t="s">
         <v>6</v>
       </c>
-      <c r="E277" s="22"/>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A278">
@@ -9281,7 +9264,6 @@
       <c r="D278" t="s">
         <v>7</v>
       </c>
-      <c r="E278" s="22"/>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A279">
@@ -9296,7 +9278,7 @@
       <c r="D279" t="s">
         <v>8</v>
       </c>
-      <c r="E279" s="22" t="s">
+      <c r="E279" s="16" t="s">
         <v>369</v>
       </c>
       <c r="F279" s="8">
@@ -9316,7 +9298,7 @@
       <c r="D280" t="s">
         <v>9</v>
       </c>
-      <c r="E280" s="22">
+      <c r="E280" s="16">
         <v>0</v>
       </c>
       <c r="F280" s="8">
@@ -9336,7 +9318,7 @@
       <c r="D281" t="s">
         <v>10</v>
       </c>
-      <c r="E281" s="22" t="s">
+      <c r="E281" s="16" t="s">
         <v>370</v>
       </c>
     </row>
@@ -9353,7 +9335,7 @@
       <c r="D282" t="s">
         <v>11</v>
       </c>
-      <c r="E282" s="22" t="s">
+      <c r="E282" s="16" t="s">
         <v>370</v>
       </c>
     </row>
@@ -9370,7 +9352,7 @@
       <c r="D283" t="s">
         <v>32</v>
       </c>
-      <c r="E283" s="23" t="s">
+      <c r="E283" s="18" t="s">
         <v>381</v>
       </c>
     </row>
@@ -9387,7 +9369,7 @@
       <c r="D284" t="s">
         <v>32</v>
       </c>
-      <c r="E284" s="23" t="s">
+      <c r="E284" s="18" t="s">
         <v>382</v>
       </c>
     </row>
@@ -9404,7 +9386,7 @@
       <c r="D285" t="s">
         <v>5</v>
       </c>
-      <c r="E285" s="22" t="s">
+      <c r="E285" s="16" t="s">
         <v>366</v>
       </c>
     </row>
@@ -9421,7 +9403,7 @@
       <c r="D286" t="s">
         <v>6</v>
       </c>
-      <c r="E286" s="22" t="s">
+      <c r="E286" s="16" t="s">
         <v>371</v>
       </c>
       <c r="F286" s="8">
@@ -9441,7 +9423,7 @@
       <c r="D287" t="s">
         <v>7</v>
       </c>
-      <c r="E287" s="22" t="s">
+      <c r="E287" s="16" t="s">
         <v>366</v>
       </c>
     </row>
@@ -9458,7 +9440,7 @@
       <c r="D288" t="s">
         <v>8</v>
       </c>
-      <c r="E288" s="22" t="s">
+      <c r="E288" s="16" t="s">
         <v>372</v>
       </c>
     </row>
@@ -9475,7 +9457,7 @@
       <c r="D289" t="s">
         <v>9</v>
       </c>
-      <c r="E289" s="22">
+      <c r="E289" s="16">
         <v>0</v>
       </c>
       <c r="F289" s="8">
@@ -9495,7 +9477,7 @@
       <c r="D290" t="s">
         <v>10</v>
       </c>
-      <c r="E290" s="22" t="s">
+      <c r="E290" s="16" t="s">
         <v>373</v>
       </c>
       <c r="F290" s="8">
@@ -9515,7 +9497,7 @@
       <c r="D291" t="s">
         <v>11</v>
       </c>
-      <c r="E291" s="22" t="s">
+      <c r="E291" s="16" t="s">
         <v>380</v>
       </c>
     </row>
@@ -9532,7 +9514,7 @@
       <c r="D292" t="s">
         <v>32</v>
       </c>
-      <c r="E292" s="23" t="s">
+      <c r="E292" s="18" t="s">
         <v>383</v>
       </c>
       <c r="F292" s="8">
@@ -9552,7 +9534,6 @@
       <c r="D293" t="s">
         <v>5</v>
       </c>
-      <c r="E293" s="22"/>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A294">
@@ -9567,7 +9548,7 @@
       <c r="D294" t="s">
         <v>6</v>
       </c>
-      <c r="E294" s="22" t="s">
+      <c r="E294" s="16" t="s">
         <v>374</v>
       </c>
       <c r="F294" s="8">
@@ -9587,7 +9568,7 @@
       <c r="D295" t="s">
         <v>7</v>
       </c>
-      <c r="E295" s="22" t="s">
+      <c r="E295" s="16" t="s">
         <v>366</v>
       </c>
     </row>
@@ -9604,7 +9585,7 @@
       <c r="D296" t="s">
         <v>8</v>
       </c>
-      <c r="E296" s="22" t="s">
+      <c r="E296" s="16" t="s">
         <v>375</v>
       </c>
       <c r="F296" s="8">
@@ -9624,7 +9605,7 @@
       <c r="D297" t="s">
         <v>9</v>
       </c>
-      <c r="E297" s="22" t="s">
+      <c r="E297" s="16" t="s">
         <v>376</v>
       </c>
     </row>
@@ -9641,7 +9622,7 @@
       <c r="D298" t="s">
         <v>10</v>
       </c>
-      <c r="E298" s="22" t="s">
+      <c r="E298" s="16" t="s">
         <v>377</v>
       </c>
     </row>
@@ -9658,7 +9639,7 @@
       <c r="D299" t="s">
         <v>11</v>
       </c>
-      <c r="E299" s="22" t="s">
+      <c r="E299" s="16" t="s">
         <v>378</v>
       </c>
     </row>
@@ -9675,7 +9656,7 @@
       <c r="D300" t="s">
         <v>32</v>
       </c>
-      <c r="E300" s="22" t="s">
+      <c r="E300" s="16" t="s">
         <v>384</v>
       </c>
     </row>
@@ -9692,7 +9673,7 @@
       <c r="D301" t="s">
         <v>32</v>
       </c>
-      <c r="E301" s="23" t="s">
+      <c r="E301" s="18" t="s">
         <v>385</v>
       </c>
       <c r="F301" s="8">
@@ -9712,7 +9693,7 @@
       <c r="D302" t="s">
         <v>32</v>
       </c>
-      <c r="E302" s="22" t="s">
+      <c r="E302" s="16" t="s">
         <v>386</v>
       </c>
       <c r="F302" s="8">
@@ -9732,7 +9713,7 @@
       <c r="D303" t="s">
         <v>32</v>
       </c>
-      <c r="E303" s="23" t="s">
+      <c r="E303" s="18" t="s">
         <v>387</v>
       </c>
       <c r="F303" s="8">
@@ -9752,7 +9733,7 @@
       <c r="D304" t="s">
         <v>32</v>
       </c>
-      <c r="E304" s="23" t="s">
+      <c r="E304" s="18" t="s">
         <v>388</v>
       </c>
       <c r="F304" s="8">
@@ -9772,7 +9753,7 @@
       <c r="D305" t="s">
         <v>5</v>
       </c>
-      <c r="E305" s="23" t="s">
+      <c r="E305" s="18" t="s">
         <v>389</v>
       </c>
       <c r="F305" s="8">
@@ -9792,7 +9773,7 @@
       <c r="D306" t="s">
         <v>6</v>
       </c>
-      <c r="E306" s="23" t="s">
+      <c r="E306" s="18" t="s">
         <v>390</v>
       </c>
       <c r="F306" s="8">
@@ -9812,7 +9793,7 @@
       <c r="D307" t="s">
         <v>7</v>
       </c>
-      <c r="E307" s="23" t="s">
+      <c r="E307" s="18" t="s">
         <v>391</v>
       </c>
       <c r="F307" s="8">
@@ -9832,7 +9813,7 @@
       <c r="D308" t="s">
         <v>32</v>
       </c>
-      <c r="E308" s="23" t="s">
+      <c r="E308" s="18" t="s">
         <v>392</v>
       </c>
       <c r="F308" s="8">
@@ -9852,7 +9833,7 @@
       <c r="D309" t="s">
         <v>32</v>
       </c>
-      <c r="E309" s="22" t="s">
+      <c r="E309" s="16" t="s">
         <v>393</v>
       </c>
       <c r="F309" s="8">
@@ -9872,7 +9853,7 @@
       <c r="D310" t="s">
         <v>32</v>
       </c>
-      <c r="E310" s="23" t="s">
+      <c r="E310" s="18" t="s">
         <v>394</v>
       </c>
       <c r="F310" s="8">
@@ -9892,7 +9873,7 @@
       <c r="D311" t="s">
         <v>32</v>
       </c>
-      <c r="E311" s="23" t="s">
+      <c r="E311" s="18" t="s">
         <v>395</v>
       </c>
       <c r="F311" s="8">
@@ -9912,7 +9893,7 @@
       <c r="D312" t="s">
         <v>32</v>
       </c>
-      <c r="E312" s="23" t="s">
+      <c r="E312" s="18" t="s">
         <v>396</v>
       </c>
       <c r="F312" s="8">
@@ -9932,7 +9913,7 @@
       <c r="D313" t="s">
         <v>32</v>
       </c>
-      <c r="E313" s="22" t="s">
+      <c r="E313" s="16" t="s">
         <v>397</v>
       </c>
       <c r="F313" s="8">
@@ -9952,7 +9933,7 @@
       <c r="D314" t="s">
         <v>32</v>
       </c>
-      <c r="E314" s="23" t="s">
+      <c r="E314" s="18" t="s">
         <v>398</v>
       </c>
       <c r="F314" s="8">
@@ -9972,7 +9953,7 @@
       <c r="D315" t="s">
         <v>32</v>
       </c>
-      <c r="E315" s="22" t="s">
+      <c r="E315" s="16" t="s">
         <v>399</v>
       </c>
       <c r="F315" s="8">
@@ -9992,7 +9973,7 @@
       <c r="D316" t="s">
         <v>32</v>
       </c>
-      <c r="E316" s="23" t="s">
+      <c r="E316" s="18" t="s">
         <v>400</v>
       </c>
       <c r="F316" s="8">
@@ -10012,7 +9993,7 @@
       <c r="D317" t="s">
         <v>32</v>
       </c>
-      <c r="E317" s="23" t="s">
+      <c r="E317" s="18" t="s">
         <v>401</v>
       </c>
       <c r="F317" s="8">
@@ -10032,7 +10013,7 @@
       <c r="D318" t="s">
         <v>32</v>
       </c>
-      <c r="E318" s="22">
+      <c r="E318" s="16">
         <v>5</v>
       </c>
       <c r="F318" s="8">
@@ -10052,7 +10033,7 @@
       <c r="D319" t="s">
         <v>32</v>
       </c>
-      <c r="E319" s="23" t="s">
+      <c r="E319" s="18" t="s">
         <v>402</v>
       </c>
       <c r="F319" s="8">
@@ -10072,7 +10053,7 @@
       <c r="D320" t="s">
         <v>32</v>
       </c>
-      <c r="E320" s="22" t="s">
+      <c r="E320" s="16" t="s">
         <v>403</v>
       </c>
       <c r="F320" s="8">
@@ -10092,7 +10073,7 @@
       <c r="D321" t="s">
         <v>32</v>
       </c>
-      <c r="E321" s="23" t="s">
+      <c r="E321" s="18" t="s">
         <v>404</v>
       </c>
     </row>
@@ -10109,7 +10090,7 @@
       <c r="D322" t="s">
         <v>32</v>
       </c>
-      <c r="E322" s="23" t="s">
+      <c r="E322" s="18" t="s">
         <v>405</v>
       </c>
     </row>
@@ -10126,7 +10107,7 @@
       <c r="D323" t="s">
         <v>32</v>
       </c>
-      <c r="E323" s="22" t="s">
+      <c r="E323" s="16" t="s">
         <v>406</v>
       </c>
     </row>
@@ -10143,7 +10124,7 @@
       <c r="D324" t="s">
         <v>32</v>
       </c>
-      <c r="E324" s="23" t="s">
+      <c r="E324" s="18" t="s">
         <v>407</v>
       </c>
     </row>
@@ -10160,7 +10141,7 @@
       <c r="D325" t="s">
         <v>32</v>
       </c>
-      <c r="E325" s="22" t="s">
+      <c r="E325" s="16" t="s">
         <v>408</v>
       </c>
     </row>
@@ -10177,7 +10158,7 @@
       <c r="D326" t="s">
         <v>32</v>
       </c>
-      <c r="E326" s="23" t="s">
+      <c r="E326" s="18" t="s">
         <v>409</v>
       </c>
     </row>
@@ -10194,7 +10175,7 @@
       <c r="D327" t="s">
         <v>32</v>
       </c>
-      <c r="E327" s="23" t="s">
+      <c r="E327" s="18" t="s">
         <v>410</v>
       </c>
     </row>
@@ -10211,7 +10192,7 @@
       <c r="D328" t="s">
         <v>32</v>
       </c>
-      <c r="E328" s="23" t="s">
+      <c r="E328" s="18" t="s">
         <v>411</v>
       </c>
     </row>
@@ -10228,7 +10209,7 @@
       <c r="D329" t="s">
         <v>32</v>
       </c>
-      <c r="E329" s="23" t="s">
+      <c r="E329" s="18" t="s">
         <v>412</v>
       </c>
     </row>
@@ -10245,7 +10226,7 @@
       <c r="D330" t="s">
         <v>32</v>
       </c>
-      <c r="E330" s="22" t="s">
+      <c r="E330" s="16" t="s">
         <v>413</v>
       </c>
     </row>
@@ -10262,7 +10243,7 @@
       <c r="D331" t="s">
         <v>32</v>
       </c>
-      <c r="E331" s="22" t="s">
+      <c r="E331" s="16" t="s">
         <v>414</v>
       </c>
     </row>
@@ -10279,7 +10260,7 @@
       <c r="D332" t="s">
         <v>32</v>
       </c>
-      <c r="E332" s="22" t="s">
+      <c r="E332" s="16" t="s">
         <v>483</v>
       </c>
     </row>
@@ -10296,7 +10277,7 @@
       <c r="D333" t="s">
         <v>5</v>
       </c>
-      <c r="E333" s="22" t="s">
+      <c r="E333" s="16" t="s">
         <v>415</v>
       </c>
       <c r="F333" s="8">
@@ -10316,7 +10297,7 @@
       <c r="D334" t="s">
         <v>6</v>
       </c>
-      <c r="E334" s="22" t="s">
+      <c r="E334" s="16" t="s">
         <v>416</v>
       </c>
       <c r="F334" s="8">
@@ -10336,7 +10317,7 @@
       <c r="D335" t="s">
         <v>7</v>
       </c>
-      <c r="E335" s="22" t="s">
+      <c r="E335" s="16" t="s">
         <v>417</v>
       </c>
     </row>
@@ -10353,7 +10334,7 @@
       <c r="D336" t="s">
         <v>8</v>
       </c>
-      <c r="E336" s="22">
+      <c r="E336" s="16">
         <v>1</v>
       </c>
       <c r="F336" s="8">
@@ -10373,7 +10354,7 @@
       <c r="D337" t="s">
         <v>9</v>
       </c>
-      <c r="E337" s="22" t="s">
+      <c r="E337" s="16" t="s">
         <v>418</v>
       </c>
       <c r="F337" s="8">
@@ -10393,7 +10374,7 @@
       <c r="D338" t="s">
         <v>10</v>
       </c>
-      <c r="E338" s="22">
+      <c r="E338" s="16">
         <v>1</v>
       </c>
       <c r="F338" s="8">
@@ -10413,7 +10394,7 @@
       <c r="D339" t="s">
         <v>11</v>
       </c>
-      <c r="E339" s="22">
+      <c r="E339" s="16">
         <v>1</v>
       </c>
       <c r="F339" s="8">
@@ -10433,7 +10414,7 @@
       <c r="D340" t="s">
         <v>12</v>
       </c>
-      <c r="E340" s="22" t="s">
+      <c r="E340" s="16" t="s">
         <v>419</v>
       </c>
     </row>
@@ -10450,7 +10431,6 @@
       <c r="D341" t="s">
         <v>5</v>
       </c>
-      <c r="E341" s="22"/>
     </row>
     <row r="342" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A342">
@@ -10465,7 +10445,7 @@
       <c r="D342" t="s">
         <v>6</v>
       </c>
-      <c r="E342" s="22" t="s">
+      <c r="E342" s="16" t="s">
         <v>420</v>
       </c>
     </row>
@@ -10482,7 +10462,6 @@
       <c r="D343" t="s">
         <v>7</v>
       </c>
-      <c r="E343" s="22"/>
     </row>
     <row r="344" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A344">
@@ -10497,7 +10476,7 @@
       <c r="D344" t="s">
         <v>8</v>
       </c>
-      <c r="E344" s="22" t="s">
+      <c r="E344" s="16" t="s">
         <v>421</v>
       </c>
       <c r="F344" s="8">
@@ -10517,7 +10496,7 @@
       <c r="D345" t="s">
         <v>9</v>
       </c>
-      <c r="E345" s="22" t="s">
+      <c r="E345" s="16" t="s">
         <v>422</v>
       </c>
       <c r="F345" s="8">
@@ -10537,7 +10516,7 @@
       <c r="D346" t="s">
         <v>10</v>
       </c>
-      <c r="E346" s="26" t="s">
+      <c r="E346" s="23" t="s">
         <v>423</v>
       </c>
     </row>
@@ -10554,7 +10533,7 @@
       <c r="D347" t="s">
         <v>11</v>
       </c>
-      <c r="E347" s="22" t="s">
+      <c r="E347" s="16" t="s">
         <v>424</v>
       </c>
     </row>
@@ -10571,7 +10550,7 @@
       <c r="D348" t="s">
         <v>5</v>
       </c>
-      <c r="E348" s="22" t="s">
+      <c r="E348" s="16" t="s">
         <v>425</v>
       </c>
     </row>
@@ -10588,7 +10567,7 @@
       <c r="D349" t="s">
         <v>6</v>
       </c>
-      <c r="E349" s="22" t="s">
+      <c r="E349" s="16" t="s">
         <v>425</v>
       </c>
     </row>
@@ -10605,7 +10584,6 @@
       <c r="D350" t="s">
         <v>7</v>
       </c>
-      <c r="E350" s="22"/>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A351">
@@ -10620,7 +10598,7 @@
       <c r="D351" t="s">
         <v>8</v>
       </c>
-      <c r="E351" s="22" t="s">
+      <c r="E351" s="16" t="s">
         <v>426</v>
       </c>
       <c r="F351" s="8">
@@ -10640,7 +10618,7 @@
       <c r="D352" t="s">
         <v>9</v>
       </c>
-      <c r="E352" s="22" t="s">
+      <c r="E352" s="16" t="s">
         <v>427</v>
       </c>
     </row>
@@ -10657,7 +10635,7 @@
       <c r="D353" t="s">
         <v>10</v>
       </c>
-      <c r="E353" s="22" t="s">
+      <c r="E353" s="16" t="s">
         <v>428</v>
       </c>
     </row>
@@ -10674,7 +10652,7 @@
       <c r="D354" t="s">
         <v>11</v>
       </c>
-      <c r="E354" s="22" t="s">
+      <c r="E354" s="16" t="s">
         <v>428</v>
       </c>
     </row>
@@ -10691,7 +10669,7 @@
       <c r="D355" t="s">
         <v>5</v>
       </c>
-      <c r="E355" s="22" t="s">
+      <c r="E355" s="16" t="s">
         <v>429</v>
       </c>
       <c r="F355" s="8">
@@ -10711,7 +10689,7 @@
       <c r="D356" t="s">
         <v>6</v>
       </c>
-      <c r="E356" s="22" t="s">
+      <c r="E356" s="16" t="s">
         <v>430</v>
       </c>
       <c r="F356" s="8">
@@ -10731,7 +10709,7 @@
       <c r="D357" t="s">
         <v>7</v>
       </c>
-      <c r="E357" s="22" t="s">
+      <c r="E357" s="16" t="s">
         <v>431</v>
       </c>
     </row>
@@ -10748,7 +10726,7 @@
       <c r="D358" t="s">
         <v>8</v>
       </c>
-      <c r="E358" s="22" t="s">
+      <c r="E358" s="16" t="s">
         <v>431</v>
       </c>
     </row>
@@ -10765,7 +10743,7 @@
       <c r="D359" t="s">
         <v>9</v>
       </c>
-      <c r="E359" s="22" t="s">
+      <c r="E359" s="16" t="s">
         <v>431</v>
       </c>
     </row>
@@ -10782,7 +10760,7 @@
       <c r="D360" t="s">
         <v>10</v>
       </c>
-      <c r="E360" s="22" t="s">
+      <c r="E360" s="16" t="s">
         <v>431</v>
       </c>
     </row>
@@ -10799,7 +10777,7 @@
       <c r="D361" t="s">
         <v>11</v>
       </c>
-      <c r="E361" s="22" t="s">
+      <c r="E361" s="16" t="s">
         <v>431</v>
       </c>
     </row>
@@ -10816,7 +10794,6 @@
       <c r="D362" t="s">
         <v>5</v>
       </c>
-      <c r="E362" s="22"/>
     </row>
     <row r="363" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A363">
@@ -10831,7 +10808,7 @@
       <c r="D363" t="s">
         <v>6</v>
       </c>
-      <c r="E363" s="22" t="s">
+      <c r="E363" s="16" t="s">
         <v>432</v>
       </c>
     </row>
@@ -10848,7 +10825,6 @@
       <c r="D364" t="s">
         <v>7</v>
       </c>
-      <c r="E364" s="22"/>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A365">
@@ -10863,7 +10839,6 @@
       <c r="D365" t="s">
         <v>8</v>
       </c>
-      <c r="E365" s="22"/>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A366">
@@ -10878,7 +10853,6 @@
       <c r="D366" t="s">
         <v>9</v>
       </c>
-      <c r="E366" s="22"/>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A367">
@@ -10893,7 +10867,6 @@
       <c r="D367" t="s">
         <v>10</v>
       </c>
-      <c r="E367" s="22"/>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A368">
@@ -10908,7 +10881,6 @@
       <c r="D368" t="s">
         <v>11</v>
       </c>
-      <c r="E368" s="22"/>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A369">
@@ -10923,7 +10895,6 @@
       <c r="D369" t="s">
         <v>5</v>
       </c>
-      <c r="E369" s="22"/>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A370">
@@ -10938,7 +10909,6 @@
       <c r="D370" t="s">
         <v>6</v>
       </c>
-      <c r="E370" s="22"/>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A371">
@@ -10953,7 +10923,6 @@
       <c r="D371" t="s">
         <v>7</v>
       </c>
-      <c r="E371" s="22"/>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A372">
@@ -10968,7 +10937,6 @@
       <c r="D372" t="s">
         <v>8</v>
       </c>
-      <c r="E372" s="22"/>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A373">
@@ -10983,7 +10951,6 @@
       <c r="D373" t="s">
         <v>9</v>
       </c>
-      <c r="E373" s="22"/>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A374">
@@ -10998,7 +10965,6 @@
       <c r="D374" t="s">
         <v>10</v>
       </c>
-      <c r="E374" s="22"/>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A375">
@@ -11013,7 +10979,6 @@
       <c r="D375" t="s">
         <v>11</v>
       </c>
-      <c r="E375" s="22"/>
     </row>
     <row r="376" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A376">
@@ -11028,7 +10993,7 @@
       <c r="D376" t="s">
         <v>98</v>
       </c>
-      <c r="E376" s="23" t="s">
+      <c r="E376" s="18" t="s">
         <v>451</v>
       </c>
     </row>
@@ -11045,7 +11010,7 @@
       <c r="D377" t="s">
         <v>32</v>
       </c>
-      <c r="E377" s="23" t="s">
+      <c r="E377" s="18" t="s">
         <v>452</v>
       </c>
       <c r="F377" s="8">
@@ -11065,7 +11030,7 @@
       <c r="D378" t="s">
         <v>5</v>
       </c>
-      <c r="E378" s="22" t="s">
+      <c r="E378" s="16" t="s">
         <v>433</v>
       </c>
     </row>
@@ -11082,7 +11047,7 @@
       <c r="D379" t="s">
         <v>6</v>
       </c>
-      <c r="E379" s="22" t="s">
+      <c r="E379" s="16" t="s">
         <v>433</v>
       </c>
     </row>
@@ -11099,7 +11064,6 @@
       <c r="D380" t="s">
         <v>7</v>
       </c>
-      <c r="E380" s="22"/>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A381">
@@ -11114,7 +11078,7 @@
       <c r="D381" t="s">
         <v>8</v>
       </c>
-      <c r="E381" s="22" t="s">
+      <c r="E381" s="16" t="s">
         <v>434</v>
       </c>
     </row>
@@ -11131,7 +11095,7 @@
       <c r="D382" t="s">
         <v>9</v>
       </c>
-      <c r="E382" s="22" t="s">
+      <c r="E382" s="16" t="s">
         <v>435</v>
       </c>
     </row>
@@ -11148,7 +11112,7 @@
       <c r="D383" t="s">
         <v>10</v>
       </c>
-      <c r="E383" s="22" t="s">
+      <c r="E383" s="16" t="s">
         <v>436</v>
       </c>
     </row>
@@ -11165,7 +11129,7 @@
       <c r="D384" t="s">
         <v>11</v>
       </c>
-      <c r="E384" s="22" t="s">
+      <c r="E384" s="16" t="s">
         <v>437</v>
       </c>
     </row>
@@ -11182,7 +11146,7 @@
       <c r="D385" t="s">
         <v>98</v>
       </c>
-      <c r="E385" s="22" t="s">
+      <c r="E385" s="16" t="s">
         <v>453</v>
       </c>
     </row>
@@ -11199,7 +11163,7 @@
       <c r="D386" t="s">
         <v>5</v>
       </c>
-      <c r="E386" s="22">
+      <c r="E386" s="16">
         <v>0</v>
       </c>
       <c r="F386" s="8">
@@ -11219,7 +11183,7 @@
       <c r="D387" t="s">
         <v>6</v>
       </c>
-      <c r="E387" s="22" t="s">
+      <c r="E387" s="16" t="s">
         <v>438</v>
       </c>
       <c r="F387" s="8">
@@ -11239,7 +11203,7 @@
       <c r="D388" t="s">
         <v>7</v>
       </c>
-      <c r="E388" s="27"/>
+      <c r="E388" s="24"/>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A389">
@@ -11254,7 +11218,7 @@
       <c r="D389" t="s">
         <v>8</v>
       </c>
-      <c r="E389" s="22">
+      <c r="E389" s="16">
         <v>0</v>
       </c>
       <c r="F389" s="8">
@@ -11274,7 +11238,7 @@
       <c r="D390" t="s">
         <v>9</v>
       </c>
-      <c r="E390" s="22">
+      <c r="E390" s="16">
         <v>0</v>
       </c>
       <c r="F390" s="8">
@@ -11294,7 +11258,7 @@
       <c r="D391" t="s">
         <v>10</v>
       </c>
-      <c r="E391" s="22" t="s">
+      <c r="E391" s="16" t="s">
         <v>439</v>
       </c>
       <c r="F391" s="8">
@@ -11314,7 +11278,7 @@
       <c r="D392" t="s">
         <v>11</v>
       </c>
-      <c r="E392" s="22" t="s">
+      <c r="E392" s="16" t="s">
         <v>440</v>
       </c>
       <c r="F392" s="8">
@@ -11334,7 +11298,7 @@
       <c r="D393" t="s">
         <v>32</v>
       </c>
-      <c r="E393" s="23" t="s">
+      <c r="E393" s="18" t="s">
         <v>454</v>
       </c>
     </row>
@@ -11351,7 +11315,7 @@
       <c r="D394" t="s">
         <v>32</v>
       </c>
-      <c r="E394" s="23" t="s">
+      <c r="E394" s="18" t="s">
         <v>455</v>
       </c>
     </row>
@@ -11368,7 +11332,7 @@
       <c r="D395" t="s">
         <v>5</v>
       </c>
-      <c r="E395" s="22">
+      <c r="E395" s="16">
         <v>0</v>
       </c>
       <c r="F395" s="8">
@@ -11388,7 +11352,7 @@
       <c r="D396" t="s">
         <v>6</v>
       </c>
-      <c r="E396" s="22" t="s">
+      <c r="E396" s="16" t="s">
         <v>441</v>
       </c>
       <c r="F396" s="8">
@@ -11408,7 +11372,6 @@
       <c r="D397" t="s">
         <v>7</v>
       </c>
-      <c r="E397" s="22"/>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A398">
@@ -11423,7 +11386,7 @@
       <c r="D398" t="s">
         <v>8</v>
       </c>
-      <c r="E398" s="22" t="s">
+      <c r="E398" s="16" t="s">
         <v>442</v>
       </c>
       <c r="F398" s="8">
@@ -11443,7 +11406,7 @@
       <c r="D399" t="s">
         <v>9</v>
       </c>
-      <c r="E399" s="22" t="s">
+      <c r="E399" s="16" t="s">
         <v>443</v>
       </c>
     </row>
@@ -11460,7 +11423,7 @@
       <c r="D400" t="s">
         <v>10</v>
       </c>
-      <c r="E400" s="22" t="s">
+      <c r="E400" s="16" t="s">
         <v>444</v>
       </c>
       <c r="F400" s="8">
@@ -11480,7 +11443,7 @@
       <c r="D401" t="s">
         <v>11</v>
       </c>
-      <c r="E401" s="22" t="s">
+      <c r="E401" s="16" t="s">
         <v>444</v>
       </c>
       <c r="F401" s="8">
@@ -11500,7 +11463,7 @@
       <c r="D402" t="s">
         <v>32</v>
       </c>
-      <c r="E402" s="23" t="s">
+      <c r="E402" s="18" t="s">
         <v>456</v>
       </c>
       <c r="F402" s="8">
@@ -11520,7 +11483,7 @@
       <c r="D403" t="s">
         <v>5</v>
       </c>
-      <c r="E403" s="22" t="s">
+      <c r="E403" s="16" t="s">
         <v>445</v>
       </c>
     </row>
@@ -11537,7 +11500,7 @@
       <c r="D404" t="s">
         <v>6</v>
       </c>
-      <c r="E404" s="22" t="s">
+      <c r="E404" s="16" t="s">
         <v>446</v>
       </c>
     </row>
@@ -11554,7 +11517,6 @@
       <c r="D405" t="s">
         <v>7</v>
       </c>
-      <c r="E405" s="22"/>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A406">
@@ -11569,7 +11531,7 @@
       <c r="D406" t="s">
         <v>8</v>
       </c>
-      <c r="E406" s="22" t="s">
+      <c r="E406" s="16" t="s">
         <v>447</v>
       </c>
     </row>
@@ -11586,7 +11548,7 @@
       <c r="D407" t="s">
         <v>9</v>
       </c>
-      <c r="E407" s="22" t="s">
+      <c r="E407" s="16" t="s">
         <v>448</v>
       </c>
       <c r="F407" s="8">
@@ -11606,7 +11568,7 @@
       <c r="D408" t="s">
         <v>10</v>
       </c>
-      <c r="E408" s="22" t="s">
+      <c r="E408" s="16" t="s">
         <v>449</v>
       </c>
       <c r="F408" s="8">
@@ -11626,7 +11588,7 @@
       <c r="D409" t="s">
         <v>11</v>
       </c>
-      <c r="E409" s="22" t="s">
+      <c r="E409" s="16" t="s">
         <v>450</v>
       </c>
     </row>
@@ -11643,7 +11605,7 @@
       <c r="D410" t="s">
         <v>32</v>
       </c>
-      <c r="E410" s="22" t="s">
+      <c r="E410" s="16" t="s">
         <v>457</v>
       </c>
       <c r="F410" s="8">
@@ -11663,7 +11625,7 @@
       <c r="D411" t="s">
         <v>32</v>
       </c>
-      <c r="E411" s="23" t="s">
+      <c r="E411" s="18" t="s">
         <v>458</v>
       </c>
       <c r="F411" s="8">
@@ -11683,7 +11645,7 @@
       <c r="D412" t="s">
         <v>32</v>
       </c>
-      <c r="E412" s="22" t="s">
+      <c r="E412" s="16" t="s">
         <v>459</v>
       </c>
       <c r="F412" s="8">
@@ -11703,7 +11665,7 @@
       <c r="D413" t="s">
         <v>32</v>
       </c>
-      <c r="E413" s="23" t="s">
+      <c r="E413" s="18" t="s">
         <v>460</v>
       </c>
     </row>
@@ -11720,7 +11682,7 @@
       <c r="D414" t="s">
         <v>32</v>
       </c>
-      <c r="E414" s="23" t="s">
+      <c r="E414" s="18" t="s">
         <v>461</v>
       </c>
       <c r="F414" s="8">
@@ -11740,7 +11702,7 @@
       <c r="D415" t="s">
         <v>5</v>
       </c>
-      <c r="E415" s="23" t="s">
+      <c r="E415" s="18" t="s">
         <v>462</v>
       </c>
       <c r="F415" s="8">
@@ -11760,7 +11722,7 @@
       <c r="D416" t="s">
         <v>6</v>
       </c>
-      <c r="E416" s="23">
+      <c r="E416" s="18">
         <v>1</v>
       </c>
       <c r="F416" s="8">
@@ -11780,7 +11742,7 @@
       <c r="D417" t="s">
         <v>7</v>
       </c>
-      <c r="E417" s="23">
+      <c r="E417" s="18">
         <v>1</v>
       </c>
       <c r="F417" s="8">
@@ -11800,7 +11762,7 @@
       <c r="D418" t="s">
         <v>32</v>
       </c>
-      <c r="E418" s="25" t="s">
+      <c r="E418" s="22" t="s">
         <v>463</v>
       </c>
       <c r="F418" s="8">
@@ -11820,7 +11782,7 @@
       <c r="D419" t="s">
         <v>32</v>
       </c>
-      <c r="E419" s="22" t="s">
+      <c r="E419" s="16" t="s">
         <v>464</v>
       </c>
     </row>
@@ -11837,7 +11799,7 @@
       <c r="D420" t="s">
         <v>32</v>
       </c>
-      <c r="E420" s="23" t="s">
+      <c r="E420" s="18" t="s">
         <v>465</v>
       </c>
       <c r="F420" s="8">
@@ -11857,7 +11819,7 @@
       <c r="D421" t="s">
         <v>32</v>
       </c>
-      <c r="E421" s="22" t="s">
+      <c r="E421" s="16" t="s">
         <v>464</v>
       </c>
     </row>
@@ -11874,7 +11836,7 @@
       <c r="D422" t="s">
         <v>32</v>
       </c>
-      <c r="E422" s="26" t="s">
+      <c r="E422" s="23" t="s">
         <v>466</v>
       </c>
     </row>
@@ -11891,7 +11853,7 @@
       <c r="D423" t="s">
         <v>32</v>
       </c>
-      <c r="E423" s="22" t="s">
+      <c r="E423" s="16" t="s">
         <v>467</v>
       </c>
       <c r="F423" s="8">
@@ -11911,7 +11873,7 @@
       <c r="D424" t="s">
         <v>32</v>
       </c>
-      <c r="E424" s="23" t="s">
+      <c r="E424" s="18" t="s">
         <v>468</v>
       </c>
       <c r="F424" s="8">
@@ -11931,7 +11893,7 @@
       <c r="D425" t="s">
         <v>32</v>
       </c>
-      <c r="E425" s="22" t="s">
+      <c r="E425" s="16" t="s">
         <v>469</v>
       </c>
       <c r="F425" s="8">
@@ -11951,7 +11913,7 @@
       <c r="D426" t="s">
         <v>32</v>
       </c>
-      <c r="E426" s="23" t="s">
+      <c r="E426" s="18" t="s">
         <v>470</v>
       </c>
       <c r="F426" s="8">
@@ -11971,7 +11933,7 @@
       <c r="D427" t="s">
         <v>32</v>
       </c>
-      <c r="E427" s="23" t="s">
+      <c r="E427" s="18" t="s">
         <v>471</v>
       </c>
     </row>
@@ -11988,7 +11950,7 @@
       <c r="D428" t="s">
         <v>32</v>
       </c>
-      <c r="E428" s="22" t="s">
+      <c r="E428" s="16" t="s">
         <v>472</v>
       </c>
       <c r="F428" s="8">
@@ -12008,7 +11970,7 @@
       <c r="D429" t="s">
         <v>32</v>
       </c>
-      <c r="E429" s="23" t="s">
+      <c r="E429" s="18" t="s">
         <v>473</v>
       </c>
       <c r="F429" s="8">
@@ -12028,7 +11990,7 @@
       <c r="D430" t="s">
         <v>32</v>
       </c>
-      <c r="E430" s="22" t="s">
+      <c r="E430" s="16" t="s">
         <v>474</v>
       </c>
       <c r="F430" s="8">
@@ -12048,7 +12010,7 @@
       <c r="D431" t="s">
         <v>32</v>
       </c>
-      <c r="E431" s="25" t="s">
+      <c r="E431" s="22" t="s">
         <v>475</v>
       </c>
     </row>
@@ -12065,7 +12027,7 @@
       <c r="D432" t="s">
         <v>32</v>
       </c>
-      <c r="E432" s="23" t="s">
+      <c r="E432" s="18" t="s">
         <v>476</v>
       </c>
     </row>
@@ -12082,7 +12044,6 @@
       <c r="D433" t="s">
         <v>32</v>
       </c>
-      <c r="E433" s="22"/>
     </row>
     <row r="434" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A434">
@@ -12097,7 +12058,7 @@
       <c r="D434" t="s">
         <v>32</v>
       </c>
-      <c r="E434" s="26" t="s">
+      <c r="E434" s="23" t="s">
         <v>477</v>
       </c>
     </row>
@@ -12114,7 +12075,7 @@
       <c r="D435" t="s">
         <v>32</v>
       </c>
-      <c r="E435" s="22" t="s">
+      <c r="E435" s="16" t="s">
         <v>478</v>
       </c>
     </row>
@@ -12131,7 +12092,7 @@
       <c r="D436" t="s">
         <v>32</v>
       </c>
-      <c r="E436" s="23"/>
+      <c r="E436" s="18"/>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A437">
@@ -12146,7 +12107,7 @@
       <c r="D437" t="s">
         <v>32</v>
       </c>
-      <c r="E437" s="23"/>
+      <c r="E437" s="18"/>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A438">
@@ -12161,7 +12122,7 @@
       <c r="D438" t="s">
         <v>32</v>
       </c>
-      <c r="E438" s="23" t="s">
+      <c r="E438" s="18" t="s">
         <v>479</v>
       </c>
     </row>
@@ -12178,7 +12139,7 @@
       <c r="D439" t="s">
         <v>32</v>
       </c>
-      <c r="E439" s="23" t="s">
+      <c r="E439" s="18" t="s">
         <v>480</v>
       </c>
     </row>
@@ -12195,7 +12156,7 @@
       <c r="D440" t="s">
         <v>32</v>
       </c>
-      <c r="E440" s="22" t="s">
+      <c r="E440" s="16" t="s">
         <v>481</v>
       </c>
     </row>
@@ -12212,7 +12173,7 @@
       <c r="D441" t="s">
         <v>32</v>
       </c>
-      <c r="E441" s="22" t="s">
+      <c r="E441" s="16" t="s">
         <v>482</v>
       </c>
     </row>
@@ -12229,7 +12190,7 @@
       <c r="D442" t="s">
         <v>32</v>
       </c>
-      <c r="E442" s="22" t="s">
+      <c r="E442" s="16" t="s">
         <v>484</v>
       </c>
     </row>
@@ -12858,7 +12819,6 @@
       <c r="D479" t="s">
         <v>5</v>
       </c>
-      <c r="E479" s="22"/>
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A480">
@@ -12873,7 +12833,6 @@
       <c r="D480" t="s">
         <v>6</v>
       </c>
-      <c r="E480" s="22"/>
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A481">
@@ -12888,7 +12847,6 @@
       <c r="D481" t="s">
         <v>7</v>
       </c>
-      <c r="E481" s="22"/>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A482">
@@ -12903,7 +12861,6 @@
       <c r="D482" t="s">
         <v>8</v>
       </c>
-      <c r="E482" s="22"/>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A483">
@@ -12918,7 +12875,6 @@
       <c r="D483" t="s">
         <v>9</v>
       </c>
-      <c r="E483" s="22"/>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A484">
@@ -12933,7 +12889,6 @@
       <c r="D484" t="s">
         <v>10</v>
       </c>
-      <c r="E484" s="22"/>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A485">
@@ -12948,7 +12903,6 @@
       <c r="D485" t="s">
         <v>11</v>
       </c>
-      <c r="E485" s="22"/>
     </row>
     <row r="486" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A486">
@@ -12963,7 +12917,7 @@
       <c r="D486" t="s">
         <v>98</v>
       </c>
-      <c r="E486" s="23" t="s">
+      <c r="E486" s="18" t="s">
         <v>510</v>
       </c>
     </row>
@@ -12980,7 +12934,7 @@
       <c r="D487" t="s">
         <v>32</v>
       </c>
-      <c r="E487" s="23" t="s">
+      <c r="E487" s="18" t="s">
         <v>511</v>
       </c>
       <c r="F487" s="8">
@@ -13271,7 +13225,7 @@
       <c r="D502" t="s">
         <v>32</v>
       </c>
-      <c r="E502" s="23" t="s">
+      <c r="E502" s="18" t="s">
         <v>518</v>
       </c>
     </row>
@@ -13288,7 +13242,7 @@
       <c r="D503" t="s">
         <v>32</v>
       </c>
-      <c r="E503" s="23" t="s">
+      <c r="E503" s="18" t="s">
         <v>519</v>
       </c>
     </row>
@@ -13439,7 +13393,7 @@
       <c r="D511" t="s">
         <v>32</v>
       </c>
-      <c r="E511" s="24" t="s">
+      <c r="E511" s="21" t="s">
         <v>526</v>
       </c>
       <c r="F511" s="8">
@@ -13578,7 +13532,7 @@
       <c r="D519" t="s">
         <v>32</v>
       </c>
-      <c r="E519" s="22" t="s">
+      <c r="E519" s="16" t="s">
         <v>531</v>
       </c>
       <c r="F519" s="8">
@@ -13598,7 +13552,7 @@
       <c r="D520" t="s">
         <v>32</v>
       </c>
-      <c r="E520" s="23" t="s">
+      <c r="E520" s="18" t="s">
         <v>532</v>
       </c>
     </row>
@@ -13615,7 +13569,7 @@
       <c r="D521" t="s">
         <v>32</v>
       </c>
-      <c r="E521" s="22" t="s">
+      <c r="E521" s="16" t="s">
         <v>533</v>
       </c>
       <c r="F521" s="8">
@@ -13635,7 +13589,7 @@
       <c r="D522" t="s">
         <v>32</v>
       </c>
-      <c r="E522" s="24" t="s">
+      <c r="E522" s="21" t="s">
         <v>534</v>
       </c>
       <c r="F522" s="8">
@@ -13655,7 +13609,7 @@
       <c r="D523" t="s">
         <v>32</v>
       </c>
-      <c r="E523" s="24" t="s">
+      <c r="E523" s="21" t="s">
         <v>535</v>
       </c>
     </row>
@@ -13672,7 +13626,7 @@
       <c r="D524" t="s">
         <v>5</v>
       </c>
-      <c r="E524" s="24" t="s">
+      <c r="E524" s="21" t="s">
         <v>536</v>
       </c>
     </row>
@@ -13689,7 +13643,7 @@
       <c r="D525" t="s">
         <v>6</v>
       </c>
-      <c r="E525" s="23" t="s">
+      <c r="E525" s="18" t="s">
         <v>537</v>
       </c>
     </row>
@@ -13706,7 +13660,7 @@
       <c r="D526" t="s">
         <v>7</v>
       </c>
-      <c r="E526" s="23" t="s">
+      <c r="E526" s="18" t="s">
         <v>537</v>
       </c>
     </row>
@@ -13723,7 +13677,7 @@
       <c r="D527" t="s">
         <v>32</v>
       </c>
-      <c r="E527" s="25" t="s">
+      <c r="E527" s="22" t="s">
         <v>538</v>
       </c>
     </row>
@@ -13740,7 +13694,7 @@
       <c r="D528" t="s">
         <v>32</v>
       </c>
-      <c r="E528" s="22" t="s">
+      <c r="E528" s="16" t="s">
         <v>540</v>
       </c>
     </row>
@@ -13757,7 +13711,7 @@
       <c r="D529" t="s">
         <v>32</v>
       </c>
-      <c r="E529" s="23" t="s">
+      <c r="E529" s="18" t="s">
         <v>539</v>
       </c>
       <c r="F529" s="8">
@@ -13777,7 +13731,7 @@
       <c r="D530" t="s">
         <v>32</v>
       </c>
-      <c r="E530" s="22" t="s">
+      <c r="E530" s="16" t="s">
         <v>540</v>
       </c>
     </row>
@@ -13794,7 +13748,7 @@
       <c r="D531" t="s">
         <v>32</v>
       </c>
-      <c r="E531" s="26" t="s">
+      <c r="E531" s="23" t="s">
         <v>541</v>
       </c>
     </row>
@@ -13811,7 +13765,7 @@
       <c r="D532" t="s">
         <v>32</v>
       </c>
-      <c r="E532" s="22" t="s">
+      <c r="E532" s="16" t="s">
         <v>542</v>
       </c>
       <c r="F532" s="8">
@@ -13831,7 +13785,7 @@
       <c r="D533" t="s">
         <v>32</v>
       </c>
-      <c r="E533" s="23" t="s">
+      <c r="E533" s="18" t="s">
         <v>543</v>
       </c>
     </row>
@@ -13848,7 +13802,7 @@
       <c r="D534" t="s">
         <v>32</v>
       </c>
-      <c r="E534" s="22" t="s">
+      <c r="E534" s="16" t="s">
         <v>544</v>
       </c>
     </row>
@@ -13865,7 +13819,7 @@
       <c r="D535" t="s">
         <v>32</v>
       </c>
-      <c r="E535" s="23" t="s">
+      <c r="E535" s="18" t="s">
         <v>545</v>
       </c>
       <c r="F535" s="8">
@@ -13885,7 +13839,7 @@
       <c r="D536" t="s">
         <v>32</v>
       </c>
-      <c r="E536" s="23" t="s">
+      <c r="E536" s="18" t="s">
         <v>546</v>
       </c>
     </row>
@@ -13902,7 +13856,7 @@
       <c r="D537" t="s">
         <v>32</v>
       </c>
-      <c r="E537" s="22" t="s">
+      <c r="E537" s="16" t="s">
         <v>547</v>
       </c>
       <c r="F537" s="8">
@@ -13922,7 +13876,7 @@
       <c r="D538" t="s">
         <v>32</v>
       </c>
-      <c r="E538" s="23" t="s">
+      <c r="E538" s="18" t="s">
         <v>545</v>
       </c>
       <c r="F538" s="8">
@@ -13942,7 +13896,7 @@
       <c r="D539" t="s">
         <v>32</v>
       </c>
-      <c r="E539" s="22" t="s">
+      <c r="E539" s="16" t="s">
         <v>548</v>
       </c>
       <c r="F539" s="8">
@@ -13962,7 +13916,7 @@
       <c r="D540" t="s">
         <v>32</v>
       </c>
-      <c r="E540" s="25" t="s">
+      <c r="E540" s="22" t="s">
         <v>549</v>
       </c>
       <c r="F540" s="8">
@@ -13982,7 +13936,7 @@
       <c r="D541" t="s">
         <v>32</v>
       </c>
-      <c r="E541" s="23" t="s">
+      <c r="E541" s="18" t="s">
         <v>550</v>
       </c>
     </row>
@@ -13999,7 +13953,6 @@
       <c r="D542" t="s">
         <v>32</v>
       </c>
-      <c r="E542" s="22"/>
     </row>
     <row r="543" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A543">
@@ -14014,7 +13967,7 @@
       <c r="D543" t="s">
         <v>32</v>
       </c>
-      <c r="E543" s="25" t="s">
+      <c r="E543" s="22" t="s">
         <v>551</v>
       </c>
     </row>
@@ -14031,7 +13984,7 @@
       <c r="D544" t="s">
         <v>32</v>
       </c>
-      <c r="E544" s="22" t="s">
+      <c r="E544" s="16" t="s">
         <v>552</v>
       </c>
     </row>
@@ -14048,7 +14001,7 @@
       <c r="D545" t="s">
         <v>32</v>
       </c>
-      <c r="E545" s="23" t="s">
+      <c r="E545" s="18" t="s">
         <v>553</v>
       </c>
     </row>
@@ -14065,7 +14018,7 @@
       <c r="D546" t="s">
         <v>32</v>
       </c>
-      <c r="E546" s="23"/>
+      <c r="E546" s="18"/>
     </row>
     <row r="547" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A547">
@@ -14080,7 +14033,7 @@
       <c r="D547" t="s">
         <v>32</v>
       </c>
-      <c r="E547" s="23" t="s">
+      <c r="E547" s="18" t="s">
         <v>554</v>
       </c>
     </row>
@@ -14097,7 +14050,7 @@
       <c r="D548" t="s">
         <v>32</v>
       </c>
-      <c r="E548" s="23" t="s">
+      <c r="E548" s="18" t="s">
         <v>555</v>
       </c>
     </row>
@@ -14114,7 +14067,7 @@
       <c r="D549" t="s">
         <v>32</v>
       </c>
-      <c r="E549" s="22">
+      <c r="E549" s="16">
         <v>5</v>
       </c>
       <c r="F549" s="8">
@@ -14134,4137 +14087,4089 @@
       <c r="D550" t="s">
         <v>32</v>
       </c>
-      <c r="E550" s="22" t="s">
+      <c r="E550" s="16" t="s">
         <v>556</v>
       </c>
     </row>
     <row r="551" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A551" s="28">
-        <v>6</v>
-      </c>
-      <c r="B551" s="28" t="s">
+      <c r="A551">
+        <v>6</v>
+      </c>
+      <c r="B551" t="s">
         <v>31</v>
       </c>
-      <c r="C551" s="28">
+      <c r="C551">
         <v>0</v>
       </c>
-      <c r="D551" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E551" s="22" t="s">
+      <c r="D551" t="s">
+        <v>32</v>
+      </c>
+      <c r="E551" s="16" t="s">
         <v>557</v>
       </c>
-      <c r="F551" s="21"/>
     </row>
     <row r="552" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A552" s="28">
-        <v>6</v>
-      </c>
-      <c r="B552" s="28" t="s">
+      <c r="A552">
+        <v>6</v>
+      </c>
+      <c r="B552" t="s">
         <v>33</v>
       </c>
-      <c r="C552" s="28">
-        <v>2</v>
-      </c>
-      <c r="D552" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="E552" s="29">
-        <v>5</v>
-      </c>
-      <c r="F552" s="21">
+      <c r="C552">
+        <v>2</v>
+      </c>
+      <c r="D552" t="s">
+        <v>5</v>
+      </c>
+      <c r="E552" s="2">
+        <v>5</v>
+      </c>
+      <c r="F552" s="8">
         <v>5</v>
       </c>
     </row>
     <row r="553" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A553" s="28">
-        <v>6</v>
-      </c>
-      <c r="B553" s="28" t="s">
+      <c r="A553">
+        <v>6</v>
+      </c>
+      <c r="B553" t="s">
         <v>33</v>
       </c>
-      <c r="C553" s="28">
-        <v>2</v>
-      </c>
-      <c r="D553" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="E553" s="30" t="s">
+      <c r="C553">
+        <v>2</v>
+      </c>
+      <c r="D553" t="s">
+        <v>6</v>
+      </c>
+      <c r="E553" s="6" t="s">
         <v>558</v>
       </c>
-      <c r="F553" s="21">
+      <c r="F553" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="554" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A554" s="28">
-        <v>6</v>
-      </c>
-      <c r="B554" s="28" t="s">
+      <c r="A554">
+        <v>6</v>
+      </c>
+      <c r="B554" t="s">
         <v>33</v>
       </c>
-      <c r="C554" s="28">
-        <v>2</v>
-      </c>
-      <c r="D554" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="E554" s="30" t="s">
+      <c r="C554">
+        <v>2</v>
+      </c>
+      <c r="D554" t="s">
+        <v>7</v>
+      </c>
+      <c r="E554" s="6" t="s">
         <v>559</v>
       </c>
-      <c r="F554" s="21">
+      <c r="F554" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="555" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A555" s="28">
-        <v>6</v>
-      </c>
-      <c r="B555" s="28" t="s">
+      <c r="A555">
+        <v>6</v>
+      </c>
+      <c r="B555" t="s">
         <v>33</v>
       </c>
-      <c r="C555" s="28">
-        <v>2</v>
-      </c>
-      <c r="D555" s="28" t="s">
+      <c r="C555">
+        <v>2</v>
+      </c>
+      <c r="D555" t="s">
         <v>8</v>
       </c>
-      <c r="E555" s="30">
-        <v>5</v>
-      </c>
-      <c r="F555" s="21">
+      <c r="E555" s="6">
+        <v>5</v>
+      </c>
+      <c r="F555" s="8">
         <v>5</v>
       </c>
     </row>
     <row r="556" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A556" s="28">
-        <v>6</v>
-      </c>
-      <c r="B556" s="28" t="s">
+      <c r="A556">
+        <v>6</v>
+      </c>
+      <c r="B556" t="s">
         <v>33</v>
       </c>
-      <c r="C556" s="28">
-        <v>2</v>
-      </c>
-      <c r="D556" s="28" t="s">
+      <c r="C556">
+        <v>2</v>
+      </c>
+      <c r="D556" t="s">
         <v>9</v>
       </c>
-      <c r="E556" s="30">
-        <v>5</v>
-      </c>
-      <c r="F556" s="21">
+      <c r="E556" s="6">
+        <v>5</v>
+      </c>
+      <c r="F556" s="8">
         <v>5</v>
       </c>
     </row>
     <row r="557" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A557" s="28">
-        <v>6</v>
-      </c>
-      <c r="B557" s="28" t="s">
+      <c r="A557">
+        <v>6</v>
+      </c>
+      <c r="B557" t="s">
         <v>33</v>
       </c>
-      <c r="C557" s="28">
-        <v>2</v>
-      </c>
-      <c r="D557" s="28" t="s">
+      <c r="C557">
+        <v>2</v>
+      </c>
+      <c r="D557" t="s">
         <v>10</v>
       </c>
-      <c r="E557" s="30" t="s">
+      <c r="E557" s="6" t="s">
         <v>560</v>
       </c>
-      <c r="F557" s="21" t="s">
+      <c r="F557" s="8" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="558" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A558" s="28">
-        <v>6</v>
-      </c>
-      <c r="B558" s="28" t="s">
+      <c r="A558">
+        <v>6</v>
+      </c>
+      <c r="B558" t="s">
         <v>33</v>
       </c>
-      <c r="C558" s="28">
-        <v>2</v>
-      </c>
-      <c r="D558" s="28" t="s">
+      <c r="C558">
+        <v>2</v>
+      </c>
+      <c r="D558" t="s">
         <v>11</v>
       </c>
-      <c r="E558" s="30" t="s">
+      <c r="E558" s="6" t="s">
         <v>561</v>
       </c>
-      <c r="F558" s="21">
+      <c r="F558" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="559" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A559" s="28">
-        <v>6</v>
-      </c>
-      <c r="B559" s="28" t="s">
+      <c r="A559">
+        <v>6</v>
+      </c>
+      <c r="B559" t="s">
         <v>33</v>
       </c>
-      <c r="C559" s="28">
-        <v>2</v>
-      </c>
-      <c r="D559" s="28" t="s">
+      <c r="C559">
+        <v>2</v>
+      </c>
+      <c r="D559" t="s">
         <v>12</v>
       </c>
-      <c r="E559" s="30" t="s">
+      <c r="E559" s="6" t="s">
         <v>562</v>
       </c>
-      <c r="F559" s="21">
+      <c r="F559" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="560" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A560" s="28">
-        <v>6</v>
-      </c>
-      <c r="B560" s="28" t="s">
+      <c r="A560">
+        <v>6</v>
+      </c>
+      <c r="B560" t="s">
         <v>34</v>
       </c>
-      <c r="C560" s="28">
-        <v>3</v>
-      </c>
-      <c r="D560" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="E560" s="30" t="s">
+      <c r="C560">
+        <v>3</v>
+      </c>
+      <c r="D560" t="s">
+        <v>5</v>
+      </c>
+      <c r="E560" s="6" t="s">
         <v>563</v>
       </c>
-      <c r="F560" s="21"/>
     </row>
     <row r="561" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A561" s="28">
-        <v>6</v>
-      </c>
-      <c r="B561" s="28" t="s">
+      <c r="A561">
+        <v>6</v>
+      </c>
+      <c r="B561" t="s">
         <v>34</v>
       </c>
-      <c r="C561" s="28">
-        <v>3</v>
-      </c>
-      <c r="D561" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="E561" s="30" t="s">
+      <c r="C561">
+        <v>3</v>
+      </c>
+      <c r="D561" t="s">
+        <v>6</v>
+      </c>
+      <c r="E561" s="6" t="s">
         <v>564</v>
       </c>
-      <c r="F561" s="21" t="s">
+      <c r="F561" s="8" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="562" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A562" s="28">
-        <v>6</v>
-      </c>
-      <c r="B562" s="28" t="s">
+      <c r="A562">
+        <v>6</v>
+      </c>
+      <c r="B562" t="s">
         <v>34</v>
       </c>
-      <c r="C562" s="28">
-        <v>3</v>
-      </c>
-      <c r="D562" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="E562" s="30" t="s">
+      <c r="C562">
+        <v>3</v>
+      </c>
+      <c r="D562" t="s">
+        <v>7</v>
+      </c>
+      <c r="E562" s="6" t="s">
         <v>565</v>
       </c>
-      <c r="F562" s="21">
+      <c r="F562" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="563" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A563" s="28">
-        <v>6</v>
-      </c>
-      <c r="B563" s="28" t="s">
+      <c r="A563">
+        <v>6</v>
+      </c>
+      <c r="B563" t="s">
         <v>34</v>
       </c>
-      <c r="C563" s="28">
-        <v>3</v>
-      </c>
-      <c r="D563" s="28" t="s">
+      <c r="C563">
+        <v>3</v>
+      </c>
+      <c r="D563" t="s">
         <v>8</v>
       </c>
-      <c r="E563" s="30">
-        <v>1</v>
-      </c>
-      <c r="F563" s="21">
+      <c r="E563" s="6">
+        <v>1</v>
+      </c>
+      <c r="F563" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="564" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A564" s="28">
-        <v>6</v>
-      </c>
-      <c r="B564" s="28" t="s">
+      <c r="A564">
+        <v>6</v>
+      </c>
+      <c r="B564" t="s">
         <v>34</v>
       </c>
-      <c r="C564" s="28">
-        <v>3</v>
-      </c>
-      <c r="D564" s="28" t="s">
+      <c r="C564">
+        <v>3</v>
+      </c>
+      <c r="D564" t="s">
         <v>9</v>
       </c>
-      <c r="E564" s="30" t="s">
+      <c r="E564" s="6" t="s">
         <v>566</v>
       </c>
-      <c r="F564" s="21">
+      <c r="F564" s="8">
         <v>3</v>
       </c>
     </row>
     <row r="565" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A565" s="28">
-        <v>6</v>
-      </c>
-      <c r="B565" s="28" t="s">
+      <c r="A565">
+        <v>6</v>
+      </c>
+      <c r="B565" t="s">
         <v>34</v>
       </c>
-      <c r="C565" s="28">
-        <v>3</v>
-      </c>
-      <c r="D565" s="28" t="s">
+      <c r="C565">
+        <v>3</v>
+      </c>
+      <c r="D565" t="s">
         <v>10</v>
       </c>
-      <c r="E565" s="30" t="s">
+      <c r="E565" s="6" t="s">
         <v>567</v>
       </c>
-      <c r="F565" s="21">
+      <c r="F565" s="8">
         <v>3</v>
       </c>
     </row>
     <row r="566" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A566" s="28">
-        <v>6</v>
-      </c>
-      <c r="B566" s="28" t="s">
+      <c r="A566">
+        <v>6</v>
+      </c>
+      <c r="B566" t="s">
         <v>34</v>
       </c>
-      <c r="C566" s="28">
-        <v>3</v>
-      </c>
-      <c r="D566" s="28" t="s">
+      <c r="C566">
+        <v>3</v>
+      </c>
+      <c r="D566" t="s">
         <v>11</v>
       </c>
-      <c r="E566" s="30" t="s">
+      <c r="E566" s="6" t="s">
         <v>568</v>
       </c>
-      <c r="F566" s="21">
+      <c r="F566" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="567" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A567" s="28">
-        <v>6</v>
-      </c>
-      <c r="B567" s="28" t="s">
+      <c r="A567">
+        <v>6</v>
+      </c>
+      <c r="B567" t="s">
         <v>35</v>
       </c>
-      <c r="C567" s="28">
+      <c r="C567">
         <v>4</v>
       </c>
-      <c r="D567" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="E567" s="30">
-        <v>1</v>
-      </c>
-      <c r="F567" s="21">
+      <c r="D567" t="s">
+        <v>5</v>
+      </c>
+      <c r="E567" s="6">
+        <v>1</v>
+      </c>
+      <c r="F567" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="568" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A568" s="28">
-        <v>6</v>
-      </c>
-      <c r="B568" s="28" t="s">
+      <c r="A568">
+        <v>6</v>
+      </c>
+      <c r="B568" t="s">
         <v>35</v>
       </c>
-      <c r="C568" s="28">
+      <c r="C568">
         <v>4</v>
       </c>
-      <c r="D568" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="E568" s="30"/>
-      <c r="F568" s="21"/>
+      <c r="D568" t="s">
+        <v>6</v>
+      </c>
+      <c r="E568" s="6"/>
     </row>
     <row r="569" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A569" s="28">
-        <v>6</v>
-      </c>
-      <c r="B569" s="28" t="s">
+      <c r="A569">
+        <v>6</v>
+      </c>
+      <c r="B569" t="s">
         <v>35</v>
       </c>
-      <c r="C569" s="28">
+      <c r="C569">
         <v>4</v>
       </c>
-      <c r="D569" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="E569" s="30">
-        <v>1</v>
-      </c>
-      <c r="F569" s="21">
+      <c r="D569" t="s">
+        <v>7</v>
+      </c>
+      <c r="E569" s="6">
+        <v>1</v>
+      </c>
+      <c r="F569" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="570" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A570" s="28">
-        <v>6</v>
-      </c>
-      <c r="B570" s="28" t="s">
+      <c r="A570">
+        <v>6</v>
+      </c>
+      <c r="B570" t="s">
         <v>35</v>
       </c>
-      <c r="C570" s="28">
+      <c r="C570">
         <v>4</v>
       </c>
-      <c r="D570" s="28" t="s">
+      <c r="D570" t="s">
         <v>8</v>
       </c>
-      <c r="E570" s="30">
-        <v>1</v>
-      </c>
-      <c r="F570" s="21">
+      <c r="E570" s="6">
+        <v>1</v>
+      </c>
+      <c r="F570" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="571" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A571" s="28">
-        <v>6</v>
-      </c>
-      <c r="B571" s="28" t="s">
+      <c r="A571">
+        <v>6</v>
+      </c>
+      <c r="B571" t="s">
         <v>35</v>
       </c>
-      <c r="C571" s="28">
+      <c r="C571">
         <v>4</v>
       </c>
-      <c r="D571" s="28" t="s">
+      <c r="D571" t="s">
         <v>9</v>
       </c>
-      <c r="E571" s="30">
-        <v>1</v>
-      </c>
-      <c r="F571" s="21">
+      <c r="E571" s="6">
+        <v>1</v>
+      </c>
+      <c r="F571" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="572" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A572" s="28">
-        <v>6</v>
-      </c>
-      <c r="B572" s="28" t="s">
+      <c r="A572">
+        <v>6</v>
+      </c>
+      <c r="B572" t="s">
         <v>35</v>
       </c>
-      <c r="C572" s="28">
+      <c r="C572">
         <v>4</v>
       </c>
-      <c r="D572" s="28" t="s">
+      <c r="D572" t="s">
         <v>10</v>
       </c>
-      <c r="E572" s="30">
-        <v>1</v>
-      </c>
-      <c r="F572" s="21">
+      <c r="E572" s="6">
+        <v>1</v>
+      </c>
+      <c r="F572" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="573" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A573" s="28">
-        <v>6</v>
-      </c>
-      <c r="B573" s="28" t="s">
+      <c r="A573">
+        <v>6</v>
+      </c>
+      <c r="B573" t="s">
         <v>35</v>
       </c>
-      <c r="C573" s="28">
+      <c r="C573">
         <v>4</v>
       </c>
-      <c r="D573" s="28" t="s">
+      <c r="D573" t="s">
         <v>11</v>
       </c>
-      <c r="E573" s="30">
-        <v>1</v>
-      </c>
-      <c r="F573" s="21">
+      <c r="E573" s="6">
+        <v>1</v>
+      </c>
+      <c r="F573" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="574" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A574" s="28">
-        <v>6</v>
-      </c>
-      <c r="B574" s="28" t="s">
+      <c r="A574">
+        <v>6</v>
+      </c>
+      <c r="B574" t="s">
         <v>36</v>
       </c>
-      <c r="C574" s="28">
-        <v>5</v>
-      </c>
-      <c r="D574" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="E574" s="30" t="s">
+      <c r="C574">
+        <v>5</v>
+      </c>
+      <c r="D574" t="s">
+        <v>5</v>
+      </c>
+      <c r="E574" s="6" t="s">
         <v>569</v>
       </c>
-      <c r="F574" s="21">
+      <c r="F574" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="575" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A575" s="28">
-        <v>6</v>
-      </c>
-      <c r="B575" s="28" t="s">
+      <c r="A575">
+        <v>6</v>
+      </c>
+      <c r="B575" t="s">
         <v>36</v>
       </c>
-      <c r="C575" s="28">
-        <v>5</v>
-      </c>
-      <c r="D575" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="E575" s="30" t="s">
+      <c r="C575">
+        <v>5</v>
+      </c>
+      <c r="D575" t="s">
+        <v>6</v>
+      </c>
+      <c r="E575" s="6" t="s">
         <v>570</v>
       </c>
-      <c r="F575" s="21">
+      <c r="F575" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="576" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A576" s="28">
-        <v>6</v>
-      </c>
-      <c r="B576" s="28" t="s">
+      <c r="A576">
+        <v>6</v>
+      </c>
+      <c r="B576" t="s">
         <v>36</v>
       </c>
-      <c r="C576" s="28">
-        <v>5</v>
-      </c>
-      <c r="D576" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="E576" s="30">
-        <v>3</v>
-      </c>
-      <c r="F576" s="21">
+      <c r="C576">
+        <v>5</v>
+      </c>
+      <c r="D576" t="s">
+        <v>7</v>
+      </c>
+      <c r="E576" s="6">
+        <v>3</v>
+      </c>
+      <c r="F576" s="8">
         <v>3</v>
       </c>
     </row>
     <row r="577" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A577" s="28">
-        <v>6</v>
-      </c>
-      <c r="B577" s="28" t="s">
+      <c r="A577">
+        <v>6</v>
+      </c>
+      <c r="B577" t="s">
         <v>36</v>
       </c>
-      <c r="C577" s="28">
-        <v>5</v>
-      </c>
-      <c r="D577" s="28" t="s">
+      <c r="C577">
+        <v>5</v>
+      </c>
+      <c r="D577" t="s">
         <v>8</v>
       </c>
-      <c r="E577" s="30">
-        <v>3</v>
-      </c>
-      <c r="F577" s="21">
+      <c r="E577" s="6">
+        <v>3</v>
+      </c>
+      <c r="F577" s="8">
         <v>3</v>
       </c>
     </row>
     <row r="578" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A578" s="28">
-        <v>6</v>
-      </c>
-      <c r="B578" s="28" t="s">
+      <c r="A578">
+        <v>6</v>
+      </c>
+      <c r="B578" t="s">
         <v>36</v>
       </c>
-      <c r="C578" s="28">
-        <v>5</v>
-      </c>
-      <c r="D578" s="28" t="s">
+      <c r="C578">
+        <v>5</v>
+      </c>
+      <c r="D578" t="s">
         <v>9</v>
       </c>
-      <c r="E578" s="30">
-        <v>3</v>
-      </c>
-      <c r="F578" s="21">
+      <c r="E578" s="6">
+        <v>3</v>
+      </c>
+      <c r="F578" s="8">
         <v>3</v>
       </c>
     </row>
     <row r="579" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A579" s="28">
-        <v>6</v>
-      </c>
-      <c r="B579" s="28" t="s">
+      <c r="A579">
+        <v>6</v>
+      </c>
+      <c r="B579" t="s">
         <v>36</v>
       </c>
-      <c r="C579" s="28">
-        <v>5</v>
-      </c>
-      <c r="D579" s="28" t="s">
+      <c r="C579">
+        <v>5</v>
+      </c>
+      <c r="D579" t="s">
         <v>10</v>
       </c>
-      <c r="E579" s="30">
-        <v>1</v>
-      </c>
-      <c r="F579" s="21">
+      <c r="E579" s="6">
+        <v>1</v>
+      </c>
+      <c r="F579" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="580" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A580" s="28">
-        <v>6</v>
-      </c>
-      <c r="B580" s="28" t="s">
+      <c r="A580">
+        <v>6</v>
+      </c>
+      <c r="B580" t="s">
         <v>36</v>
       </c>
-      <c r="C580" s="28">
-        <v>5</v>
-      </c>
-      <c r="D580" s="28" t="s">
+      <c r="C580">
+        <v>5</v>
+      </c>
+      <c r="D580" t="s">
         <v>11</v>
       </c>
-      <c r="E580" s="30">
-        <v>1</v>
-      </c>
-      <c r="F580" s="21">
+      <c r="E580" s="6">
+        <v>1</v>
+      </c>
+      <c r="F580" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="581" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A581" s="28">
-        <v>6</v>
-      </c>
-      <c r="B581" s="28" t="s">
+      <c r="A581">
+        <v>6</v>
+      </c>
+      <c r="B581" t="s">
         <v>37</v>
       </c>
-      <c r="C581" s="28">
-        <v>6</v>
-      </c>
-      <c r="D581" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="E581" s="30" t="s">
+      <c r="C581">
+        <v>6</v>
+      </c>
+      <c r="D581" t="s">
+        <v>5</v>
+      </c>
+      <c r="E581" s="6" t="s">
         <v>571</v>
       </c>
-      <c r="F581" s="21">
+      <c r="F581" s="8">
         <v>5</v>
       </c>
     </row>
     <row r="582" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A582" s="28">
-        <v>6</v>
-      </c>
-      <c r="B582" s="28" t="s">
+      <c r="A582">
+        <v>6</v>
+      </c>
+      <c r="B582" t="s">
         <v>37</v>
       </c>
-      <c r="C582" s="28">
-        <v>6</v>
-      </c>
-      <c r="D582" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="E582" s="30" t="s">
+      <c r="C582">
+        <v>6</v>
+      </c>
+      <c r="D582" t="s">
+        <v>6</v>
+      </c>
+      <c r="E582" s="6" t="s">
         <v>571</v>
       </c>
-      <c r="F582" s="21">
+      <c r="F582" s="8">
         <v>5</v>
       </c>
     </row>
     <row r="583" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A583" s="28">
-        <v>6</v>
-      </c>
-      <c r="B583" s="28" t="s">
+      <c r="A583">
+        <v>6</v>
+      </c>
+      <c r="B583" t="s">
         <v>37</v>
       </c>
-      <c r="C583" s="28">
-        <v>6</v>
-      </c>
-      <c r="D583" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="E583" s="30" t="s">
+      <c r="C583">
+        <v>6</v>
+      </c>
+      <c r="D583" t="s">
+        <v>7</v>
+      </c>
+      <c r="E583" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="F583" s="21"/>
     </row>
     <row r="584" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A584" s="28">
-        <v>6</v>
-      </c>
-      <c r="B584" s="28" t="s">
+      <c r="A584">
+        <v>6</v>
+      </c>
+      <c r="B584" t="s">
         <v>37</v>
       </c>
-      <c r="C584" s="28">
-        <v>6</v>
-      </c>
-      <c r="D584" s="28" t="s">
+      <c r="C584">
+        <v>6</v>
+      </c>
+      <c r="D584" t="s">
         <v>8</v>
       </c>
-      <c r="E584" s="30" t="s">
+      <c r="E584" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="F584" s="21"/>
     </row>
     <row r="585" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A585" s="28">
-        <v>6</v>
-      </c>
-      <c r="B585" s="28" t="s">
+      <c r="A585">
+        <v>6</v>
+      </c>
+      <c r="B585" t="s">
         <v>37</v>
       </c>
-      <c r="C585" s="28">
-        <v>6</v>
-      </c>
-      <c r="D585" s="28" t="s">
+      <c r="C585">
+        <v>6</v>
+      </c>
+      <c r="D585" t="s">
         <v>9</v>
       </c>
-      <c r="E585" s="30"/>
-      <c r="F585" s="21"/>
+      <c r="E585" s="6"/>
     </row>
     <row r="586" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A586" s="28">
-        <v>6</v>
-      </c>
-      <c r="B586" s="28" t="s">
+      <c r="A586">
+        <v>6</v>
+      </c>
+      <c r="B586" t="s">
         <v>37</v>
       </c>
-      <c r="C586" s="28">
-        <v>6</v>
-      </c>
-      <c r="D586" s="28" t="s">
+      <c r="C586">
+        <v>6</v>
+      </c>
+      <c r="D586" t="s">
         <v>10</v>
       </c>
-      <c r="E586" s="30" t="s">
+      <c r="E586" s="6" t="s">
         <v>572</v>
       </c>
-      <c r="F586" s="21">
+      <c r="F586" s="8">
         <v>3</v>
       </c>
     </row>
     <row r="587" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A587" s="28">
-        <v>6</v>
-      </c>
-      <c r="B587" s="28" t="s">
+      <c r="A587">
+        <v>6</v>
+      </c>
+      <c r="B587" t="s">
         <v>37</v>
       </c>
-      <c r="C587" s="28">
-        <v>6</v>
-      </c>
-      <c r="D587" s="28" t="s">
+      <c r="C587">
+        <v>6</v>
+      </c>
+      <c r="D587" t="s">
         <v>11</v>
       </c>
-      <c r="E587" s="30" t="s">
+      <c r="E587" s="6" t="s">
         <v>572</v>
       </c>
-      <c r="F587" s="21">
+      <c r="F587" s="8">
         <v>3</v>
       </c>
     </row>
     <row r="588" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A588" s="28">
-        <v>6</v>
-      </c>
-      <c r="B588" s="28" t="s">
+      <c r="A588">
+        <v>6</v>
+      </c>
+      <c r="B588" t="s">
         <v>38</v>
       </c>
-      <c r="C588" s="28">
-        <v>7</v>
-      </c>
-      <c r="D588" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="E588" s="22"/>
-      <c r="F588" s="21"/>
+      <c r="C588">
+        <v>7</v>
+      </c>
+      <c r="D588" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="589" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A589" s="28">
-        <v>6</v>
-      </c>
-      <c r="B589" s="28" t="s">
+      <c r="A589">
+        <v>6</v>
+      </c>
+      <c r="B589" t="s">
         <v>38</v>
       </c>
-      <c r="C589" s="28">
-        <v>7</v>
-      </c>
-      <c r="D589" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="E589" s="22"/>
-      <c r="F589" s="21"/>
+      <c r="C589">
+        <v>7</v>
+      </c>
+      <c r="D589" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="590" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A590" s="28">
-        <v>6</v>
-      </c>
-      <c r="B590" s="28" t="s">
+      <c r="A590">
+        <v>6</v>
+      </c>
+      <c r="B590" t="s">
         <v>38</v>
       </c>
-      <c r="C590" s="28">
-        <v>7</v>
-      </c>
-      <c r="D590" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="E590" s="22"/>
-      <c r="F590" s="21"/>
+      <c r="C590">
+        <v>7</v>
+      </c>
+      <c r="D590" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="591" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A591" s="28">
-        <v>6</v>
-      </c>
-      <c r="B591" s="28" t="s">
+      <c r="A591">
+        <v>6</v>
+      </c>
+      <c r="B591" t="s">
         <v>38</v>
       </c>
-      <c r="C591" s="28">
-        <v>7</v>
-      </c>
-      <c r="D591" s="28" t="s">
+      <c r="C591">
+        <v>7</v>
+      </c>
+      <c r="D591" t="s">
         <v>8</v>
       </c>
-      <c r="E591" s="22"/>
-      <c r="F591" s="21"/>
     </row>
     <row r="592" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A592" s="28">
-        <v>6</v>
-      </c>
-      <c r="B592" s="28" t="s">
+      <c r="A592">
+        <v>6</v>
+      </c>
+      <c r="B592" t="s">
         <v>38</v>
       </c>
-      <c r="C592" s="28">
-        <v>7</v>
-      </c>
-      <c r="D592" s="28" t="s">
+      <c r="C592">
+        <v>7</v>
+      </c>
+      <c r="D592" t="s">
         <v>9</v>
       </c>
-      <c r="E592" s="22"/>
-      <c r="F592" s="21"/>
     </row>
     <row r="593" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A593" s="28">
-        <v>6</v>
-      </c>
-      <c r="B593" s="28" t="s">
+      <c r="A593">
+        <v>6</v>
+      </c>
+      <c r="B593" t="s">
         <v>38</v>
       </c>
-      <c r="C593" s="28">
-        <v>7</v>
-      </c>
-      <c r="D593" s="28" t="s">
+      <c r="C593">
+        <v>7</v>
+      </c>
+      <c r="D593" t="s">
         <v>10</v>
       </c>
-      <c r="E593" s="22"/>
-      <c r="F593" s="21"/>
     </row>
     <row r="594" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A594" s="28">
-        <v>6</v>
-      </c>
-      <c r="B594" s="28" t="s">
+      <c r="A594">
+        <v>6</v>
+      </c>
+      <c r="B594" t="s">
         <v>38</v>
       </c>
-      <c r="C594" s="28">
-        <v>7</v>
-      </c>
-      <c r="D594" s="28" t="s">
+      <c r="C594">
+        <v>7</v>
+      </c>
+      <c r="D594" t="s">
         <v>11</v>
       </c>
-      <c r="E594" s="22"/>
-      <c r="F594" s="21"/>
     </row>
     <row r="595" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A595" s="28">
-        <v>6</v>
-      </c>
-      <c r="B595" s="28" t="s">
+      <c r="A595">
+        <v>6</v>
+      </c>
+      <c r="B595" t="s">
         <v>38</v>
       </c>
-      <c r="C595" s="28">
-        <v>7</v>
-      </c>
-      <c r="D595" s="28" t="s">
+      <c r="C595">
+        <v>7</v>
+      </c>
+      <c r="D595" t="s">
         <v>98</v>
       </c>
-      <c r="E595" s="23" t="s">
+      <c r="E595" s="18" t="s">
         <v>573</v>
       </c>
-      <c r="F595" s="21">
+      <c r="F595" s="8">
         <v>4</v>
       </c>
     </row>
     <row r="596" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A596" s="28">
-        <v>6</v>
-      </c>
-      <c r="B596" s="28" t="s">
+      <c r="A596">
+        <v>6</v>
+      </c>
+      <c r="B596" t="s">
         <v>39</v>
       </c>
-      <c r="C596" s="28">
+      <c r="C596">
         <v>8</v>
       </c>
-      <c r="D596" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E596" s="23" t="s">
+      <c r="D596" t="s">
+        <v>32</v>
+      </c>
+      <c r="E596" s="18" t="s">
         <v>574</v>
       </c>
-      <c r="F596" s="21">
+      <c r="F596" s="8">
         <v>3</v>
       </c>
     </row>
     <row r="597" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A597" s="28">
-        <v>6</v>
-      </c>
-      <c r="B597" s="28" t="s">
+      <c r="A597">
+        <v>6</v>
+      </c>
+      <c r="B597" t="s">
         <v>40</v>
       </c>
-      <c r="C597" s="28">
+      <c r="C597">
         <v>9</v>
       </c>
-      <c r="D597" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="E597" s="30" t="s">
+      <c r="D597" t="s">
+        <v>5</v>
+      </c>
+      <c r="E597" s="6" t="s">
         <v>575</v>
       </c>
-      <c r="F597" s="21">
+      <c r="F597" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="598" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A598" s="28">
-        <v>6</v>
-      </c>
-      <c r="B598" s="28" t="s">
+      <c r="A598">
+        <v>6</v>
+      </c>
+      <c r="B598" t="s">
         <v>40</v>
       </c>
-      <c r="C598" s="28">
+      <c r="C598">
         <v>9</v>
       </c>
-      <c r="D598" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="E598" s="30" t="s">
+      <c r="D598" t="s">
+        <v>6</v>
+      </c>
+      <c r="E598" s="6" t="s">
         <v>576</v>
       </c>
-      <c r="F598" s="21"/>
     </row>
     <row r="599" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A599" s="28">
-        <v>6</v>
-      </c>
-      <c r="B599" s="28" t="s">
+      <c r="A599">
+        <v>6</v>
+      </c>
+      <c r="B599" t="s">
         <v>40</v>
       </c>
-      <c r="C599" s="28">
+      <c r="C599">
         <v>9</v>
       </c>
-      <c r="D599" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="E599" s="30" t="s">
+      <c r="D599" t="s">
+        <v>7</v>
+      </c>
+      <c r="E599" s="6" t="s">
         <v>577</v>
       </c>
-      <c r="F599" s="21">
+      <c r="F599" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="600" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A600" s="28">
-        <v>6</v>
-      </c>
-      <c r="B600" s="28" t="s">
+      <c r="A600">
+        <v>6</v>
+      </c>
+      <c r="B600" t="s">
         <v>40</v>
       </c>
-      <c r="C600" s="28">
+      <c r="C600">
         <v>9</v>
       </c>
-      <c r="D600" s="28" t="s">
+      <c r="D600" t="s">
         <v>8</v>
       </c>
-      <c r="E600" s="30">
+      <c r="E600" s="6">
         <v>0</v>
       </c>
-      <c r="F600" s="21">
+      <c r="F600" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="601" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A601" s="28">
-        <v>6</v>
-      </c>
-      <c r="B601" s="28" t="s">
+      <c r="A601">
+        <v>6</v>
+      </c>
+      <c r="B601" t="s">
         <v>40</v>
       </c>
-      <c r="C601" s="28">
+      <c r="C601">
         <v>9</v>
       </c>
-      <c r="D601" s="28" t="s">
+      <c r="D601" t="s">
         <v>9</v>
       </c>
-      <c r="E601" s="30">
-        <v>1</v>
-      </c>
-      <c r="F601" s="21">
+      <c r="E601" s="6">
+        <v>1</v>
+      </c>
+      <c r="F601" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="602" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A602" s="28">
-        <v>6</v>
-      </c>
-      <c r="B602" s="28" t="s">
+      <c r="A602">
+        <v>6</v>
+      </c>
+      <c r="B602" t="s">
         <v>40</v>
       </c>
-      <c r="C602" s="28">
+      <c r="C602">
         <v>9</v>
       </c>
-      <c r="D602" s="28" t="s">
+      <c r="D602" t="s">
         <v>10</v>
       </c>
-      <c r="E602" s="30">
-        <v>1</v>
-      </c>
-      <c r="F602" s="21">
+      <c r="E602" s="6">
+        <v>1</v>
+      </c>
+      <c r="F602" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="603" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A603" s="28">
-        <v>6</v>
-      </c>
-      <c r="B603" s="28" t="s">
+      <c r="A603">
+        <v>6</v>
+      </c>
+      <c r="B603" t="s">
         <v>40</v>
       </c>
-      <c r="C603" s="28">
+      <c r="C603">
         <v>9</v>
       </c>
-      <c r="D603" s="28" t="s">
+      <c r="D603" t="s">
         <v>11</v>
       </c>
-      <c r="E603" s="30" t="s">
+      <c r="E603" s="6" t="s">
         <v>578</v>
       </c>
-      <c r="F603" s="21">
+      <c r="F603" s="8">
         <v>2.5</v>
       </c>
     </row>
     <row r="604" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A604" s="28">
-        <v>6</v>
-      </c>
-      <c r="B604" s="28" t="s">
+      <c r="A604">
+        <v>6</v>
+      </c>
+      <c r="B604" t="s">
         <v>41</v>
       </c>
-      <c r="C604" s="28">
+      <c r="C604">
         <v>10</v>
       </c>
-      <c r="D604" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="E604" s="30" t="s">
+      <c r="D604" t="s">
+        <v>5</v>
+      </c>
+      <c r="E604" s="6" t="s">
         <v>579</v>
       </c>
-      <c r="F604" s="21">
+      <c r="F604" s="8">
         <v>3</v>
       </c>
     </row>
     <row r="605" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A605" s="28">
-        <v>6</v>
-      </c>
-      <c r="B605" s="28" t="s">
+      <c r="A605">
+        <v>6</v>
+      </c>
+      <c r="B605" t="s">
         <v>41</v>
       </c>
-      <c r="C605" s="28">
+      <c r="C605">
         <v>10</v>
       </c>
-      <c r="D605" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="E605" s="30">
+      <c r="D605" t="s">
+        <v>6</v>
+      </c>
+      <c r="E605" s="6">
         <v>0</v>
       </c>
-      <c r="F605" s="21">
+      <c r="F605" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="606" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A606" s="28">
-        <v>6</v>
-      </c>
-      <c r="B606" s="28" t="s">
+      <c r="A606">
+        <v>6</v>
+      </c>
+      <c r="B606" t="s">
         <v>41</v>
       </c>
-      <c r="C606" s="28">
+      <c r="C606">
         <v>10</v>
       </c>
-      <c r="D606" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="E606" s="30" t="s">
+      <c r="D606" t="s">
+        <v>7</v>
+      </c>
+      <c r="E606" s="6" t="s">
         <v>580</v>
       </c>
-      <c r="F606" s="21">
+      <c r="F606" s="8">
         <v>3</v>
       </c>
     </row>
     <row r="607" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A607" s="28">
-        <v>6</v>
-      </c>
-      <c r="B607" s="28" t="s">
+      <c r="A607">
+        <v>6</v>
+      </c>
+      <c r="B607" t="s">
         <v>41</v>
       </c>
-      <c r="C607" s="28">
+      <c r="C607">
         <v>10</v>
       </c>
-      <c r="D607" s="28" t="s">
+      <c r="D607" t="s">
         <v>8</v>
       </c>
-      <c r="E607" s="30">
+      <c r="E607" s="6">
         <v>0</v>
       </c>
-      <c r="F607" s="21">
+      <c r="F607" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="608" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A608" s="28">
-        <v>6</v>
-      </c>
-      <c r="B608" s="28" t="s">
+      <c r="A608">
+        <v>6</v>
+      </c>
+      <c r="B608" t="s">
         <v>41</v>
       </c>
-      <c r="C608" s="28">
+      <c r="C608">
         <v>10</v>
       </c>
-      <c r="D608" s="28" t="s">
+      <c r="D608" t="s">
         <v>9</v>
       </c>
-      <c r="E608" s="30">
+      <c r="E608" s="6">
         <v>0</v>
       </c>
-      <c r="F608" s="21">
+      <c r="F608" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="609" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A609" s="28">
-        <v>6</v>
-      </c>
-      <c r="B609" s="28" t="s">
+      <c r="A609">
+        <v>6</v>
+      </c>
+      <c r="B609" t="s">
         <v>41</v>
       </c>
-      <c r="C609" s="28">
+      <c r="C609">
         <v>10</v>
       </c>
-      <c r="D609" s="28" t="s">
+      <c r="D609" t="s">
         <v>10</v>
       </c>
-      <c r="E609" s="30">
+      <c r="E609" s="6">
         <v>0</v>
       </c>
-      <c r="F609" s="21">
+      <c r="F609" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="610" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A610" s="28">
-        <v>6</v>
-      </c>
-      <c r="B610" s="28" t="s">
+      <c r="A610">
+        <v>6</v>
+      </c>
+      <c r="B610" t="s">
         <v>41</v>
       </c>
-      <c r="C610" s="28">
+      <c r="C610">
         <v>10</v>
       </c>
-      <c r="D610" s="28" t="s">
+      <c r="D610" t="s">
         <v>11</v>
       </c>
-      <c r="E610" s="30" t="s">
+      <c r="E610" s="6" t="s">
         <v>581</v>
       </c>
-      <c r="F610" s="21">
+      <c r="F610" s="8">
         <v>3</v>
       </c>
     </row>
     <row r="611" spans="1:6" ht="72" x14ac:dyDescent="0.3">
-      <c r="A611" s="28">
-        <v>6</v>
-      </c>
-      <c r="B611" s="28" t="s">
+      <c r="A611">
+        <v>6</v>
+      </c>
+      <c r="B611" t="s">
         <v>42</v>
       </c>
-      <c r="C611" s="28">
+      <c r="C611">
         <v>11</v>
       </c>
-      <c r="D611" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E611" s="23" t="s">
+      <c r="D611" t="s">
+        <v>32</v>
+      </c>
+      <c r="E611" s="18" t="s">
         <v>582</v>
       </c>
-      <c r="F611" s="21"/>
     </row>
     <row r="612" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A612" s="28">
-        <v>6</v>
-      </c>
-      <c r="B612" s="28" t="s">
+      <c r="A612">
+        <v>6</v>
+      </c>
+      <c r="B612" t="s">
         <v>43</v>
       </c>
-      <c r="C612" s="28">
+      <c r="C612">
         <v>12</v>
       </c>
-      <c r="D612" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E612" s="23" t="s">
+      <c r="D612" t="s">
+        <v>32</v>
+      </c>
+      <c r="E612" s="18" t="s">
         <v>583</v>
       </c>
-      <c r="F612" s="21"/>
     </row>
     <row r="613" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A613" s="28">
-        <v>6</v>
-      </c>
-      <c r="B613" s="28" t="s">
+      <c r="A613">
+        <v>6</v>
+      </c>
+      <c r="B613" t="s">
         <v>44</v>
       </c>
-      <c r="C613" s="28">
+      <c r="C613">
         <v>13</v>
       </c>
-      <c r="D613" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="E613" s="30" t="s">
+      <c r="D613" t="s">
+        <v>5</v>
+      </c>
+      <c r="E613" s="6" t="s">
         <v>584</v>
       </c>
-      <c r="F613" s="21">
+      <c r="F613" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="614" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A614" s="28">
-        <v>6</v>
-      </c>
-      <c r="B614" s="28" t="s">
+      <c r="A614">
+        <v>6</v>
+      </c>
+      <c r="B614" t="s">
         <v>44</v>
       </c>
-      <c r="C614" s="28">
+      <c r="C614">
         <v>13</v>
       </c>
-      <c r="D614" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="E614" s="30">
+      <c r="D614" t="s">
+        <v>6</v>
+      </c>
+      <c r="E614" s="6">
         <v>0</v>
       </c>
-      <c r="F614" s="21">
+      <c r="F614" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="615" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A615" s="28">
-        <v>6</v>
-      </c>
-      <c r="B615" s="28" t="s">
+      <c r="A615">
+        <v>6</v>
+      </c>
+      <c r="B615" t="s">
         <v>44</v>
       </c>
-      <c r="C615" s="28">
+      <c r="C615">
         <v>13</v>
       </c>
-      <c r="D615" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="E615" s="30" t="s">
+      <c r="D615" t="s">
+        <v>7</v>
+      </c>
+      <c r="E615" s="6" t="s">
         <v>585</v>
       </c>
-      <c r="F615" s="21">
+      <c r="F615" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="616" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A616" s="28">
-        <v>6</v>
-      </c>
-      <c r="B616" s="28" t="s">
+      <c r="A616">
+        <v>6</v>
+      </c>
+      <c r="B616" t="s">
         <v>44</v>
       </c>
-      <c r="C616" s="28">
+      <c r="C616">
         <v>13</v>
       </c>
-      <c r="D616" s="28" t="s">
+      <c r="D616" t="s">
         <v>8</v>
       </c>
-      <c r="E616" s="30">
+      <c r="E616" s="6">
         <v>0</v>
       </c>
-      <c r="F616" s="21">
+      <c r="F616" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="617" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A617" s="28">
-        <v>6</v>
-      </c>
-      <c r="B617" s="28" t="s">
+      <c r="A617">
+        <v>6</v>
+      </c>
+      <c r="B617" t="s">
         <v>44</v>
       </c>
-      <c r="C617" s="28">
+      <c r="C617">
         <v>13</v>
       </c>
-      <c r="D617" s="28" t="s">
+      <c r="D617" t="s">
         <v>9</v>
       </c>
-      <c r="E617" s="30">
+      <c r="E617" s="6">
         <v>0</v>
       </c>
-      <c r="F617" s="21">
+      <c r="F617" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="618" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A618" s="28">
-        <v>6</v>
-      </c>
-      <c r="B618" s="28" t="s">
+      <c r="A618">
+        <v>6</v>
+      </c>
+      <c r="B618" t="s">
         <v>44</v>
       </c>
-      <c r="C618" s="28">
+      <c r="C618">
         <v>13</v>
       </c>
-      <c r="D618" s="28" t="s">
+      <c r="D618" t="s">
         <v>10</v>
       </c>
-      <c r="E618" s="30">
+      <c r="E618" s="6">
         <v>0</v>
       </c>
-      <c r="F618" s="21">
+      <c r="F618" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="619" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A619" s="28">
-        <v>6</v>
-      </c>
-      <c r="B619" s="28" t="s">
+      <c r="A619">
+        <v>6</v>
+      </c>
+      <c r="B619" t="s">
         <v>44</v>
       </c>
-      <c r="C619" s="28">
+      <c r="C619">
         <v>13</v>
       </c>
-      <c r="D619" s="28" t="s">
+      <c r="D619" t="s">
         <v>11</v>
       </c>
-      <c r="E619" s="30" t="s">
+      <c r="E619" s="6" t="s">
         <v>585</v>
       </c>
-      <c r="F619" s="21">
+      <c r="F619" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="620" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A620" s="28">
-        <v>6</v>
-      </c>
-      <c r="B620" s="28" t="s">
+      <c r="A620">
+        <v>6</v>
+      </c>
+      <c r="B620" t="s">
         <v>45</v>
       </c>
-      <c r="C620" s="28">
+      <c r="C620">
         <v>14</v>
       </c>
-      <c r="D620" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E620" s="30" t="s">
+      <c r="D620" t="s">
+        <v>32</v>
+      </c>
+      <c r="E620" s="6" t="s">
         <v>586</v>
       </c>
-      <c r="F620" s="21">
+      <c r="F620" s="8">
         <v>4</v>
       </c>
     </row>
     <row r="621" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A621" s="28">
-        <v>6</v>
-      </c>
-      <c r="B621" s="28" t="s">
+      <c r="A621">
+        <v>6</v>
+      </c>
+      <c r="B621" t="s">
         <v>46</v>
       </c>
-      <c r="C621" s="28">
+      <c r="C621">
         <v>15</v>
       </c>
-      <c r="D621" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="E621" s="29" t="s">
+      <c r="D621" t="s">
+        <v>5</v>
+      </c>
+      <c r="E621" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="F621" s="21">
+      <c r="F621" s="8">
         <v>3.5</v>
       </c>
     </row>
     <row r="622" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A622" s="28">
-        <v>6</v>
-      </c>
-      <c r="B622" s="28" t="s">
+      <c r="A622">
+        <v>6</v>
+      </c>
+      <c r="B622" t="s">
         <v>46</v>
       </c>
-      <c r="C622" s="28">
+      <c r="C622">
         <v>15</v>
       </c>
-      <c r="D622" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="E622" s="29" t="s">
+      <c r="D622" t="s">
+        <v>6</v>
+      </c>
+      <c r="E622" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="F622" s="21"/>
     </row>
     <row r="623" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A623" s="28">
-        <v>6</v>
-      </c>
-      <c r="B623" s="28" t="s">
+      <c r="A623">
+        <v>6</v>
+      </c>
+      <c r="B623" t="s">
         <v>46</v>
       </c>
-      <c r="C623" s="28">
+      <c r="C623">
         <v>15</v>
       </c>
-      <c r="D623" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="E623" s="29" t="s">
+      <c r="D623" t="s">
+        <v>7</v>
+      </c>
+      <c r="E623" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="F623" s="21"/>
     </row>
     <row r="624" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A624" s="28">
-        <v>6</v>
-      </c>
-      <c r="B624" s="28" t="s">
+      <c r="A624">
+        <v>6</v>
+      </c>
+      <c r="B624" t="s">
         <v>46</v>
       </c>
-      <c r="C624" s="28">
+      <c r="C624">
         <v>15</v>
       </c>
-      <c r="D624" s="28" t="s">
+      <c r="D624" t="s">
         <v>8</v>
       </c>
-      <c r="E624" s="29" t="s">
+      <c r="E624" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="F624" s="21"/>
     </row>
     <row r="625" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A625" s="28">
-        <v>6</v>
-      </c>
-      <c r="B625" s="28" t="s">
+      <c r="A625">
+        <v>6</v>
+      </c>
+      <c r="B625" t="s">
         <v>46</v>
       </c>
-      <c r="C625" s="28">
+      <c r="C625">
         <v>15</v>
       </c>
-      <c r="D625" s="28" t="s">
+      <c r="D625" t="s">
         <v>9</v>
       </c>
-      <c r="E625" s="29" t="s">
+      <c r="E625" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="F625" s="21"/>
     </row>
     <row r="626" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A626" s="28">
-        <v>6</v>
-      </c>
-      <c r="B626" s="28" t="s">
+      <c r="A626">
+        <v>6</v>
+      </c>
+      <c r="B626" t="s">
         <v>46</v>
       </c>
-      <c r="C626" s="28">
+      <c r="C626">
         <v>15</v>
       </c>
-      <c r="D626" s="28" t="s">
+      <c r="D626" t="s">
         <v>10</v>
       </c>
-      <c r="E626" s="29" t="s">
+      <c r="E626" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="F626" s="21"/>
     </row>
     <row r="627" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A627" s="28">
-        <v>6</v>
-      </c>
-      <c r="B627" s="28" t="s">
+      <c r="A627">
+        <v>6</v>
+      </c>
+      <c r="B627" t="s">
         <v>46</v>
       </c>
-      <c r="C627" s="28">
+      <c r="C627">
         <v>15</v>
       </c>
-      <c r="D627" s="28" t="s">
+      <c r="D627" t="s">
         <v>11</v>
       </c>
-      <c r="E627" s="29" t="s">
+      <c r="E627" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="F627" s="21"/>
     </row>
     <row r="628" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A628" s="28">
-        <v>6</v>
-      </c>
-      <c r="B628" s="28" t="s">
+      <c r="A628">
+        <v>6</v>
+      </c>
+      <c r="B628" t="s">
         <v>47</v>
       </c>
-      <c r="C628" s="28">
+      <c r="C628">
         <v>16</v>
       </c>
-      <c r="D628" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E628" s="30" t="s">
+      <c r="D628" t="s">
+        <v>32</v>
+      </c>
+      <c r="E628" s="6" t="s">
         <v>592</v>
       </c>
-      <c r="F628" s="21"/>
     </row>
     <row r="629" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A629" s="28">
-        <v>6</v>
-      </c>
-      <c r="B629" s="28" t="s">
+      <c r="A629">
+        <v>6</v>
+      </c>
+      <c r="B629" t="s">
         <v>48</v>
       </c>
-      <c r="C629" s="28">
+      <c r="C629">
         <v>17</v>
       </c>
-      <c r="D629" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E629" s="23" t="s">
+      <c r="D629" t="s">
+        <v>32</v>
+      </c>
+      <c r="E629" s="18" t="s">
         <v>593</v>
       </c>
-      <c r="F629" s="21"/>
     </row>
     <row r="630" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A630" s="28">
-        <v>6</v>
-      </c>
-      <c r="B630" s="28" t="s">
+      <c r="A630">
+        <v>6</v>
+      </c>
+      <c r="B630" t="s">
         <v>49</v>
       </c>
-      <c r="C630" s="28">
+      <c r="C630">
         <v>18</v>
       </c>
-      <c r="D630" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E630" s="22" t="s">
+      <c r="D630" t="s">
+        <v>32</v>
+      </c>
+      <c r="E630" s="16" t="s">
         <v>594</v>
       </c>
-      <c r="F630" s="21">
+      <c r="F630" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="631" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A631" s="28">
-        <v>6</v>
-      </c>
-      <c r="B631" s="28" t="s">
+      <c r="A631">
+        <v>6</v>
+      </c>
+      <c r="B631" t="s">
         <v>50</v>
       </c>
-      <c r="C631" s="28">
+      <c r="C631">
         <v>19</v>
       </c>
-      <c r="D631" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E631" s="30" t="s">
+      <c r="D631" t="s">
+        <v>32</v>
+      </c>
+      <c r="E631" s="6" t="s">
         <v>595</v>
       </c>
-      <c r="F631" s="21"/>
     </row>
     <row r="632" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A632" s="28">
-        <v>6</v>
-      </c>
-      <c r="B632" s="28" t="s">
+      <c r="A632">
+        <v>6</v>
+      </c>
+      <c r="B632" t="s">
         <v>51</v>
       </c>
-      <c r="C632" s="28">
+      <c r="C632">
         <v>20</v>
       </c>
-      <c r="D632" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E632" s="30" t="s">
+      <c r="D632" t="s">
+        <v>32</v>
+      </c>
+      <c r="E632" s="6" t="s">
         <v>596</v>
       </c>
-      <c r="F632" s="21">
+      <c r="F632" s="8">
         <v>1.5</v>
       </c>
     </row>
     <row r="633" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A633" s="28">
-        <v>6</v>
-      </c>
-      <c r="B633" s="28" t="s">
+      <c r="A633">
+        <v>6</v>
+      </c>
+      <c r="B633" t="s">
         <v>52</v>
       </c>
-      <c r="C633" s="28">
+      <c r="C633">
         <v>21</v>
       </c>
-      <c r="D633" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="E633" s="30" t="s">
+      <c r="D633" t="s">
+        <v>5</v>
+      </c>
+      <c r="E633" s="6" t="s">
         <v>597</v>
       </c>
-      <c r="F633" s="21">
+      <c r="F633" s="8">
         <v>4</v>
       </c>
     </row>
     <row r="634" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A634" s="28">
-        <v>6</v>
-      </c>
-      <c r="B634" s="28" t="s">
+      <c r="A634">
+        <v>6</v>
+      </c>
+      <c r="B634" t="s">
         <v>53</v>
       </c>
-      <c r="C634" s="28">
+      <c r="C634">
         <v>21</v>
       </c>
-      <c r="D634" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="E634" s="23" t="s">
+      <c r="D634" t="s">
+        <v>6</v>
+      </c>
+      <c r="E634" s="18" t="s">
         <v>598</v>
       </c>
-      <c r="F634" s="21"/>
     </row>
     <row r="635" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A635" s="28">
-        <v>6</v>
-      </c>
-      <c r="B635" s="28" t="s">
+      <c r="A635">
+        <v>6</v>
+      </c>
+      <c r="B635" t="s">
         <v>54</v>
       </c>
-      <c r="C635" s="28">
+      <c r="C635">
         <v>21</v>
       </c>
-      <c r="D635" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="E635" s="23" t="s">
+      <c r="D635" t="s">
+        <v>7</v>
+      </c>
+      <c r="E635" s="18" t="s">
         <v>599</v>
       </c>
-      <c r="F635" s="21">
+      <c r="F635" s="8">
         <v>4</v>
       </c>
     </row>
     <row r="636" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A636" s="28">
-        <v>6</v>
-      </c>
-      <c r="B636" s="28" t="s">
+      <c r="A636">
+        <v>6</v>
+      </c>
+      <c r="B636" t="s">
         <v>55</v>
       </c>
-      <c r="C636" s="28">
+      <c r="C636">
         <v>22</v>
       </c>
-      <c r="D636" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E636" s="23" t="s">
+      <c r="D636" t="s">
+        <v>32</v>
+      </c>
+      <c r="E636" s="18" t="s">
         <v>600</v>
       </c>
-      <c r="F636" s="21">
+      <c r="F636" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="637" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A637" s="28">
-        <v>6</v>
-      </c>
-      <c r="B637" s="28" t="s">
+      <c r="A637">
+        <v>6</v>
+      </c>
+      <c r="B637" t="s">
         <v>56</v>
       </c>
-      <c r="C637" s="28">
+      <c r="C637">
         <v>23</v>
       </c>
-      <c r="D637" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E637" s="22" t="s">
+      <c r="D637" t="s">
+        <v>32</v>
+      </c>
+      <c r="E637" s="16" t="s">
         <v>601</v>
       </c>
-      <c r="F637" s="21">
+      <c r="F637" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="638" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A638" s="28">
-        <v>6</v>
-      </c>
-      <c r="B638" s="28" t="s">
+      <c r="A638">
+        <v>6</v>
+      </c>
+      <c r="B638" t="s">
         <v>57</v>
       </c>
-      <c r="C638" s="28">
+      <c r="C638">
         <v>24</v>
       </c>
-      <c r="D638" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E638" s="23" t="s">
+      <c r="D638" t="s">
+        <v>32</v>
+      </c>
+      <c r="E638" s="18" t="s">
         <v>602</v>
       </c>
-      <c r="F638" s="21">
+      <c r="F638" s="8">
         <v>4.5</v>
       </c>
     </row>
     <row r="639" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A639" s="28">
-        <v>6</v>
-      </c>
-      <c r="B639" s="28" t="s">
+      <c r="A639">
+        <v>6</v>
+      </c>
+      <c r="B639" t="s">
         <v>58</v>
       </c>
-      <c r="C639" s="28">
+      <c r="C639">
         <v>25</v>
       </c>
-      <c r="D639" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E639" s="22" t="s">
+      <c r="D639" t="s">
+        <v>32</v>
+      </c>
+      <c r="E639" s="16" t="s">
         <v>603</v>
       </c>
-      <c r="F639" s="21">
+      <c r="F639" s="8">
         <v>5</v>
       </c>
     </row>
     <row r="640" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A640" s="28">
-        <v>6</v>
-      </c>
-      <c r="B640" s="28" t="s">
+      <c r="A640">
+        <v>6</v>
+      </c>
+      <c r="B640" t="s">
         <v>59</v>
       </c>
-      <c r="C640" s="28">
+      <c r="C640">
         <v>26</v>
       </c>
-      <c r="D640" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E640" s="23" t="s">
+      <c r="D640" t="s">
+        <v>32</v>
+      </c>
+      <c r="E640" s="18" t="s">
         <v>604</v>
       </c>
-      <c r="F640" s="21">
+      <c r="F640" s="8">
         <v>5</v>
       </c>
     </row>
     <row r="641" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A641" s="28">
-        <v>6</v>
-      </c>
-      <c r="B641" s="28" t="s">
+      <c r="A641">
+        <v>6</v>
+      </c>
+      <c r="B641" t="s">
         <v>60</v>
       </c>
-      <c r="C641" s="28">
+      <c r="C641">
         <v>27</v>
       </c>
-      <c r="D641" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E641" s="22" t="s">
+      <c r="D641" t="s">
+        <v>32</v>
+      </c>
+      <c r="E641" s="16" t="s">
         <v>605</v>
       </c>
-      <c r="F641" s="21">
+      <c r="F641" s="8">
         <v>5</v>
       </c>
     </row>
     <row r="642" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A642" s="28">
-        <v>6</v>
-      </c>
-      <c r="B642" s="28" t="s">
+      <c r="A642">
+        <v>6</v>
+      </c>
+      <c r="B642" t="s">
         <v>61</v>
       </c>
-      <c r="C642" s="28">
+      <c r="C642">
         <v>28</v>
       </c>
-      <c r="D642" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E642" s="23" t="s">
+      <c r="D642" t="s">
+        <v>32</v>
+      </c>
+      <c r="E642" s="18" t="s">
         <v>606</v>
       </c>
-      <c r="F642" s="21">
+      <c r="F642" s="8">
         <v>3</v>
       </c>
     </row>
     <row r="643" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A643" s="28">
-        <v>6</v>
-      </c>
-      <c r="B643" s="28" t="s">
+      <c r="A643">
+        <v>6</v>
+      </c>
+      <c r="B643" t="s">
         <v>62</v>
       </c>
-      <c r="C643" s="28">
+      <c r="C643">
         <v>29</v>
       </c>
-      <c r="D643" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E643" s="22" t="s">
+      <c r="D643" t="s">
+        <v>32</v>
+      </c>
+      <c r="E643" s="16" t="s">
         <v>607</v>
       </c>
-      <c r="F643" s="21">
+      <c r="F643" s="8">
         <v>5</v>
       </c>
     </row>
     <row r="644" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A644" s="28">
-        <v>6</v>
-      </c>
-      <c r="B644" s="28" t="s">
+      <c r="A644">
+        <v>6</v>
+      </c>
+      <c r="B644" t="s">
         <v>63</v>
       </c>
-      <c r="C644" s="28">
+      <c r="C644">
         <v>30</v>
       </c>
-      <c r="D644" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E644" s="30" t="s">
+      <c r="D644" t="s">
+        <v>32</v>
+      </c>
+      <c r="E644" s="6" t="s">
         <v>608</v>
       </c>
-      <c r="F644" s="21">
+      <c r="F644" s="8">
         <v>5</v>
       </c>
     </row>
     <row r="645" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A645" s="28">
-        <v>6</v>
-      </c>
-      <c r="B645" s="28" t="s">
+      <c r="A645">
+        <v>6</v>
+      </c>
+      <c r="B645" t="s">
         <v>64</v>
       </c>
-      <c r="C645" s="28">
+      <c r="C645">
         <v>31</v>
       </c>
-      <c r="D645" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E645" s="23" t="s">
+      <c r="D645" t="s">
+        <v>32</v>
+      </c>
+      <c r="E645" s="18" t="s">
         <v>609</v>
       </c>
-      <c r="F645" s="21"/>
     </row>
     <row r="646" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A646" s="28">
-        <v>6</v>
-      </c>
-      <c r="B646" s="28" t="s">
+      <c r="A646">
+        <v>6</v>
+      </c>
+      <c r="B646" t="s">
         <v>65</v>
       </c>
-      <c r="C646" s="28">
-        <v>32</v>
-      </c>
-      <c r="D646" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E646" s="22" t="s">
+      <c r="C646">
+        <v>32</v>
+      </c>
+      <c r="D646" t="s">
+        <v>32</v>
+      </c>
+      <c r="E646" s="16" t="s">
         <v>610</v>
       </c>
-      <c r="F646" s="21"/>
     </row>
     <row r="647" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A647" s="28">
-        <v>6</v>
-      </c>
-      <c r="B647" s="28" t="s">
+      <c r="A647">
+        <v>6</v>
+      </c>
+      <c r="B647" t="s">
         <v>66</v>
       </c>
-      <c r="C647" s="28">
+      <c r="C647">
         <v>33</v>
       </c>
-      <c r="D647" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E647" s="30" t="s">
+      <c r="D647" t="s">
+        <v>32</v>
+      </c>
+      <c r="E647" s="6" t="s">
         <v>611</v>
       </c>
-      <c r="F647" s="21"/>
     </row>
     <row r="648" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A648" s="28">
-        <v>6</v>
-      </c>
-      <c r="B648" s="28" t="s">
+      <c r="A648">
+        <v>6</v>
+      </c>
+      <c r="B648" t="s">
         <v>67</v>
       </c>
-      <c r="C648" s="28">
+      <c r="C648">
         <v>34</v>
       </c>
-      <c r="D648" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E648" s="23" t="s">
+      <c r="D648" t="s">
+        <v>32</v>
+      </c>
+      <c r="E648" s="18" t="s">
         <v>612</v>
       </c>
-      <c r="F648" s="21"/>
     </row>
     <row r="649" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A649" s="28">
-        <v>6</v>
-      </c>
-      <c r="B649" s="28" t="s">
+      <c r="A649">
+        <v>6</v>
+      </c>
+      <c r="B649" t="s">
         <v>68</v>
       </c>
-      <c r="C649" s="28">
+      <c r="C649">
         <v>35</v>
       </c>
-      <c r="D649" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E649" s="30" t="s">
+      <c r="D649" t="s">
+        <v>32</v>
+      </c>
+      <c r="E649" s="6" t="s">
         <v>623</v>
       </c>
-      <c r="F649" s="21"/>
     </row>
     <row r="650" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A650" s="28">
-        <v>6</v>
-      </c>
-      <c r="B650" s="28" t="s">
+      <c r="A650">
+        <v>6</v>
+      </c>
+      <c r="B650" t="s">
         <v>69</v>
       </c>
-      <c r="C650" s="28">
+      <c r="C650">
         <v>36</v>
       </c>
-      <c r="D650" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E650" s="30" t="s">
+      <c r="D650" t="s">
+        <v>32</v>
+      </c>
+      <c r="E650" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="F650" s="21"/>
     </row>
     <row r="651" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A651" s="28">
-        <v>6</v>
-      </c>
-      <c r="B651" s="28" t="s">
+      <c r="A651">
+        <v>6</v>
+      </c>
+      <c r="B651" t="s">
         <v>70</v>
       </c>
-      <c r="C651" s="28">
+      <c r="C651">
         <v>37</v>
       </c>
-      <c r="D651" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E651" s="22" t="s">
+      <c r="D651" t="s">
+        <v>32</v>
+      </c>
+      <c r="E651" s="16" t="s">
         <v>614</v>
       </c>
-      <c r="F651" s="21"/>
     </row>
     <row r="652" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A652" s="28">
-        <v>6</v>
-      </c>
-      <c r="B652" s="28" t="s">
+      <c r="A652">
+        <v>6</v>
+      </c>
+      <c r="B652" t="s">
         <v>71</v>
       </c>
-      <c r="C652" s="28">
+      <c r="C652">
         <v>38</v>
       </c>
-      <c r="D652" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E652" s="30" t="s">
+      <c r="D652" t="s">
+        <v>32</v>
+      </c>
+      <c r="E652" s="6" t="s">
         <v>615</v>
       </c>
-      <c r="F652" s="21"/>
     </row>
     <row r="653" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A653" s="28">
-        <v>6</v>
-      </c>
-      <c r="B653" s="28" t="s">
+      <c r="A653">
+        <v>6</v>
+      </c>
+      <c r="B653" t="s">
         <v>72</v>
       </c>
-      <c r="C653" s="28">
+      <c r="C653">
         <v>39</v>
       </c>
-      <c r="D653" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E653" s="22" t="s">
+      <c r="D653" t="s">
+        <v>32</v>
+      </c>
+      <c r="E653" s="16" t="s">
         <v>616</v>
       </c>
-      <c r="F653" s="21"/>
     </row>
     <row r="654" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A654" s="28">
-        <v>6</v>
-      </c>
-      <c r="B654" s="28" t="s">
+      <c r="A654">
+        <v>6</v>
+      </c>
+      <c r="B654" t="s">
         <v>73</v>
       </c>
-      <c r="C654" s="28">
+      <c r="C654">
         <v>40</v>
       </c>
-      <c r="D654" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E654" s="23" t="s">
+      <c r="D654" t="s">
+        <v>32</v>
+      </c>
+      <c r="E654" s="18" t="s">
         <v>617</v>
       </c>
-      <c r="F654" s="21"/>
     </row>
     <row r="655" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A655" s="28">
-        <v>6</v>
-      </c>
-      <c r="B655" s="28" t="s">
+      <c r="A655">
+        <v>6</v>
+      </c>
+      <c r="B655" t="s">
         <v>74</v>
       </c>
-      <c r="C655" s="28">
+      <c r="C655">
         <v>41</v>
       </c>
-      <c r="D655" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E655" s="23" t="s">
+      <c r="D655" t="s">
+        <v>32</v>
+      </c>
+      <c r="E655" s="18" t="s">
         <v>618</v>
       </c>
-      <c r="F655" s="21"/>
     </row>
     <row r="656" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A656" s="28">
-        <v>6</v>
-      </c>
-      <c r="B656" s="28" t="s">
+      <c r="A656">
+        <v>6</v>
+      </c>
+      <c r="B656" t="s">
         <v>75</v>
       </c>
-      <c r="C656" s="28">
+      <c r="C656">
         <v>42</v>
       </c>
-      <c r="D656" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E656" s="23" t="s">
+      <c r="D656" t="s">
+        <v>32</v>
+      </c>
+      <c r="E656" s="18" t="s">
         <v>619</v>
       </c>
-      <c r="F656" s="21"/>
     </row>
     <row r="657" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A657" s="28">
-        <v>6</v>
-      </c>
-      <c r="B657" s="28" t="s">
+      <c r="A657">
+        <v>6</v>
+      </c>
+      <c r="B657" t="s">
         <v>76</v>
       </c>
-      <c r="C657" s="28">
+      <c r="C657">
         <v>43</v>
       </c>
-      <c r="D657" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E657" s="23" t="s">
+      <c r="D657" t="s">
+        <v>32</v>
+      </c>
+      <c r="E657" s="18" t="s">
         <v>620</v>
       </c>
-      <c r="F657" s="21"/>
     </row>
     <row r="658" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A658" s="28">
-        <v>6</v>
-      </c>
-      <c r="B658" s="28" t="s">
+      <c r="A658">
+        <v>6</v>
+      </c>
+      <c r="B658" t="s">
         <v>77</v>
       </c>
-      <c r="C658" s="28">
+      <c r="C658">
         <v>44</v>
       </c>
-      <c r="D658" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E658" s="22" t="s">
+      <c r="D658" t="s">
+        <v>32</v>
+      </c>
+      <c r="E658" s="16" t="s">
         <v>621</v>
       </c>
-      <c r="F658" s="21"/>
     </row>
     <row r="659" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A659" s="28">
-        <v>6</v>
-      </c>
-      <c r="B659" s="28" t="s">
+      <c r="A659">
+        <v>6</v>
+      </c>
+      <c r="B659" t="s">
         <v>106</v>
       </c>
-      <c r="C659" s="28">
+      <c r="C659">
         <v>45</v>
       </c>
-      <c r="D659" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E659" s="22" t="s">
+      <c r="D659" t="s">
+        <v>32</v>
+      </c>
+      <c r="E659" s="16" t="s">
         <v>622</v>
       </c>
-      <c r="F659" s="21"/>
     </row>
     <row r="660" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A660" s="28">
-        <v>7</v>
-      </c>
-      <c r="B660" s="28" t="s">
+      <c r="A660">
+        <v>7</v>
+      </c>
+      <c r="B660" t="s">
         <v>31</v>
       </c>
-      <c r="C660" s="28">
+      <c r="C660">
         <v>0</v>
       </c>
-      <c r="D660" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E660" s="29" t="s">
+      <c r="D660" t="s">
+        <v>32</v>
+      </c>
+      <c r="E660" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="F660" s="28"/>
+      <c r="F660"/>
     </row>
     <row r="661" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A661" s="28">
-        <v>7</v>
-      </c>
-      <c r="B661" s="28" t="s">
+      <c r="A661">
+        <v>7</v>
+      </c>
+      <c r="B661" t="s">
         <v>33</v>
       </c>
-      <c r="C661" s="28">
-        <v>2</v>
-      </c>
-      <c r="D661" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="E661" s="29" t="s">
+      <c r="C661">
+        <v>2</v>
+      </c>
+      <c r="D661" t="s">
+        <v>5</v>
+      </c>
+      <c r="E661" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="F661" s="28">
+      <c r="F661">
         <v>4.5</v>
       </c>
     </row>
     <row r="662" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A662" s="28">
-        <v>7</v>
-      </c>
-      <c r="B662" s="28" t="s">
+      <c r="A662">
+        <v>7</v>
+      </c>
+      <c r="B662" t="s">
         <v>33</v>
       </c>
-      <c r="C662" s="28">
-        <v>2</v>
-      </c>
-      <c r="D662" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="E662" s="29" t="s">
+      <c r="C662">
+        <v>2</v>
+      </c>
+      <c r="D662" t="s">
+        <v>6</v>
+      </c>
+      <c r="E662" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="F662" s="28">
+      <c r="F662">
         <v>2</v>
       </c>
     </row>
     <row r="663" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A663" s="28">
-        <v>7</v>
-      </c>
-      <c r="B663" s="28" t="s">
+      <c r="A663">
+        <v>7</v>
+      </c>
+      <c r="B663" t="s">
         <v>33</v>
       </c>
-      <c r="C663" s="28">
-        <v>2</v>
-      </c>
-      <c r="D663" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="E663" s="29" t="s">
+      <c r="C663">
+        <v>2</v>
+      </c>
+      <c r="D663" t="s">
+        <v>7</v>
+      </c>
+      <c r="E663" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="F663" s="28"/>
+      <c r="F663"/>
     </row>
     <row r="664" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A664" s="28">
-        <v>7</v>
-      </c>
-      <c r="B664" s="28" t="s">
+      <c r="A664">
+        <v>7</v>
+      </c>
+      <c r="B664" t="s">
         <v>33</v>
       </c>
-      <c r="C664" s="28">
-        <v>2</v>
-      </c>
-      <c r="D664" s="28" t="s">
+      <c r="C664">
+        <v>2</v>
+      </c>
+      <c r="D664" t="s">
         <v>8</v>
       </c>
-      <c r="E664" s="29" t="s">
+      <c r="E664" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="F664" s="28"/>
+      <c r="F664"/>
     </row>
     <row r="665" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A665" s="28">
-        <v>7</v>
-      </c>
-      <c r="B665" s="28" t="s">
+      <c r="A665">
+        <v>7</v>
+      </c>
+      <c r="B665" t="s">
         <v>33</v>
       </c>
-      <c r="C665" s="28">
-        <v>2</v>
-      </c>
-      <c r="D665" s="28" t="s">
+      <c r="C665">
+        <v>2</v>
+      </c>
+      <c r="D665" t="s">
         <v>9</v>
       </c>
-      <c r="E665" s="29" t="s">
+      <c r="E665" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="F665" s="28"/>
+      <c r="F665"/>
     </row>
     <row r="666" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A666" s="28">
-        <v>7</v>
-      </c>
-      <c r="B666" s="28" t="s">
+      <c r="A666">
+        <v>7</v>
+      </c>
+      <c r="B666" t="s">
         <v>33</v>
       </c>
-      <c r="C666" s="28">
-        <v>2</v>
-      </c>
-      <c r="D666" s="28" t="s">
+      <c r="C666">
+        <v>2</v>
+      </c>
+      <c r="D666" t="s">
         <v>10</v>
       </c>
-      <c r="E666" s="29" t="s">
+      <c r="E666" s="2" t="s">
         <v>629</v>
       </c>
-      <c r="F666" s="28"/>
+      <c r="F666"/>
     </row>
     <row r="667" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A667" s="28">
-        <v>7</v>
-      </c>
-      <c r="B667" s="28" t="s">
+      <c r="A667">
+        <v>7</v>
+      </c>
+      <c r="B667" t="s">
         <v>33</v>
       </c>
-      <c r="C667" s="28">
-        <v>2</v>
-      </c>
-      <c r="D667" s="28" t="s">
+      <c r="C667">
+        <v>2</v>
+      </c>
+      <c r="D667" t="s">
         <v>11</v>
       </c>
-      <c r="E667" s="29">
-        <v>1</v>
-      </c>
-      <c r="F667" s="28">
+      <c r="E667" s="2">
+        <v>1</v>
+      </c>
+      <c r="F667">
         <v>1</v>
       </c>
     </row>
     <row r="668" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A668" s="28">
-        <v>7</v>
-      </c>
-      <c r="B668" s="28" t="s">
+      <c r="A668">
+        <v>7</v>
+      </c>
+      <c r="B668" t="s">
         <v>33</v>
       </c>
-      <c r="C668" s="28">
-        <v>2</v>
-      </c>
-      <c r="D668" s="28" t="s">
+      <c r="C668">
+        <v>2</v>
+      </c>
+      <c r="D668" t="s">
         <v>12</v>
       </c>
-      <c r="E668" s="29" t="s">
+      <c r="E668" s="2" t="s">
         <v>630</v>
       </c>
-      <c r="F668" s="28"/>
+      <c r="F668"/>
     </row>
     <row r="669" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A669" s="28">
-        <v>7</v>
-      </c>
-      <c r="B669" s="28" t="s">
+      <c r="A669">
+        <v>7</v>
+      </c>
+      <c r="B669" t="s">
         <v>34</v>
       </c>
-      <c r="C669" s="28">
-        <v>3</v>
-      </c>
-      <c r="D669" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="E669" s="29" t="s">
+      <c r="C669">
+        <v>3</v>
+      </c>
+      <c r="D669" t="s">
+        <v>5</v>
+      </c>
+      <c r="E669" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="F669" s="28"/>
+      <c r="F669"/>
     </row>
     <row r="670" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A670" s="28">
-        <v>7</v>
-      </c>
-      <c r="B670" s="28" t="s">
+      <c r="A670">
+        <v>7</v>
+      </c>
+      <c r="B670" t="s">
         <v>34</v>
       </c>
-      <c r="C670" s="28">
-        <v>3</v>
-      </c>
-      <c r="D670" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="E670" s="29" t="s">
+      <c r="C670">
+        <v>3</v>
+      </c>
+      <c r="D670" t="s">
+        <v>6</v>
+      </c>
+      <c r="E670" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="F670" s="28"/>
+      <c r="F670"/>
     </row>
     <row r="671" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A671" s="28">
-        <v>7</v>
-      </c>
-      <c r="B671" s="28" t="s">
+      <c r="A671">
+        <v>7</v>
+      </c>
+      <c r="B671" t="s">
         <v>34</v>
       </c>
-      <c r="C671" s="28">
-        <v>3</v>
-      </c>
-      <c r="D671" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="E671" s="29" t="s">
+      <c r="C671">
+        <v>3</v>
+      </c>
+      <c r="D671" t="s">
+        <v>7</v>
+      </c>
+      <c r="E671" s="2" t="s">
         <v>633</v>
       </c>
-      <c r="F671" s="28"/>
+      <c r="F671"/>
     </row>
     <row r="672" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A672" s="28">
-        <v>7</v>
-      </c>
-      <c r="B672" s="28" t="s">
+      <c r="A672">
+        <v>7</v>
+      </c>
+      <c r="B672" t="s">
         <v>34</v>
       </c>
-      <c r="C672" s="28">
-        <v>3</v>
-      </c>
-      <c r="D672" s="28" t="s">
+      <c r="C672">
+        <v>3</v>
+      </c>
+      <c r="D672" t="s">
         <v>8</v>
       </c>
-      <c r="E672" s="29" t="s">
+      <c r="E672" s="2" t="s">
         <v>634</v>
       </c>
-      <c r="F672" s="28"/>
+      <c r="F672"/>
     </row>
     <row r="673" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A673" s="28">
-        <v>7</v>
-      </c>
-      <c r="B673" s="28" t="s">
+      <c r="A673">
+        <v>7</v>
+      </c>
+      <c r="B673" t="s">
         <v>34</v>
       </c>
-      <c r="C673" s="28">
-        <v>3</v>
-      </c>
-      <c r="D673" s="28" t="s">
+      <c r="C673">
+        <v>3</v>
+      </c>
+      <c r="D673" t="s">
         <v>9</v>
       </c>
-      <c r="E673" s="29">
-        <v>3</v>
-      </c>
-      <c r="F673" s="28">
+      <c r="E673" s="2">
+        <v>3</v>
+      </c>
+      <c r="F673">
         <v>3</v>
       </c>
     </row>
     <row r="674" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A674" s="28">
-        <v>7</v>
-      </c>
-      <c r="B674" s="28" t="s">
+      <c r="A674">
+        <v>7</v>
+      </c>
+      <c r="B674" t="s">
         <v>34</v>
       </c>
-      <c r="C674" s="28">
-        <v>3</v>
-      </c>
-      <c r="D674" s="28" t="s">
+      <c r="C674">
+        <v>3</v>
+      </c>
+      <c r="D674" t="s">
         <v>10</v>
       </c>
-      <c r="E674" s="29">
-        <v>1</v>
-      </c>
-      <c r="F674" s="28">
+      <c r="E674" s="2">
+        <v>1</v>
+      </c>
+      <c r="F674">
         <v>1</v>
       </c>
     </row>
     <row r="675" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A675" s="28">
-        <v>7</v>
-      </c>
-      <c r="B675" s="28" t="s">
+      <c r="A675">
+        <v>7</v>
+      </c>
+      <c r="B675" t="s">
         <v>34</v>
       </c>
-      <c r="C675" s="28">
-        <v>3</v>
-      </c>
-      <c r="D675" s="28" t="s">
+      <c r="C675">
+        <v>3</v>
+      </c>
+      <c r="D675" t="s">
         <v>11</v>
       </c>
-      <c r="E675" s="29">
-        <v>1</v>
-      </c>
-      <c r="F675" s="28">
+      <c r="E675" s="2">
+        <v>1</v>
+      </c>
+      <c r="F675">
         <v>1</v>
       </c>
     </row>
     <row r="676" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A676" s="28">
-        <v>7</v>
-      </c>
-      <c r="B676" s="28" t="s">
+      <c r="A676">
+        <v>7</v>
+      </c>
+      <c r="B676" t="s">
         <v>35</v>
       </c>
-      <c r="C676" s="28">
+      <c r="C676">
         <v>4</v>
       </c>
-      <c r="D676" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="E676" s="29" t="s">
+      <c r="D676" t="s">
+        <v>5</v>
+      </c>
+      <c r="E676" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="F676" s="28"/>
+      <c r="F676"/>
     </row>
     <row r="677" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A677" s="28">
-        <v>7</v>
-      </c>
-      <c r="B677" s="28" t="s">
+      <c r="A677">
+        <v>7</v>
+      </c>
+      <c r="B677" t="s">
         <v>35</v>
       </c>
-      <c r="C677" s="28">
+      <c r="C677">
         <v>4</v>
       </c>
-      <c r="D677" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="E677" s="29" t="s">
+      <c r="D677" t="s">
+        <v>6</v>
+      </c>
+      <c r="E677" s="2" t="s">
         <v>636</v>
       </c>
-      <c r="F677" s="28" t="s">
+      <c r="F677" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="678" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A678" s="28">
-        <v>7</v>
-      </c>
-      <c r="B678" s="28" t="s">
+      <c r="A678">
+        <v>7</v>
+      </c>
+      <c r="B678" t="s">
         <v>35</v>
       </c>
-      <c r="C678" s="28">
+      <c r="C678">
         <v>4</v>
       </c>
-      <c r="D678" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="E678" s="29" t="s">
+      <c r="D678" t="s">
+        <v>7</v>
+      </c>
+      <c r="E678" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="F678" s="28"/>
+      <c r="F678"/>
     </row>
     <row r="679" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A679" s="28">
-        <v>7</v>
-      </c>
-      <c r="B679" s="28" t="s">
+      <c r="A679">
+        <v>7</v>
+      </c>
+      <c r="B679" t="s">
         <v>35</v>
       </c>
-      <c r="C679" s="28">
+      <c r="C679">
         <v>4</v>
       </c>
-      <c r="D679" s="28" t="s">
+      <c r="D679" t="s">
         <v>8</v>
       </c>
-      <c r="E679" s="29" t="s">
+      <c r="E679" s="2" t="s">
         <v>638</v>
       </c>
-      <c r="F679" s="28"/>
+      <c r="F679"/>
     </row>
     <row r="680" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A680" s="28">
-        <v>7</v>
-      </c>
-      <c r="B680" s="28" t="s">
+      <c r="A680">
+        <v>7</v>
+      </c>
+      <c r="B680" t="s">
         <v>35</v>
       </c>
-      <c r="C680" s="28">
+      <c r="C680">
         <v>4</v>
       </c>
-      <c r="D680" s="28" t="s">
+      <c r="D680" t="s">
         <v>9</v>
       </c>
-      <c r="E680" s="29">
-        <v>1</v>
-      </c>
-      <c r="F680" s="28">
+      <c r="E680" s="2">
+        <v>1</v>
+      </c>
+      <c r="F680">
         <v>1</v>
       </c>
     </row>
     <row r="681" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A681" s="28">
-        <v>7</v>
-      </c>
-      <c r="B681" s="28" t="s">
+      <c r="A681">
+        <v>7</v>
+      </c>
+      <c r="B681" t="s">
         <v>35</v>
       </c>
-      <c r="C681" s="28">
+      <c r="C681">
         <v>4</v>
       </c>
-      <c r="D681" s="28" t="s">
+      <c r="D681" t="s">
         <v>10</v>
       </c>
-      <c r="E681" s="29" t="s">
+      <c r="E681" s="2" t="s">
         <v>639</v>
       </c>
-      <c r="F681" s="28"/>
+      <c r="F681"/>
     </row>
     <row r="682" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A682" s="28">
-        <v>7</v>
-      </c>
-      <c r="B682" s="28" t="s">
+      <c r="A682">
+        <v>7</v>
+      </c>
+      <c r="B682" t="s">
         <v>35</v>
       </c>
-      <c r="C682" s="28">
+      <c r="C682">
         <v>4</v>
       </c>
-      <c r="D682" s="28" t="s">
+      <c r="D682" t="s">
         <v>11</v>
       </c>
-      <c r="E682" s="29" t="s">
+      <c r="E682" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="F682" s="28"/>
+      <c r="F682"/>
     </row>
     <row r="683" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A683" s="28">
-        <v>7</v>
-      </c>
-      <c r="B683" s="28" t="s">
+      <c r="A683">
+        <v>7</v>
+      </c>
+      <c r="B683" t="s">
         <v>36</v>
       </c>
-      <c r="C683" s="28">
-        <v>5</v>
-      </c>
-      <c r="D683" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="E683" s="29">
-        <v>3</v>
-      </c>
-      <c r="F683" s="28">
+      <c r="C683">
+        <v>5</v>
+      </c>
+      <c r="D683" t="s">
+        <v>5</v>
+      </c>
+      <c r="E683" s="2">
+        <v>3</v>
+      </c>
+      <c r="F683">
         <v>3</v>
       </c>
     </row>
     <row r="684" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A684" s="28">
-        <v>7</v>
-      </c>
-      <c r="B684" s="28" t="s">
+      <c r="A684">
+        <v>7</v>
+      </c>
+      <c r="B684" t="s">
         <v>36</v>
       </c>
-      <c r="C684" s="28">
-        <v>5</v>
-      </c>
-      <c r="D684" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="E684" s="29" t="s">
+      <c r="C684">
+        <v>5</v>
+      </c>
+      <c r="D684" t="s">
+        <v>6</v>
+      </c>
+      <c r="E684" s="2" t="s">
         <v>641</v>
       </c>
-      <c r="F684" s="28" t="s">
+      <c r="F684" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="685" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A685" s="28">
-        <v>7</v>
-      </c>
-      <c r="B685" s="28" t="s">
+      <c r="A685">
+        <v>7</v>
+      </c>
+      <c r="B685" t="s">
         <v>36</v>
       </c>
-      <c r="C685" s="28">
-        <v>5</v>
-      </c>
-      <c r="D685" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="E685" s="29" t="s">
+      <c r="C685">
+        <v>5</v>
+      </c>
+      <c r="D685" t="s">
+        <v>7</v>
+      </c>
+      <c r="E685" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="F685" s="28"/>
+      <c r="F685"/>
     </row>
     <row r="686" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A686" s="28">
-        <v>7</v>
-      </c>
-      <c r="B686" s="28" t="s">
+      <c r="A686">
+        <v>7</v>
+      </c>
+      <c r="B686" t="s">
         <v>36</v>
       </c>
-      <c r="C686" s="28">
-        <v>5</v>
-      </c>
-      <c r="D686" s="28" t="s">
+      <c r="C686">
+        <v>5</v>
+      </c>
+      <c r="D686" t="s">
         <v>8</v>
       </c>
-      <c r="E686" s="29" t="s">
+      <c r="E686" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="F686" s="28"/>
+      <c r="F686"/>
     </row>
     <row r="687" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A687" s="28">
-        <v>7</v>
-      </c>
-      <c r="B687" s="28" t="s">
+      <c r="A687">
+        <v>7</v>
+      </c>
+      <c r="B687" t="s">
         <v>36</v>
       </c>
-      <c r="C687" s="28">
-        <v>5</v>
-      </c>
-      <c r="D687" s="28" t="s">
+      <c r="C687">
+        <v>5</v>
+      </c>
+      <c r="D687" t="s">
         <v>9</v>
       </c>
-      <c r="E687" s="29">
-        <v>3</v>
-      </c>
-      <c r="F687" s="28">
+      <c r="E687" s="2">
+        <v>3</v>
+      </c>
+      <c r="F687">
         <v>3</v>
       </c>
     </row>
     <row r="688" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A688" s="28">
-        <v>7</v>
-      </c>
-      <c r="B688" s="28" t="s">
+      <c r="A688">
+        <v>7</v>
+      </c>
+      <c r="B688" t="s">
         <v>36</v>
       </c>
-      <c r="C688" s="28">
-        <v>5</v>
-      </c>
-      <c r="D688" s="28" t="s">
+      <c r="C688">
+        <v>5</v>
+      </c>
+      <c r="D688" t="s">
         <v>10</v>
       </c>
-      <c r="E688" s="29" t="s">
+      <c r="E688" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="F688" s="28">
+      <c r="F688">
         <v>3</v>
       </c>
     </row>
     <row r="689" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A689" s="28">
-        <v>7</v>
-      </c>
-      <c r="B689" s="28" t="s">
+      <c r="A689">
+        <v>7</v>
+      </c>
+      <c r="B689" t="s">
         <v>36</v>
       </c>
-      <c r="C689" s="28">
-        <v>5</v>
-      </c>
-      <c r="D689" s="28" t="s">
+      <c r="C689">
+        <v>5</v>
+      </c>
+      <c r="D689" t="s">
         <v>11</v>
       </c>
-      <c r="E689" s="29">
-        <v>3</v>
-      </c>
-      <c r="F689" s="28">
+      <c r="E689" s="2">
+        <v>3</v>
+      </c>
+      <c r="F689">
         <v>3</v>
       </c>
     </row>
     <row r="690" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A690" s="28">
-        <v>7</v>
-      </c>
-      <c r="B690" s="28" t="s">
+      <c r="A690">
+        <v>7</v>
+      </c>
+      <c r="B690" t="s">
         <v>37</v>
       </c>
-      <c r="C690" s="28">
-        <v>6</v>
-      </c>
-      <c r="D690" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="E690" s="29"/>
-      <c r="F690" s="28"/>
+      <c r="C690">
+        <v>6</v>
+      </c>
+      <c r="D690" t="s">
+        <v>5</v>
+      </c>
+      <c r="E690" s="2"/>
+      <c r="F690"/>
     </row>
     <row r="691" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A691" s="28">
-        <v>7</v>
-      </c>
-      <c r="B691" s="28" t="s">
+      <c r="A691">
+        <v>7</v>
+      </c>
+      <c r="B691" t="s">
         <v>37</v>
       </c>
-      <c r="C691" s="28">
-        <v>6</v>
-      </c>
-      <c r="D691" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="E691" s="29" t="s">
+      <c r="C691">
+        <v>6</v>
+      </c>
+      <c r="D691" t="s">
+        <v>6</v>
+      </c>
+      <c r="E691" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="F691" s="28">
+      <c r="F691">
         <v>3</v>
       </c>
     </row>
     <row r="692" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A692" s="28">
-        <v>7</v>
-      </c>
-      <c r="B692" s="28" t="s">
+      <c r="A692">
+        <v>7</v>
+      </c>
+      <c r="B692" t="s">
         <v>37</v>
       </c>
-      <c r="C692" s="28">
-        <v>6</v>
-      </c>
-      <c r="D692" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="E692" s="29"/>
-      <c r="F692" s="28"/>
+      <c r="C692">
+        <v>6</v>
+      </c>
+      <c r="D692" t="s">
+        <v>7</v>
+      </c>
+      <c r="E692" s="2"/>
+      <c r="F692"/>
     </row>
     <row r="693" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A693" s="28">
-        <v>7</v>
-      </c>
-      <c r="B693" s="28" t="s">
+      <c r="A693">
+        <v>7</v>
+      </c>
+      <c r="B693" t="s">
         <v>37</v>
       </c>
-      <c r="C693" s="28">
-        <v>6</v>
-      </c>
-      <c r="D693" s="28" t="s">
+      <c r="C693">
+        <v>6</v>
+      </c>
+      <c r="D693" t="s">
         <v>8</v>
       </c>
-      <c r="E693" s="29"/>
-      <c r="F693" s="28"/>
+      <c r="E693" s="2"/>
+      <c r="F693"/>
     </row>
     <row r="694" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A694" s="28">
-        <v>7</v>
-      </c>
-      <c r="B694" s="28" t="s">
+      <c r="A694">
+        <v>7</v>
+      </c>
+      <c r="B694" t="s">
         <v>37</v>
       </c>
-      <c r="C694" s="28">
-        <v>6</v>
-      </c>
-      <c r="D694" s="28" t="s">
+      <c r="C694">
+        <v>6</v>
+      </c>
+      <c r="D694" t="s">
         <v>9</v>
       </c>
-      <c r="E694" s="29"/>
-      <c r="F694" s="28"/>
+      <c r="E694" s="2"/>
+      <c r="F694"/>
     </row>
     <row r="695" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A695" s="28">
-        <v>7</v>
-      </c>
-      <c r="B695" s="28" t="s">
+      <c r="A695">
+        <v>7</v>
+      </c>
+      <c r="B695" t="s">
         <v>37</v>
       </c>
-      <c r="C695" s="28">
-        <v>6</v>
-      </c>
-      <c r="D695" s="28" t="s">
+      <c r="C695">
+        <v>6</v>
+      </c>
+      <c r="D695" t="s">
         <v>10</v>
       </c>
-      <c r="E695" s="29"/>
-      <c r="F695" s="28"/>
+      <c r="E695" s="2"/>
+      <c r="F695"/>
     </row>
     <row r="696" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A696" s="28">
-        <v>7</v>
-      </c>
-      <c r="B696" s="28" t="s">
+      <c r="A696">
+        <v>7</v>
+      </c>
+      <c r="B696" t="s">
         <v>37</v>
       </c>
-      <c r="C696" s="28">
-        <v>6</v>
-      </c>
-      <c r="D696" s="28" t="s">
+      <c r="C696">
+        <v>6</v>
+      </c>
+      <c r="D696" t="s">
         <v>11</v>
       </c>
-      <c r="E696" s="29"/>
-      <c r="F696" s="28"/>
+      <c r="E696" s="2"/>
+      <c r="F696"/>
     </row>
     <row r="697" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A697" s="28">
-        <v>7</v>
-      </c>
-      <c r="B697" s="28" t="s">
+      <c r="A697">
+        <v>7</v>
+      </c>
+      <c r="B697" t="s">
         <v>38</v>
       </c>
-      <c r="C697" s="28">
-        <v>7</v>
-      </c>
-      <c r="D697" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="E697" s="29"/>
-      <c r="F697" s="28"/>
+      <c r="C697">
+        <v>7</v>
+      </c>
+      <c r="D697" t="s">
+        <v>5</v>
+      </c>
+      <c r="E697" s="2"/>
+      <c r="F697"/>
     </row>
     <row r="698" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A698" s="28">
-        <v>7</v>
-      </c>
-      <c r="B698" s="28" t="s">
+      <c r="A698">
+        <v>7</v>
+      </c>
+      <c r="B698" t="s">
         <v>38</v>
       </c>
-      <c r="C698" s="28">
-        <v>7</v>
-      </c>
-      <c r="D698" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="E698" s="29"/>
-      <c r="F698" s="28"/>
+      <c r="C698">
+        <v>7</v>
+      </c>
+      <c r="D698" t="s">
+        <v>6</v>
+      </c>
+      <c r="E698" s="2"/>
+      <c r="F698"/>
     </row>
     <row r="699" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A699" s="28">
-        <v>7</v>
-      </c>
-      <c r="B699" s="28" t="s">
+      <c r="A699">
+        <v>7</v>
+      </c>
+      <c r="B699" t="s">
         <v>38</v>
       </c>
-      <c r="C699" s="28">
-        <v>7</v>
-      </c>
-      <c r="D699" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="E699" s="29"/>
-      <c r="F699" s="28"/>
+      <c r="C699">
+        <v>7</v>
+      </c>
+      <c r="D699" t="s">
+        <v>7</v>
+      </c>
+      <c r="E699" s="2"/>
+      <c r="F699"/>
     </row>
     <row r="700" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A700" s="28">
-        <v>7</v>
-      </c>
-      <c r="B700" s="28" t="s">
+      <c r="A700">
+        <v>7</v>
+      </c>
+      <c r="B700" t="s">
         <v>38</v>
       </c>
-      <c r="C700" s="28">
-        <v>7</v>
-      </c>
-      <c r="D700" s="28" t="s">
+      <c r="C700">
+        <v>7</v>
+      </c>
+      <c r="D700" t="s">
         <v>8</v>
       </c>
-      <c r="E700" s="29"/>
-      <c r="F700" s="28"/>
+      <c r="E700" s="2"/>
+      <c r="F700"/>
     </row>
     <row r="701" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A701" s="28">
-        <v>7</v>
-      </c>
-      <c r="B701" s="28" t="s">
+      <c r="A701">
+        <v>7</v>
+      </c>
+      <c r="B701" t="s">
         <v>38</v>
       </c>
-      <c r="C701" s="28">
-        <v>7</v>
-      </c>
-      <c r="D701" s="28" t="s">
+      <c r="C701">
+        <v>7</v>
+      </c>
+      <c r="D701" t="s">
         <v>9</v>
       </c>
-      <c r="E701" s="29"/>
-      <c r="F701" s="28"/>
+      <c r="E701" s="2"/>
+      <c r="F701"/>
     </row>
     <row r="702" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A702" s="28">
-        <v>7</v>
-      </c>
-      <c r="B702" s="28" t="s">
+      <c r="A702">
+        <v>7</v>
+      </c>
+      <c r="B702" t="s">
         <v>38</v>
       </c>
-      <c r="C702" s="28">
-        <v>7</v>
-      </c>
-      <c r="D702" s="28" t="s">
+      <c r="C702">
+        <v>7</v>
+      </c>
+      <c r="D702" t="s">
         <v>10</v>
       </c>
-      <c r="E702" s="29"/>
-      <c r="F702" s="28"/>
+      <c r="E702" s="2"/>
+      <c r="F702"/>
     </row>
     <row r="703" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A703" s="28">
-        <v>7</v>
-      </c>
-      <c r="B703" s="28" t="s">
+      <c r="A703">
+        <v>7</v>
+      </c>
+      <c r="B703" t="s">
         <v>38</v>
       </c>
-      <c r="C703" s="28">
-        <v>7</v>
-      </c>
-      <c r="D703" s="28" t="s">
+      <c r="C703">
+        <v>7</v>
+      </c>
+      <c r="D703" t="s">
         <v>11</v>
       </c>
-      <c r="E703" s="29"/>
-      <c r="F703" s="28"/>
+      <c r="E703" s="2"/>
+      <c r="F703"/>
     </row>
     <row r="704" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A704" s="28">
-        <v>7</v>
-      </c>
-      <c r="B704" s="28" t="s">
+      <c r="A704">
+        <v>7</v>
+      </c>
+      <c r="B704" t="s">
         <v>38</v>
       </c>
-      <c r="C704" s="28">
-        <v>7</v>
-      </c>
-      <c r="D704" s="28" t="s">
+      <c r="C704">
+        <v>7</v>
+      </c>
+      <c r="D704" t="s">
         <v>98</v>
       </c>
-      <c r="E704" s="29" t="s">
+      <c r="E704" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="F704" s="28">
+      <c r="F704">
         <v>3.5</v>
       </c>
     </row>
     <row r="705" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A705" s="28">
-        <v>7</v>
-      </c>
-      <c r="B705" s="28" t="s">
+      <c r="A705">
+        <v>7</v>
+      </c>
+      <c r="B705" t="s">
         <v>39</v>
       </c>
-      <c r="C705" s="28">
+      <c r="C705">
         <v>8</v>
       </c>
-      <c r="D705" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E705" s="29" t="s">
+      <c r="D705" t="s">
+        <v>32</v>
+      </c>
+      <c r="E705" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="F705" s="28">
+      <c r="F705">
         <v>2</v>
       </c>
     </row>
     <row r="706" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A706" s="28">
-        <v>7</v>
-      </c>
-      <c r="B706" s="28" t="s">
+      <c r="A706">
+        <v>7</v>
+      </c>
+      <c r="B706" t="s">
         <v>40</v>
       </c>
-      <c r="C706" s="28">
+      <c r="C706">
         <v>9</v>
       </c>
-      <c r="D706" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="E706" s="29" t="s">
+      <c r="D706" t="s">
+        <v>5</v>
+      </c>
+      <c r="E706" s="2" t="s">
         <v>648</v>
       </c>
-      <c r="F706" s="28">
+      <c r="F706">
         <v>2</v>
       </c>
     </row>
     <row r="707" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A707" s="28">
-        <v>7</v>
-      </c>
-      <c r="B707" s="28" t="s">
+      <c r="A707">
+        <v>7</v>
+      </c>
+      <c r="B707" t="s">
         <v>40</v>
       </c>
-      <c r="C707" s="28">
+      <c r="C707">
         <v>9</v>
       </c>
-      <c r="D707" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="E707" s="29">
+      <c r="D707" t="s">
+        <v>6</v>
+      </c>
+      <c r="E707" s="2">
         <v>0</v>
       </c>
-      <c r="F707" s="28">
+      <c r="F707">
         <v>0</v>
       </c>
     </row>
     <row r="708" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A708" s="28">
-        <v>7</v>
-      </c>
-      <c r="B708" s="28" t="s">
+      <c r="A708">
+        <v>7</v>
+      </c>
+      <c r="B708" t="s">
         <v>40</v>
       </c>
-      <c r="C708" s="28">
+      <c r="C708">
         <v>9</v>
       </c>
-      <c r="D708" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="E708" s="29" t="s">
+      <c r="D708" t="s">
+        <v>7</v>
+      </c>
+      <c r="E708" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="F708" s="28"/>
+      <c r="F708"/>
     </row>
     <row r="709" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A709" s="28">
-        <v>7</v>
-      </c>
-      <c r="B709" s="28" t="s">
+      <c r="A709">
+        <v>7</v>
+      </c>
+      <c r="B709" t="s">
         <v>40</v>
       </c>
-      <c r="C709" s="28">
+      <c r="C709">
         <v>9</v>
       </c>
-      <c r="D709" s="28" t="s">
+      <c r="D709" t="s">
         <v>8</v>
       </c>
-      <c r="E709" s="29">
+      <c r="E709" s="2">
         <v>0</v>
       </c>
-      <c r="F709" s="28">
+      <c r="F709">
         <v>0</v>
       </c>
     </row>
     <row r="710" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A710" s="28">
-        <v>7</v>
-      </c>
-      <c r="B710" s="28" t="s">
+      <c r="A710">
+        <v>7</v>
+      </c>
+      <c r="B710" t="s">
         <v>40</v>
       </c>
-      <c r="C710" s="28">
+      <c r="C710">
         <v>9</v>
       </c>
-      <c r="D710" s="28" t="s">
+      <c r="D710" t="s">
         <v>9</v>
       </c>
-      <c r="E710" s="29">
+      <c r="E710" s="2">
         <v>0</v>
       </c>
-      <c r="F710" s="28">
+      <c r="F710">
         <v>0</v>
       </c>
     </row>
     <row r="711" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A711" s="28">
-        <v>7</v>
-      </c>
-      <c r="B711" s="28" t="s">
+      <c r="A711">
+        <v>7</v>
+      </c>
+      <c r="B711" t="s">
         <v>40</v>
       </c>
-      <c r="C711" s="28">
+      <c r="C711">
         <v>9</v>
       </c>
-      <c r="D711" s="28" t="s">
+      <c r="D711" t="s">
         <v>10</v>
       </c>
-      <c r="E711" s="29">
-        <v>2</v>
-      </c>
-      <c r="F711" s="28">
+      <c r="E711" s="2">
+        <v>2</v>
+      </c>
+      <c r="F711">
         <v>2</v>
       </c>
     </row>
     <row r="712" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A712" s="28">
-        <v>7</v>
-      </c>
-      <c r="B712" s="28" t="s">
+      <c r="A712">
+        <v>7</v>
+      </c>
+      <c r="B712" t="s">
         <v>40</v>
       </c>
-      <c r="C712" s="28">
+      <c r="C712">
         <v>9</v>
       </c>
-      <c r="D712" s="28" t="s">
+      <c r="D712" t="s">
         <v>11</v>
       </c>
-      <c r="E712" s="29">
-        <v>2</v>
-      </c>
-      <c r="F712" s="28">
+      <c r="E712" s="2">
+        <v>2</v>
+      </c>
+      <c r="F712">
         <v>2</v>
       </c>
     </row>
     <row r="713" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A713" s="28">
-        <v>7</v>
-      </c>
-      <c r="B713" s="28" t="s">
+      <c r="A713">
+        <v>7</v>
+      </c>
+      <c r="B713" t="s">
         <v>41</v>
       </c>
-      <c r="C713" s="28">
+      <c r="C713">
         <v>10</v>
       </c>
-      <c r="D713" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="E713" s="29">
+      <c r="D713" t="s">
+        <v>5</v>
+      </c>
+      <c r="E713" s="2">
         <v>0</v>
       </c>
-      <c r="F713" s="28">
+      <c r="F713">
         <v>0</v>
       </c>
     </row>
     <row r="714" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A714" s="28">
-        <v>7</v>
-      </c>
-      <c r="B714" s="28" t="s">
+      <c r="A714">
+        <v>7</v>
+      </c>
+      <c r="B714" t="s">
         <v>41</v>
       </c>
-      <c r="C714" s="28">
+      <c r="C714">
         <v>10</v>
       </c>
-      <c r="D714" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="E714" s="29">
+      <c r="D714" t="s">
+        <v>6</v>
+      </c>
+      <c r="E714" s="2">
         <v>0</v>
       </c>
-      <c r="F714" s="28">
+      <c r="F714">
         <v>0</v>
       </c>
     </row>
     <row r="715" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A715" s="28">
-        <v>7</v>
-      </c>
-      <c r="B715" s="28" t="s">
+      <c r="A715">
+        <v>7</v>
+      </c>
+      <c r="B715" t="s">
         <v>41</v>
       </c>
-      <c r="C715" s="28">
+      <c r="C715">
         <v>10</v>
       </c>
-      <c r="D715" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="E715" s="29" t="s">
+      <c r="D715" t="s">
+        <v>7</v>
+      </c>
+      <c r="E715" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="F715" s="28"/>
+      <c r="F715"/>
     </row>
     <row r="716" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A716" s="28">
-        <v>7</v>
-      </c>
-      <c r="B716" s="28" t="s">
+      <c r="A716">
+        <v>7</v>
+      </c>
+      <c r="B716" t="s">
         <v>41</v>
       </c>
-      <c r="C716" s="28">
+      <c r="C716">
         <v>10</v>
       </c>
-      <c r="D716" s="28" t="s">
+      <c r="D716" t="s">
         <v>8</v>
       </c>
-      <c r="E716" s="29" t="s">
+      <c r="E716" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="F716" s="28">
+      <c r="F716">
         <v>1</v>
       </c>
     </row>
     <row r="717" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A717" s="28">
-        <v>7</v>
-      </c>
-      <c r="B717" s="28" t="s">
+      <c r="A717">
+        <v>7</v>
+      </c>
+      <c r="B717" t="s">
         <v>41</v>
       </c>
-      <c r="C717" s="28">
+      <c r="C717">
         <v>10</v>
       </c>
-      <c r="D717" s="28" t="s">
+      <c r="D717" t="s">
         <v>9</v>
       </c>
-      <c r="E717" s="29" t="s">
+      <c r="E717" s="2" t="s">
         <v>651</v>
       </c>
-      <c r="F717" s="28">
+      <c r="F717">
         <v>0</v>
       </c>
     </row>
     <row r="718" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A718" s="28">
-        <v>7</v>
-      </c>
-      <c r="B718" s="28" t="s">
+      <c r="A718">
+        <v>7</v>
+      </c>
+      <c r="B718" t="s">
         <v>41</v>
       </c>
-      <c r="C718" s="28">
+      <c r="C718">
         <v>10</v>
       </c>
-      <c r="D718" s="28" t="s">
+      <c r="D718" t="s">
         <v>10</v>
       </c>
-      <c r="E718" s="29" t="s">
+      <c r="E718" s="2" t="s">
         <v>652</v>
       </c>
-      <c r="F718" s="28">
+      <c r="F718">
         <v>1</v>
       </c>
     </row>
     <row r="719" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A719" s="28">
-        <v>7</v>
-      </c>
-      <c r="B719" s="28" t="s">
+      <c r="A719">
+        <v>7</v>
+      </c>
+      <c r="B719" t="s">
         <v>41</v>
       </c>
-      <c r="C719" s="28">
+      <c r="C719">
         <v>10</v>
       </c>
-      <c r="D719" s="28" t="s">
+      <c r="D719" t="s">
         <v>11</v>
       </c>
-      <c r="E719" s="29" t="s">
+      <c r="E719" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="F719" s="28">
+      <c r="F719">
         <v>2</v>
       </c>
     </row>
     <row r="720" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A720" s="28">
-        <v>7</v>
-      </c>
-      <c r="B720" s="28" t="s">
+      <c r="A720">
+        <v>7</v>
+      </c>
+      <c r="B720" t="s">
         <v>42</v>
       </c>
-      <c r="C720" s="28">
+      <c r="C720">
         <v>11</v>
       </c>
-      <c r="D720" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E720" s="29" t="s">
+      <c r="D720" t="s">
+        <v>32</v>
+      </c>
+      <c r="E720" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="F720" s="28"/>
+      <c r="F720"/>
     </row>
     <row r="721" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A721" s="28">
-        <v>7</v>
-      </c>
-      <c r="B721" s="28" t="s">
+      <c r="A721">
+        <v>7</v>
+      </c>
+      <c r="B721" t="s">
         <v>43</v>
       </c>
-      <c r="C721" s="28">
+      <c r="C721">
         <v>12</v>
       </c>
-      <c r="D721" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E721" s="29" t="s">
+      <c r="D721" t="s">
+        <v>32</v>
+      </c>
+      <c r="E721" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="F721" s="28"/>
+      <c r="F721"/>
     </row>
     <row r="722" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A722" s="28">
-        <v>7</v>
-      </c>
-      <c r="B722" s="28" t="s">
+      <c r="A722">
+        <v>7</v>
+      </c>
+      <c r="B722" t="s">
         <v>44</v>
       </c>
-      <c r="C722" s="28">
+      <c r="C722">
         <v>13</v>
       </c>
-      <c r="D722" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="E722" s="29" t="s">
+      <c r="D722" t="s">
+        <v>5</v>
+      </c>
+      <c r="E722" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="F722" s="28">
+      <c r="F722">
         <v>2</v>
       </c>
     </row>
     <row r="723" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A723" s="28">
-        <v>7</v>
-      </c>
-      <c r="B723" s="28" t="s">
+      <c r="A723">
+        <v>7</v>
+      </c>
+      <c r="B723" t="s">
         <v>44</v>
       </c>
-      <c r="C723" s="28">
+      <c r="C723">
         <v>13</v>
       </c>
-      <c r="D723" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="E723" s="29" t="s">
+      <c r="D723" t="s">
+        <v>6</v>
+      </c>
+      <c r="E723" s="2" t="s">
         <v>657</v>
       </c>
-      <c r="F723" s="28">
+      <c r="F723">
         <v>1</v>
       </c>
     </row>
     <row r="724" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A724" s="28">
-        <v>7</v>
-      </c>
-      <c r="B724" s="28" t="s">
+      <c r="A724">
+        <v>7</v>
+      </c>
+      <c r="B724" t="s">
         <v>44</v>
       </c>
-      <c r="C724" s="28">
+      <c r="C724">
         <v>13</v>
       </c>
-      <c r="D724" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="E724" s="29" t="s">
+      <c r="D724" t="s">
+        <v>7</v>
+      </c>
+      <c r="E724" s="2" t="s">
         <v>658</v>
       </c>
-      <c r="F724" s="28"/>
+      <c r="F724"/>
     </row>
     <row r="725" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A725" s="28">
-        <v>7</v>
-      </c>
-      <c r="B725" s="28" t="s">
+      <c r="A725">
+        <v>7</v>
+      </c>
+      <c r="B725" t="s">
         <v>44</v>
       </c>
-      <c r="C725" s="28">
+      <c r="C725">
         <v>13</v>
       </c>
-      <c r="D725" s="28" t="s">
+      <c r="D725" t="s">
         <v>8</v>
       </c>
-      <c r="E725" s="29"/>
-      <c r="F725" s="28"/>
+      <c r="E725" s="2"/>
+      <c r="F725"/>
     </row>
     <row r="726" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A726" s="28">
-        <v>7</v>
-      </c>
-      <c r="B726" s="28" t="s">
+      <c r="A726">
+        <v>7</v>
+      </c>
+      <c r="B726" t="s">
         <v>44</v>
       </c>
-      <c r="C726" s="28">
+      <c r="C726">
         <v>13</v>
       </c>
-      <c r="D726" s="28" t="s">
+      <c r="D726" t="s">
         <v>9</v>
       </c>
-      <c r="E726" s="29">
+      <c r="E726" s="2">
         <v>0</v>
       </c>
-      <c r="F726" s="28">
+      <c r="F726">
         <v>0</v>
       </c>
     </row>
     <row r="727" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A727" s="28">
-        <v>7</v>
-      </c>
-      <c r="B727" s="28" t="s">
+      <c r="A727">
+        <v>7</v>
+      </c>
+      <c r="B727" t="s">
         <v>44</v>
       </c>
-      <c r="C727" s="28">
+      <c r="C727">
         <v>13</v>
       </c>
-      <c r="D727" s="28" t="s">
+      <c r="D727" t="s">
         <v>10</v>
       </c>
-      <c r="E727" s="29" t="s">
+      <c r="E727" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="F727" s="28"/>
+      <c r="F727"/>
     </row>
     <row r="728" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A728" s="28">
-        <v>7</v>
-      </c>
-      <c r="B728" s="28" t="s">
+      <c r="A728">
+        <v>7</v>
+      </c>
+      <c r="B728" t="s">
         <v>44</v>
       </c>
-      <c r="C728" s="28">
+      <c r="C728">
         <v>13</v>
       </c>
-      <c r="D728" s="28" t="s">
+      <c r="D728" t="s">
         <v>11</v>
       </c>
-      <c r="E728" s="29" t="s">
+      <c r="E728" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="F728" s="28">
+      <c r="F728">
         <v>2</v>
       </c>
     </row>
     <row r="729" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A729" s="28">
-        <v>7</v>
-      </c>
-      <c r="B729" s="28" t="s">
+      <c r="A729">
+        <v>7</v>
+      </c>
+      <c r="B729" t="s">
         <v>45</v>
       </c>
-      <c r="C729" s="28">
+      <c r="C729">
         <v>14</v>
       </c>
-      <c r="D729" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E729" s="29" t="s">
+      <c r="D729" t="s">
+        <v>32</v>
+      </c>
+      <c r="E729" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="F729" s="28">
+      <c r="F729">
         <v>2</v>
       </c>
     </row>
     <row r="730" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A730" s="28">
-        <v>7</v>
-      </c>
-      <c r="B730" s="28" t="s">
+      <c r="A730">
+        <v>7</v>
+      </c>
+      <c r="B730" t="s">
         <v>46</v>
       </c>
-      <c r="C730" s="28">
+      <c r="C730">
         <v>15</v>
       </c>
-      <c r="D730" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="E730" s="29" t="s">
+      <c r="D730" t="s">
+        <v>5</v>
+      </c>
+      <c r="E730" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="F730" s="28">
+      <c r="F730">
         <v>1</v>
       </c>
     </row>
     <row r="731" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A731" s="28">
-        <v>7</v>
-      </c>
-      <c r="B731" s="28" t="s">
+      <c r="A731">
+        <v>7</v>
+      </c>
+      <c r="B731" t="s">
         <v>46</v>
       </c>
-      <c r="C731" s="28">
+      <c r="C731">
         <v>15</v>
       </c>
-      <c r="D731" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="E731" s="29" t="s">
+      <c r="D731" t="s">
+        <v>6</v>
+      </c>
+      <c r="E731" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="F731" s="28">
+      <c r="F731">
         <v>2</v>
       </c>
     </row>
     <row r="732" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A732" s="28">
-        <v>7</v>
-      </c>
-      <c r="B732" s="28" t="s">
+      <c r="A732">
+        <v>7</v>
+      </c>
+      <c r="B732" t="s">
         <v>46</v>
       </c>
-      <c r="C732" s="28">
+      <c r="C732">
         <v>15</v>
       </c>
-      <c r="D732" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="E732" s="29" t="s">
+      <c r="D732" t="s">
+        <v>7</v>
+      </c>
+      <c r="E732" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="F732" s="28"/>
+      <c r="F732"/>
     </row>
     <row r="733" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A733" s="28">
-        <v>7</v>
-      </c>
-      <c r="B733" s="28" t="s">
+      <c r="A733">
+        <v>7</v>
+      </c>
+      <c r="B733" t="s">
         <v>46</v>
       </c>
-      <c r="C733" s="28">
+      <c r="C733">
         <v>15</v>
       </c>
-      <c r="D733" s="28" t="s">
+      <c r="D733" t="s">
         <v>8</v>
       </c>
-      <c r="E733" s="29"/>
-      <c r="F733" s="28"/>
+      <c r="E733" s="2"/>
+      <c r="F733"/>
     </row>
     <row r="734" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A734" s="28">
-        <v>7</v>
-      </c>
-      <c r="B734" s="28" t="s">
+      <c r="A734">
+        <v>7</v>
+      </c>
+      <c r="B734" t="s">
         <v>46</v>
       </c>
-      <c r="C734" s="28">
+      <c r="C734">
         <v>15</v>
       </c>
-      <c r="D734" s="28" t="s">
+      <c r="D734" t="s">
         <v>9</v>
       </c>
-      <c r="E734" s="29" t="s">
+      <c r="E734" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="F734" s="28">
+      <c r="F734">
         <v>1</v>
       </c>
     </row>
     <row r="735" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A735" s="28">
-        <v>7</v>
-      </c>
-      <c r="B735" s="28" t="s">
+      <c r="A735">
+        <v>7</v>
+      </c>
+      <c r="B735" t="s">
         <v>46</v>
       </c>
-      <c r="C735" s="28">
+      <c r="C735">
         <v>15</v>
       </c>
-      <c r="D735" s="28" t="s">
+      <c r="D735" t="s">
         <v>10</v>
       </c>
-      <c r="E735" s="29" t="s">
+      <c r="E735" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="F735" s="28">
+      <c r="F735">
         <v>4</v>
       </c>
     </row>
     <row r="736" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A736" s="28">
-        <v>7</v>
-      </c>
-      <c r="B736" s="28" t="s">
+      <c r="A736">
+        <v>7</v>
+      </c>
+      <c r="B736" t="s">
         <v>46</v>
       </c>
-      <c r="C736" s="28">
+      <c r="C736">
         <v>15</v>
       </c>
-      <c r="D736" s="28" t="s">
+      <c r="D736" t="s">
         <v>11</v>
       </c>
-      <c r="E736" s="29" t="s">
+      <c r="E736" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="F736" s="28"/>
+      <c r="F736"/>
     </row>
     <row r="737" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A737" s="28">
-        <v>7</v>
-      </c>
-      <c r="B737" s="28" t="s">
+      <c r="A737">
+        <v>7</v>
+      </c>
+      <c r="B737" t="s">
         <v>47</v>
       </c>
-      <c r="C737" s="28">
+      <c r="C737">
         <v>16</v>
       </c>
-      <c r="D737" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E737" s="29" t="s">
+      <c r="D737" t="s">
+        <v>32</v>
+      </c>
+      <c r="E737" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="F737" s="28" t="s">
+      <c r="F737" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="738" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A738" s="28">
-        <v>7</v>
-      </c>
-      <c r="B738" s="28" t="s">
+      <c r="A738">
+        <v>7</v>
+      </c>
+      <c r="B738" t="s">
         <v>48</v>
       </c>
-      <c r="C738" s="28">
+      <c r="C738">
         <v>17</v>
       </c>
-      <c r="D738" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E738" s="29" t="s">
+      <c r="D738" t="s">
+        <v>32</v>
+      </c>
+      <c r="E738" s="2" t="s">
         <v>669</v>
       </c>
-      <c r="F738" s="28">
+      <c r="F738">
         <v>0</v>
       </c>
     </row>
     <row r="739" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A739" s="28">
-        <v>7</v>
-      </c>
-      <c r="B739" s="28" t="s">
+      <c r="A739">
+        <v>7</v>
+      </c>
+      <c r="B739" t="s">
         <v>49</v>
       </c>
-      <c r="C739" s="28">
+      <c r="C739">
         <v>18</v>
       </c>
-      <c r="D739" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E739" s="29" t="s">
+      <c r="D739" t="s">
+        <v>32</v>
+      </c>
+      <c r="E739" s="2" t="s">
         <v>670</v>
       </c>
-      <c r="F739" s="28">
+      <c r="F739">
         <v>1</v>
       </c>
     </row>
     <row r="740" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A740" s="28">
-        <v>7</v>
-      </c>
-      <c r="B740" s="28" t="s">
+      <c r="A740">
+        <v>7</v>
+      </c>
+      <c r="B740" t="s">
         <v>50</v>
       </c>
-      <c r="C740" s="28">
+      <c r="C740">
         <v>19</v>
       </c>
-      <c r="D740" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E740" s="29" t="s">
+      <c r="D740" t="s">
+        <v>32</v>
+      </c>
+      <c r="E740" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="F740" s="28"/>
+      <c r="F740"/>
     </row>
     <row r="741" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A741" s="28">
-        <v>7</v>
-      </c>
-      <c r="B741" s="28" t="s">
+      <c r="A741">
+        <v>7</v>
+      </c>
+      <c r="B741" t="s">
         <v>51</v>
       </c>
-      <c r="C741" s="28">
+      <c r="C741">
         <v>20</v>
       </c>
-      <c r="D741" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E741" s="29" t="s">
+      <c r="D741" t="s">
+        <v>32</v>
+      </c>
+      <c r="E741" s="2" t="s">
         <v>672</v>
       </c>
-      <c r="F741" s="28">
+      <c r="F741">
         <v>3</v>
       </c>
     </row>
     <row r="742" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A742" s="28">
-        <v>7</v>
-      </c>
-      <c r="B742" s="28" t="s">
+      <c r="A742">
+        <v>7</v>
+      </c>
+      <c r="B742" t="s">
         <v>52</v>
       </c>
-      <c r="C742" s="28">
+      <c r="C742">
         <v>21</v>
       </c>
-      <c r="D742" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="E742" s="29" t="s">
+      <c r="D742" t="s">
+        <v>5</v>
+      </c>
+      <c r="E742" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="F742" s="28">
+      <c r="F742">
         <v>1</v>
       </c>
     </row>
     <row r="743" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A743" s="28">
-        <v>7</v>
-      </c>
-      <c r="B743" s="28" t="s">
+      <c r="A743">
+        <v>7</v>
+      </c>
+      <c r="B743" t="s">
         <v>53</v>
       </c>
-      <c r="C743" s="28">
+      <c r="C743">
         <v>21</v>
       </c>
-      <c r="D743" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="E743" s="29" t="s">
+      <c r="D743" t="s">
+        <v>6</v>
+      </c>
+      <c r="E743" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="F743" s="28">
+      <c r="F743">
         <v>4</v>
       </c>
     </row>
     <row r="744" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A744" s="28">
-        <v>7</v>
-      </c>
-      <c r="B744" s="28" t="s">
+      <c r="A744">
+        <v>7</v>
+      </c>
+      <c r="B744" t="s">
         <v>54</v>
       </c>
-      <c r="C744" s="28">
+      <c r="C744">
         <v>21</v>
       </c>
-      <c r="D744" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="E744" s="29" t="s">
+      <c r="D744" t="s">
+        <v>7</v>
+      </c>
+      <c r="E744" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="F744" s="28">
+      <c r="F744">
         <v>1</v>
       </c>
     </row>
     <row r="745" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A745" s="28">
-        <v>7</v>
-      </c>
-      <c r="B745" s="28" t="s">
+      <c r="A745">
+        <v>7</v>
+      </c>
+      <c r="B745" t="s">
         <v>55</v>
       </c>
-      <c r="C745" s="28">
+      <c r="C745">
         <v>22</v>
       </c>
-      <c r="D745" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E745" s="29" t="s">
+      <c r="D745" t="s">
+        <v>32</v>
+      </c>
+      <c r="E745" s="2" t="s">
         <v>676</v>
       </c>
-      <c r="F745" s="28">
+      <c r="F745">
         <v>1</v>
       </c>
     </row>
     <row r="746" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A746" s="28">
-        <v>7</v>
-      </c>
-      <c r="B746" s="28" t="s">
+      <c r="A746">
+        <v>7</v>
+      </c>
+      <c r="B746" t="s">
         <v>56</v>
       </c>
-      <c r="C746" s="28">
+      <c r="C746">
         <v>23</v>
       </c>
-      <c r="D746" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E746" s="29" t="s">
+      <c r="D746" t="s">
+        <v>32</v>
+      </c>
+      <c r="E746" s="2" t="s">
         <v>677</v>
       </c>
-      <c r="F746" s="28">
+      <c r="F746">
         <v>3</v>
       </c>
     </row>
     <row r="747" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A747" s="28">
-        <v>7</v>
-      </c>
-      <c r="B747" s="28" t="s">
+      <c r="A747">
+        <v>7</v>
+      </c>
+      <c r="B747" t="s">
         <v>57</v>
       </c>
-      <c r="C747" s="28">
+      <c r="C747">
         <v>24</v>
       </c>
-      <c r="D747" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E747" s="29" t="s">
+      <c r="D747" t="s">
+        <v>32</v>
+      </c>
+      <c r="E747" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="F747" s="28">
+      <c r="F747">
         <v>4</v>
       </c>
     </row>
     <row r="748" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A748" s="28">
-        <v>7</v>
-      </c>
-      <c r="B748" s="28" t="s">
+      <c r="A748">
+        <v>7</v>
+      </c>
+      <c r="B748" t="s">
         <v>58</v>
       </c>
-      <c r="C748" s="28">
+      <c r="C748">
         <v>25</v>
       </c>
-      <c r="D748" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E748" s="29" t="s">
+      <c r="D748" t="s">
+        <v>32</v>
+      </c>
+      <c r="E748" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="F748" s="28"/>
+      <c r="F748"/>
     </row>
     <row r="749" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A749" s="28">
-        <v>7</v>
-      </c>
-      <c r="B749" s="28" t="s">
+      <c r="A749">
+        <v>7</v>
+      </c>
+      <c r="B749" t="s">
         <v>59</v>
       </c>
-      <c r="C749" s="28">
+      <c r="C749">
         <v>26</v>
       </c>
-      <c r="D749" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E749" s="29" t="s">
+      <c r="D749" t="s">
+        <v>32</v>
+      </c>
+      <c r="E749" s="2" t="s">
         <v>680</v>
       </c>
-      <c r="F749" s="28">
+      <c r="F749">
         <v>4</v>
       </c>
     </row>
     <row r="750" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A750" s="28">
-        <v>7</v>
-      </c>
-      <c r="B750" s="28" t="s">
+      <c r="A750">
+        <v>7</v>
+      </c>
+      <c r="B750" t="s">
         <v>60</v>
       </c>
-      <c r="C750" s="28">
+      <c r="C750">
         <v>27</v>
       </c>
-      <c r="D750" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E750" s="29" t="s">
+      <c r="D750" t="s">
+        <v>32</v>
+      </c>
+      <c r="E750" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="F750" s="28">
+      <c r="F750">
         <v>5</v>
       </c>
     </row>
     <row r="751" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A751" s="28">
-        <v>7</v>
-      </c>
-      <c r="B751" s="28" t="s">
+      <c r="A751">
+        <v>7</v>
+      </c>
+      <c r="B751" t="s">
         <v>61</v>
       </c>
-      <c r="C751" s="28">
+      <c r="C751">
         <v>28</v>
       </c>
-      <c r="D751" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E751" s="29" t="s">
+      <c r="D751" t="s">
+        <v>32</v>
+      </c>
+      <c r="E751" s="2" t="s">
         <v>682</v>
       </c>
-      <c r="F751" s="28">
+      <c r="F751">
         <v>5</v>
       </c>
     </row>
     <row r="752" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A752" s="28">
-        <v>7</v>
-      </c>
-      <c r="B752" s="28" t="s">
+      <c r="A752">
+        <v>7</v>
+      </c>
+      <c r="B752" t="s">
         <v>62</v>
       </c>
-      <c r="C752" s="28">
+      <c r="C752">
         <v>29</v>
       </c>
-      <c r="D752" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E752" s="29" t="s">
+      <c r="D752" t="s">
+        <v>32</v>
+      </c>
+      <c r="E752" s="2" t="s">
         <v>683</v>
       </c>
-      <c r="F752" s="28">
+      <c r="F752">
         <v>4</v>
       </c>
     </row>
     <row r="753" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A753" s="28">
-        <v>7</v>
-      </c>
-      <c r="B753" s="28" t="s">
+      <c r="A753">
+        <v>7</v>
+      </c>
+      <c r="B753" t="s">
         <v>63</v>
       </c>
-      <c r="C753" s="28">
+      <c r="C753">
         <v>30</v>
       </c>
-      <c r="D753" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E753" s="29" t="s">
+      <c r="D753" t="s">
+        <v>32</v>
+      </c>
+      <c r="E753" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="F753" s="28">
+      <c r="F753">
         <v>5</v>
       </c>
     </row>
     <row r="754" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A754" s="28">
-        <v>7</v>
-      </c>
-      <c r="B754" s="28" t="s">
+      <c r="A754">
+        <v>7</v>
+      </c>
+      <c r="B754" t="s">
         <v>64</v>
       </c>
-      <c r="C754" s="28">
+      <c r="C754">
         <v>31</v>
       </c>
-      <c r="D754" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E754" s="29" t="s">
+      <c r="D754" t="s">
+        <v>32</v>
+      </c>
+      <c r="E754" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="F754" s="28">
+      <c r="F754">
         <v>3</v>
       </c>
     </row>
     <row r="755" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A755" s="28">
-        <v>7</v>
-      </c>
-      <c r="B755" s="28" t="s">
+      <c r="A755">
+        <v>7</v>
+      </c>
+      <c r="B755" t="s">
         <v>65</v>
       </c>
-      <c r="C755" s="28">
-        <v>32</v>
-      </c>
-      <c r="D755" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E755" s="29" t="s">
+      <c r="C755">
+        <v>32</v>
+      </c>
+      <c r="D755" t="s">
+        <v>32</v>
+      </c>
+      <c r="E755" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="F755" s="28">
+      <c r="F755">
         <v>5</v>
       </c>
     </row>
     <row r="756" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A756" s="28">
-        <v>7</v>
-      </c>
-      <c r="B756" s="28" t="s">
+      <c r="A756">
+        <v>7</v>
+      </c>
+      <c r="B756" t="s">
         <v>66</v>
       </c>
-      <c r="C756" s="28">
+      <c r="C756">
         <v>33</v>
       </c>
-      <c r="D756" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E756" s="29" t="s">
+      <c r="D756" t="s">
+        <v>32</v>
+      </c>
+      <c r="E756" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="F756" s="28">
+      <c r="F756">
         <v>4.5</v>
       </c>
     </row>
     <row r="757" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A757" s="28">
-        <v>7</v>
-      </c>
-      <c r="B757" s="28" t="s">
+      <c r="A757">
+        <v>7</v>
+      </c>
+      <c r="B757" t="s">
         <v>67</v>
       </c>
-      <c r="C757" s="28">
+      <c r="C757">
         <v>34</v>
       </c>
-      <c r="D757" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E757" s="29" t="s">
+      <c r="D757" t="s">
+        <v>32</v>
+      </c>
+      <c r="E757" s="2" t="s">
         <v>699</v>
       </c>
-      <c r="F757" s="28">
+      <c r="F757">
         <v>4</v>
       </c>
     </row>
     <row r="758" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A758" s="28">
-        <v>7</v>
-      </c>
-      <c r="B758" s="28" t="s">
+      <c r="A758">
+        <v>7</v>
+      </c>
+      <c r="B758" t="s">
         <v>68</v>
       </c>
-      <c r="C758" s="28">
+      <c r="C758">
         <v>35</v>
       </c>
-      <c r="D758" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E758" s="29" t="s">
+      <c r="D758" t="s">
+        <v>32</v>
+      </c>
+      <c r="E758" s="2" t="s">
         <v>688</v>
       </c>
-      <c r="F758" s="28">
+      <c r="F758">
         <v>2</v>
       </c>
     </row>
     <row r="759" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A759" s="28">
-        <v>7</v>
-      </c>
-      <c r="B759" s="28" t="s">
+      <c r="A759">
+        <v>7</v>
+      </c>
+      <c r="B759" t="s">
         <v>69</v>
       </c>
-      <c r="C759" s="28">
+      <c r="C759">
         <v>36</v>
       </c>
-      <c r="D759" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E759" s="29" t="s">
+      <c r="D759" t="s">
+        <v>32</v>
+      </c>
+      <c r="E759" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="F759" s="28"/>
+      <c r="F759"/>
     </row>
     <row r="760" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A760" s="28">
-        <v>7</v>
-      </c>
-      <c r="B760" s="28" t="s">
+      <c r="A760">
+        <v>7</v>
+      </c>
+      <c r="B760" t="s">
         <v>70</v>
       </c>
-      <c r="C760" s="28">
+      <c r="C760">
         <v>37</v>
       </c>
-      <c r="D760" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E760" s="29" t="s">
+      <c r="D760" t="s">
+        <v>32</v>
+      </c>
+      <c r="E760" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="F760" s="28"/>
+      <c r="F760"/>
     </row>
     <row r="761" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A761" s="28">
-        <v>7</v>
-      </c>
-      <c r="B761" s="28" t="s">
+      <c r="A761">
+        <v>7</v>
+      </c>
+      <c r="B761" t="s">
         <v>71</v>
       </c>
-      <c r="C761" s="28">
+      <c r="C761">
         <v>38</v>
       </c>
-      <c r="D761" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E761" s="29" t="s">
+      <c r="D761" t="s">
+        <v>32</v>
+      </c>
+      <c r="E761" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="F761" s="28"/>
+      <c r="F761"/>
     </row>
     <row r="762" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A762" s="28">
-        <v>7</v>
-      </c>
-      <c r="B762" s="28" t="s">
+      <c r="A762">
+        <v>7</v>
+      </c>
+      <c r="B762" t="s">
         <v>72</v>
       </c>
-      <c r="C762" s="28">
+      <c r="C762">
         <v>39</v>
       </c>
-      <c r="D762" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E762" s="29" t="s">
+      <c r="D762" t="s">
+        <v>32</v>
+      </c>
+      <c r="E762" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="F762" s="28"/>
+      <c r="F762"/>
     </row>
     <row r="763" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A763" s="28">
-        <v>7</v>
-      </c>
-      <c r="B763" s="28" t="s">
+      <c r="A763">
+        <v>7</v>
+      </c>
+      <c r="B763" t="s">
         <v>73</v>
       </c>
-      <c r="C763" s="28">
+      <c r="C763">
         <v>40</v>
       </c>
-      <c r="D763" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E763" s="29" t="s">
+      <c r="D763" t="s">
+        <v>32</v>
+      </c>
+      <c r="E763" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="F763" s="28"/>
+      <c r="F763"/>
     </row>
     <row r="764" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A764" s="28">
-        <v>7</v>
-      </c>
-      <c r="B764" s="28" t="s">
+      <c r="A764">
+        <v>7</v>
+      </c>
+      <c r="B764" t="s">
         <v>74</v>
       </c>
-      <c r="C764" s="28">
+      <c r="C764">
         <v>41</v>
       </c>
-      <c r="D764" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E764" s="29" t="s">
+      <c r="D764" t="s">
+        <v>32</v>
+      </c>
+      <c r="E764" s="2" t="s">
         <v>694</v>
       </c>
-      <c r="F764" s="28"/>
+      <c r="F764"/>
     </row>
     <row r="765" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A765" s="28">
-        <v>7</v>
-      </c>
-      <c r="B765" s="28" t="s">
+      <c r="A765">
+        <v>7</v>
+      </c>
+      <c r="B765" t="s">
         <v>75</v>
       </c>
-      <c r="C765" s="28">
+      <c r="C765">
         <v>42</v>
       </c>
-      <c r="D765" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E765" s="29" t="s">
+      <c r="D765" t="s">
+        <v>32</v>
+      </c>
+      <c r="E765" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="F765" s="28"/>
+      <c r="F765"/>
     </row>
     <row r="766" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A766" s="28">
-        <v>7</v>
-      </c>
-      <c r="B766" s="28" t="s">
+      <c r="A766">
+        <v>7</v>
+      </c>
+      <c r="B766" t="s">
         <v>76</v>
       </c>
-      <c r="C766" s="28">
+      <c r="C766">
         <v>43</v>
       </c>
-      <c r="D766" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E766" s="29" t="s">
+      <c r="D766" t="s">
+        <v>32</v>
+      </c>
+      <c r="E766" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="F766" s="28"/>
+      <c r="F766"/>
     </row>
     <row r="767" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A767" s="28">
-        <v>7</v>
-      </c>
-      <c r="B767" s="28" t="s">
+      <c r="A767">
+        <v>7</v>
+      </c>
+      <c r="B767" t="s">
         <v>77</v>
       </c>
-      <c r="C767" s="28">
+      <c r="C767">
         <v>44</v>
       </c>
-      <c r="D767" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E767" s="29" t="s">
+      <c r="D767" t="s">
+        <v>32</v>
+      </c>
+      <c r="E767" s="2" t="s">
         <v>697</v>
       </c>
-      <c r="F767" s="28">
+      <c r="F767">
         <v>5</v>
       </c>
     </row>
     <row r="768" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A768" s="28">
-        <v>7</v>
-      </c>
-      <c r="B768" s="28" t="s">
+      <c r="A768">
+        <v>7</v>
+      </c>
+      <c r="B768" t="s">
         <v>106</v>
       </c>
-      <c r="C768" s="28">
+      <c r="C768">
         <v>45</v>
       </c>
-      <c r="D768" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="E768" s="29" t="s">
+      <c r="D768" t="s">
+        <v>32</v>
+      </c>
+      <c r="E768" s="2" t="s">
         <v>698</v>
       </c>
-      <c r="F768" s="28"/>
+      <c r="F768"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18939,6 +18844,9 @@
       <c r="B2" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="C2" s="8" t="s">
+        <v>700</v>
+      </c>
     </row>
     <row r="3" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -18947,6 +18855,9 @@
       <c r="B3" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="C3" s="8" t="s">
+        <v>701</v>
+      </c>
     </row>
     <row r="4" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -18954,6 +18865,9 @@
       </c>
       <c r="B4" s="1" t="s">
         <v>24</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>702</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
@@ -18963,6 +18877,9 @@
       <c r="B5" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="C5" s="8" t="s">
+        <v>703</v>
+      </c>
     </row>
     <row r="6" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -18971,6 +18888,9 @@
       <c r="B6" s="1" t="s">
         <v>26</v>
       </c>
+      <c r="C6" s="8" t="s">
+        <v>704</v>
+      </c>
     </row>
     <row r="7" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -18979,6 +18899,9 @@
       <c r="B7" s="1" t="s">
         <v>27</v>
       </c>
+      <c r="C7" s="8" t="s">
+        <v>705</v>
+      </c>
     </row>
     <row r="8" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -18986,6 +18909,9 @@
       </c>
       <c r="B8" s="1" t="s">
         <v>28</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>706</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">

--- a/data/values.xlsx
+++ b/data/values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\extreme_weather_risk\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15F6972D-F1B0-4060-BEE6-242680179736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39BCE727-0745-4796-B16B-D28CDC0DBD45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25710" yWindow="-4220" windowWidth="19070" windowHeight="12010" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="responses" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2559" uniqueCount="707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2561" uniqueCount="709">
   <si>
     <t>id_I</t>
   </si>
@@ -3795,6 +3795,12 @@
   </si>
   <si>
     <t>sto</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>max</t>
   </si>
 </sst>
 </file>
@@ -18178,14 +18184,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB0C1215-8C4B-4DD1-B4FD-B5114F43AD08}">
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="3" width="68.77734375" style="2" customWidth="1"/>
     <col min="4" max="4" width="9.88671875" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -18198,8 +18204,14 @@
       <c r="D1" s="8" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E1" t="s">
+        <v>707</v>
+      </c>
+      <c r="F1" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2</v>
       </c>
@@ -18212,8 +18224,14 @@
       <c r="D2" s="8" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>3</v>
       </c>
@@ -18226,8 +18244,14 @@
       <c r="D3" s="8" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>4</v>
       </c>
@@ -18240,8 +18264,14 @@
       <c r="D4" s="8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>5</v>
       </c>
@@ -18254,8 +18284,14 @@
       <c r="D5" s="9" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>6</v>
       </c>
@@ -18268,8 +18304,14 @@
       <c r="D6" s="9" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>7</v>
       </c>
@@ -18282,8 +18324,14 @@
       <c r="D7" s="8" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>8</v>
       </c>
@@ -18296,8 +18344,14 @@
       <c r="D8" s="8" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>9</v>
       </c>
@@ -18310,8 +18364,14 @@
       <c r="D9" s="8" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>10</v>
       </c>
@@ -18324,8 +18384,14 @@
       <c r="D10" s="8" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>11</v>
       </c>
@@ -18339,7 +18405,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>12</v>
       </c>
@@ -18353,7 +18419,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>13</v>
       </c>
@@ -18366,8 +18432,14 @@
       <c r="D13" s="8" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>14</v>
       </c>
@@ -18380,8 +18452,14 @@
       <c r="D14" s="8" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>15</v>
       </c>
@@ -18394,8 +18472,14 @@
       <c r="D15" s="8" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>16</v>
       </c>
@@ -18408,8 +18492,14 @@
       <c r="D16" s="9" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>17</v>
       </c>
@@ -18422,8 +18512,14 @@
       <c r="D17" s="9" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>18</v>
       </c>
@@ -18436,8 +18532,14 @@
       <c r="D18" s="9" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>19</v>
       </c>
@@ -18450,8 +18552,14 @@
       <c r="D19" s="9" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>20</v>
       </c>
@@ -18464,8 +18572,14 @@
       <c r="D20" s="8" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>21</v>
       </c>
@@ -18478,8 +18592,14 @@
       <c r="D21" s="9" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>22</v>
       </c>
@@ -18492,8 +18612,14 @@
       <c r="D22" s="8" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>23</v>
       </c>
@@ -18506,8 +18632,14 @@
       <c r="D23" s="9" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>24</v>
       </c>
@@ -18520,8 +18652,14 @@
       <c r="D24" s="9" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>25</v>
       </c>
@@ -18534,8 +18672,14 @@
       <c r="D25" s="7" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26</v>
       </c>
@@ -18548,8 +18692,14 @@
       <c r="D26" s="8" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>27</v>
       </c>
@@ -18562,8 +18712,14 @@
       <c r="D27" s="7" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>28</v>
       </c>
@@ -18576,8 +18732,14 @@
       <c r="D28" s="7" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>29</v>
       </c>
@@ -18590,8 +18752,14 @@
       <c r="D29" s="7" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>30</v>
       </c>
@@ -18604,8 +18772,14 @@
       <c r="D30" s="7" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>31</v>
       </c>
@@ -18618,8 +18792,14 @@
       <c r="D31" s="8" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="F31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>32</v>
       </c>
@@ -18632,8 +18812,14 @@
       <c r="D32" s="7" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>33</v>
       </c>
@@ -18646,8 +18832,14 @@
       <c r="D33" s="7" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E33">
+        <v>1</v>
+      </c>
+      <c r="F33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>34</v>
       </c>
@@ -18660,8 +18852,14 @@
       <c r="D34" s="7" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E34">
+        <v>1</v>
+      </c>
+      <c r="F34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>35</v>
       </c>
@@ -18674,8 +18872,14 @@
       <c r="D35" s="8" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E35">
+        <v>1</v>
+      </c>
+      <c r="F35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>36</v>
       </c>
@@ -18689,7 +18893,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>37</v>
       </c>
@@ -18703,7 +18907,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>38</v>
       </c>
@@ -18717,7 +18921,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>39</v>
       </c>
@@ -18731,7 +18935,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>40</v>
       </c>
@@ -18745,7 +18949,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>41</v>
       </c>
@@ -18759,7 +18963,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>42</v>
       </c>
@@ -18773,7 +18977,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>43</v>
       </c>
@@ -18787,7 +18991,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>44</v>
       </c>
@@ -18800,8 +19004,14 @@
       <c r="D44" s="8" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E44">
+        <v>1</v>
+      </c>
+      <c r="F44">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>45</v>
       </c>
